--- a/Versão5/SIS/Ontologia_Incendio.xlsx
+++ b/Versão5/SIS/Ontologia_Incendio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\INCE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53C8499-09BC-4323-88D1-623EF11E316C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFB7C6F-069D-4B24-BF90-050EB17632BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -2162,15 +2162,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="56" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="56" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="56"/>
+    <col min="1" max="1" width="8.69140625" style="56" customWidth="1"/>
+    <col min="2" max="2" width="40.15234375" style="56" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2260,7 +2260,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2315,7 +2315,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -2359,19 +2359,19 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46244.666254629628</v>
+        <v>46249.428025578702</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>88</v>
       </c>
@@ -2447,35 +2447,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA35"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="62" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.7109375" style="54" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8" style="54" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" style="54" customWidth="1"/>
-    <col min="16" max="16" width="83.85546875" style="54" customWidth="1"/>
-    <col min="17" max="17" width="88.7109375" style="54" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.42578125" style="54" customWidth="1"/>
-    <col min="22" max="22" width="4.7109375" style="54" customWidth="1"/>
-    <col min="23" max="23" width="7.140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="65.85546875" style="54" customWidth="1"/>
-    <col min="25" max="25" width="35.5703125" style="55" customWidth="1"/>
-    <col min="26" max="26" width="5.5703125" style="54" customWidth="1"/>
-    <col min="27" max="27" width="82.140625" style="54" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="54"/>
+    <col min="1" max="1" width="1.765625" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.921875" style="62" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.4609375" style="54" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.23046875" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.15234375" style="54" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="80.921875" style="54" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="86.15234375" style="54" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.4609375" style="54" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.07421875" style="54" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.07421875" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="59.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="28.765625" style="55" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="80.4609375" style="54" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
         <v>93</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="60">
         <v>2</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>Building Fire Fighting System</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="60">
         <v>3</v>
       </c>
@@ -2739,7 +2739,7 @@
         <v>Device that signals the existence of a condition or situation of danger.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="60">
         <v>4</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>Audible alarm.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="60">
         <v>5</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>Alarm activation mechanism in which a protective glass needs to be broken to allow the button to be pressed.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="60">
         <v>6</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>Visual light alarm.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="60">
         <v>7</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>Alarm activation mechanism in which activation occurs by a pulling action.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="60">
         <v>8</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>A coin-sized device that is used as a high warning signal to train train drivers.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="60">
         <v>9</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>Audible alarm produced by a siren.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="60">
         <v>10</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>Audible alarm produced by a whistle.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="60">
         <v>11</v>
       </c>
@@ -3467,7 +3467,7 @@
         <v>Fire suppression terminal has the purpose of providing a fluid (gas or liquid) that will suppress.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="60">
         <v>12</v>
       </c>
@@ -3558,7 +3558,7 @@
         <v>Symmetrical pipe connection that joins two or more inlets into a single pipe.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="60">
         <v>13</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>Support structure on which a hose can be wound.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="60">
         <v>14</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>Fire monitor.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="60">
         <v>15</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>Smoke detector.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="60">
         <v>16</v>
       </c>
@@ -3922,7 +3922,7 @@
         <v>A device, installed in a pipe, through which a temporary supply of water can be supplied.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="60">
         <v>17</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>A device for spraying water from a pipe under pressure over an area.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="60">
         <v>18</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>Device connected to a sprinkler to divert the flow of water in a propagation pattern to cover what is needed.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="60">
         <v>19</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>Water system accessory like brackets, hooks, pedestals, etc.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="60">
         <v>20</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>Upper Cistern</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="60">
         <v>21</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>Intermediate Cistern</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="60">
         <v>22</v>
       </c>
@@ -4467,7 +4467,7 @@
         <v>Lower Cistern</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="60">
         <v>23</v>
       </c>
@@ -4558,7 +4558,7 @@
         <v>Cold Water Pipe</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="60">
         <v>24</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>Cold Water Pipe</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="60">
         <v>25</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>Fire door that closed prevents the passage of fire and smoke.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="60">
         <v>26</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>Walls and partitions that limit the spread of flames thanks to their fire resistance properties, designed specifically for this function.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="60">
         <v>27</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>Shafts and vertical passages designed with intumescent sealing, smoke-free dumpers and fire barriers on each floor.</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="60">
         <v>28</v>
       </c>
@@ -5013,7 +5013,7 @@
         <v>Sprinkler Pendant is an automatic shower installed on the ceiling with the water jet down.</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="60">
         <v>29</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>Upright Sprinkler is an automatic shower installed in exposed piping below the ceiling with the water jet up.</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="60">
         <v>30</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>Side Sprinkler is an automatic shower installed on walls, ideal for corridors.</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="60">
         <v>31</v>
       </c>
@@ -5286,7 +5286,7 @@
         <v>Detects very small particles of smoke in fast-burning fires.</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="60">
         <v>32</v>
       </c>
@@ -5377,7 +5377,7 @@
         <v>It detects smoke by scattering light in an internal chamber. Most effective on smoldering fires (dense smoke). It is the most common type in residential and commercial buildings.</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="60">
         <v>33</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>It detects using a network of pipes that continuously sucks in air from the environment. Detects very small particles, allowing early detection. Ideal for data centers, museums, libraries, and critical environments.</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="60">
         <v>34</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>It detects thanks to a beam of light (laser or infrared) between emitter and receiver.</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="60">
         <v>35</v>
       </c>
@@ -5655,16 +5655,16 @@
     <sortCondition ref="F2:F883"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AA2:AA35 A2:B35">
+  <conditionalFormatting sqref="A2:B35 AA2:AA35">
     <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="22" priority="1514"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F2 F19:F1048576">
-    <cfRule type="duplicateValues" dxfId="22" priority="1536"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="21" priority="1514"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1536"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
     <cfRule type="duplicateValues" dxfId="20" priority="1558"/>
@@ -5708,6 +5708,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -5715,15 +5718,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -5788,7 +5791,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -5853,7 +5856,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -5936,15 +5939,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -5967,7 +5970,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -6023,30 +6026,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S22"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" customWidth="1"/>
-    <col min="7" max="7" width="56.140625" customWidth="1"/>
-    <col min="8" max="8" width="5.140625" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" customWidth="1"/>
+    <col min="3" max="3" width="10.3828125" customWidth="1"/>
+    <col min="4" max="4" width="7.84375" customWidth="1"/>
+    <col min="5" max="5" width="7.53515625" customWidth="1"/>
+    <col min="6" max="6" width="5.15234375" customWidth="1"/>
+    <col min="7" max="7" width="56.15234375" customWidth="1"/>
+    <col min="8" max="8" width="5.15234375" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" customWidth="1"/>
-    <col min="15" max="15" width="33.5703125" customWidth="1"/>
-    <col min="16" max="16" width="4.7109375" customWidth="1"/>
-    <col min="17" max="17" width="42.85546875" customWidth="1"/>
-    <col min="18" max="18" width="6.7109375" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.84375" customWidth="1"/>
+    <col min="11" max="11" width="18.69140625" customWidth="1"/>
+    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.53515625" customWidth="1"/>
+    <col min="14" max="14" width="6.84375" customWidth="1"/>
+    <col min="15" max="15" width="33.53515625" customWidth="1"/>
+    <col min="16" max="16" width="4.69140625" customWidth="1"/>
+    <col min="17" max="17" width="42.84375" customWidth="1"/>
+    <col min="18" max="18" width="6.69140625" customWidth="1"/>
+    <col min="19" max="19" width="6.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -6105,7 +6108,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -6164,7 +6167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>3</v>
       </c>
@@ -6223,7 +6226,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>4</v>
       </c>
@@ -6282,7 +6285,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>5</v>
       </c>
@@ -6341,7 +6344,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20">
         <v>6</v>
       </c>
@@ -6400,7 +6403,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20">
         <v>7</v>
       </c>
@@ -6459,7 +6462,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20">
         <v>8</v>
       </c>
@@ -6518,7 +6521,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20">
         <v>9</v>
       </c>
@@ -6577,7 +6580,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20">
         <v>10</v>
       </c>
@@ -6636,7 +6639,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20">
         <v>11</v>
       </c>
@@ -6695,7 +6698,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20">
         <v>12</v>
       </c>
@@ -6754,7 +6757,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="20">
         <v>13</v>
       </c>
@@ -6813,7 +6816,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="20">
         <v>14</v>
       </c>
@@ -6872,7 +6875,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20">
         <v>15</v>
       </c>
@@ -6931,7 +6934,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20">
         <v>16</v>
       </c>
@@ -6990,7 +6993,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="20">
         <v>17</v>
       </c>
@@ -7049,7 +7052,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20">
         <v>18</v>
       </c>
@@ -7108,7 +7111,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20">
         <v>19</v>
       </c>
@@ -7167,7 +7170,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="20">
         <v>20</v>
       </c>
@@ -7226,7 +7229,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="20">
         <v>21</v>
       </c>
@@ -7285,7 +7288,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="20">
         <v>22</v>
       </c>

--- a/Versão5/SIS/Ontologia_Incendio.xlsx
+++ b/Versão5/SIS/Ontologia_Incendio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFB7C6F-069D-4B24-BF90-050EB17632BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66DA67A-C43A-44D9-A329-2347F90F88D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="349">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -321,12 +321,6 @@
     <t>é.dentro.de</t>
   </si>
   <si>
-    <t>CategoriaRvt</t>
-  </si>
-  <si>
-    <t>ClasseIfc</t>
-  </si>
-  <si>
     <t>ABNT</t>
   </si>
   <si>
@@ -969,6 +963,162 @@
   </si>
   <si>
     <t>"[ IfcSensorSMOKESENSOR : IfcFireSuppressionTerminalSPRINKLER : IfcPipeSegment : IfcPipeFitting ]"</t>
+  </si>
+  <si>
+    <t>Building Fire Fighting System</t>
+  </si>
+  <si>
+    <t>Device that signals the existence of a condition or situation of danger.</t>
+  </si>
+  <si>
+    <t>Audible alarm.</t>
+  </si>
+  <si>
+    <t>Alarm activation mechanism in which a protective glass needs to be broken to allow the button to be pressed.</t>
+  </si>
+  <si>
+    <t>Visual light alarm.</t>
+  </si>
+  <si>
+    <t>Alarm activation mechanism in which activation occurs by a pulling action.</t>
+  </si>
+  <si>
+    <t>A coin-sized device that is used as a high warning signal to train train drivers.</t>
+  </si>
+  <si>
+    <t>Audible alarm produced by a siren.</t>
+  </si>
+  <si>
+    <t>Audible alarm produced by a whistle.</t>
+  </si>
+  <si>
+    <t>Fire suppression terminal has the purpose of providing a fluid (gas or liquid) that will suppress.</t>
+  </si>
+  <si>
+    <t>Symmetrical pipe connection that joins two or more inlets into a single pipe.</t>
+  </si>
+  <si>
+    <t>Support structure on which a hose can be wound.</t>
+  </si>
+  <si>
+    <t>Fire monitor.</t>
+  </si>
+  <si>
+    <t>Smoke detector.</t>
+  </si>
+  <si>
+    <t>A device, installed in a pipe, through which a temporary supply of water can be supplied.</t>
+  </si>
+  <si>
+    <t>A device for spraying water from a pipe under pressure over an area.</t>
+  </si>
+  <si>
+    <t>Device connected to a sprinkler to divert the flow of water in a propagation pattern to cover what is needed.</t>
+  </si>
+  <si>
+    <t>Water system accessory like brackets, hooks, pedestals, etc.</t>
+  </si>
+  <si>
+    <t>Upper Cistern</t>
+  </si>
+  <si>
+    <t>Intermediate Cistern</t>
+  </si>
+  <si>
+    <t>Lower Cistern</t>
+  </si>
+  <si>
+    <t>Cold Water Pipe</t>
+  </si>
+  <si>
+    <t>Fire door that closed prevents the passage of fire and smoke.</t>
+  </si>
+  <si>
+    <t>Walls and partitions that limit the spread of flames thanks to their fire resistance properties, designed specifically for this function.</t>
+  </si>
+  <si>
+    <t>Shafts and vertical passages designed with intumescent sealing, smoke-free dumpers and fire barriers on each floor.</t>
+  </si>
+  <si>
+    <t>Sprinkler Pendant is an automatic shower installed on the ceiling with the water jet down.</t>
+  </si>
+  <si>
+    <t>Upright Sprinkler is an automatic shower installed in exposed piping below the ceiling with the water jet up.</t>
+  </si>
+  <si>
+    <t>Side Sprinkler is an automatic shower installed on walls, ideal for corridors.</t>
+  </si>
+  <si>
+    <t>Detects very small particles of smoke in fast-burning fires.</t>
+  </si>
+  <si>
+    <t>It detects smoke by scattering light in an internal chamber. Most effective on smoldering fires (dense smoke). It is the most common type in residential and commercial buildings.</t>
+  </si>
+  <si>
+    <t>It detects using a network of pipes that continuously sucks in air from the environment. Detects very small particles, allowing early detection. Ideal for data centers, museums, libraries, and critical environments.</t>
+  </si>
+  <si>
+    <t>It detects thanks to a beam of light (laser or infrared) between emitter and receiver.</t>
+  </si>
+  <si>
+    <t>Detector that integrates smoke and heat detection in the same device. Increases reliability, being indicated for industrial environments or with temperature variations.</t>
+  </si>
+  <si>
+    <t>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</t>
+  </si>
+  <si>
+    <t>Cisterna intermedia</t>
+  </si>
+  <si>
+    <t>Tubería de agua fría</t>
+  </si>
+  <si>
+    <t>La puerta cortafuegos que se cierra impide el paso del fuego y el humo.</t>
+  </si>
+  <si>
+    <t>Muros y tabiques que limitan la propagación de las llamas gracias a sus propiedades de resistencia al fuego, diseñados específicamente para esta función.</t>
+  </si>
+  <si>
+    <t>Pozos y pasadizos verticales diseñados con sellado intumescente, volcadores sin humo y barreras cortafuego en cada planta.</t>
+  </si>
+  <si>
+    <t>El colgante de aspersores es una ducha automática instalada en el techo con el chorro de agua hacia abajo.</t>
+  </si>
+  <si>
+    <t>El rociador vertical es una ducha automática instalada en tuberías expuestas bajo el techo con el chorro de agua hacia arriba.</t>
+  </si>
+  <si>
+    <t>El rociador lateral es una ducha automática instalada en las paredes, ideal para pasillos.</t>
+  </si>
+  <si>
+    <t>Detecta partículas muy pequeñas de humo en incendios de combustión rápida.</t>
+  </si>
+  <si>
+    <t>Detecta el humo dispersando la luz en una cámara interna. Más efectivo en incendios latentes (humo denso). Es el tipo más común en edificios residenciales y comerciales.</t>
+  </si>
+  <si>
+    <t>Detecta el uso de una red de tuberías que succiona continuamente aire del entorno. Detecta partículas muy pequeñas, permitiendo una detección temprana. Ideal para centros de datos, museos, bibliotecas y entornos críticos.</t>
+  </si>
+  <si>
+    <t>Detecta gracias a un haz de luz (láser o infrarrojo) entre el emisor y el receptor.</t>
+  </si>
+  <si>
+    <t>Detector que integra detección de humo y calor en el mismo dispositivo. Aumenta la fiabilidad, estando indicado para entornos industriales o con variaciones de temperatura.</t>
+  </si>
+  <si>
+    <t>Categoria Rvt</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>[ - ]</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>Classe IFC</t>
   </si>
 </sst>
 </file>
@@ -1504,7 +1654,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="26">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1577,6 +1727,22 @@
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2178,7 +2344,7 @@
         <v>45</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2189,7 +2355,7 @@
         <v>47</v>
       </c>
       <c r="C2" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2197,10 +2363,10 @@
         <v>48</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C3" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2211,7 +2377,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2223,7 +2389,7 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2235,7 +2401,7 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2246,7 +2412,7 @@
         <v>53</v>
       </c>
       <c r="C7" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2254,10 +2420,10 @@
         <v>54</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2268,7 +2434,7 @@
         <v>56</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2279,7 +2445,7 @@
         <v>58</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2290,7 +2456,7 @@
         <v>58</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2301,7 +2467,7 @@
         <v>58</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2312,7 +2478,7 @@
         <v>58</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2323,7 +2489,7 @@
         <v>58</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2334,7 +2500,7 @@
         <v>58</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2345,7 +2511,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2353,10 +2519,10 @@
         <v>65</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2365,10 +2531,10 @@
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46249.428025578702</v>
+        <v>46253.810137615743</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2379,7 +2545,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2390,7 +2556,7 @@
         <v>58</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2401,7 +2567,7 @@
         <v>58</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2409,10 +2575,10 @@
         <v>71</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2420,22 +2586,22 @@
         <v>72</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B24" s="16" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific Fire Fighting Objects</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2446,10 +2612,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.765625" customWidth="1"/>
+    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.23046875" style="54" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.3828125" style="54" bestFit="1" customWidth="1"/>
@@ -2462,22 +2628,24 @@
     <col min="15" max="15" width="14.15234375" style="54" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="80.921875" style="54" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="86.15234375" style="54" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.69140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.4609375" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.07421875" style="54" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.53515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.07421875" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="59.53515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="28.765625" style="55" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.84375" style="54" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="80.4609375" style="54" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.15234375" style="54"/>
+    <col min="18" max="18" width="80.4609375" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.4609375" style="54" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.07421875" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.07421875" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="59.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.765625" style="54" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="28.765625" style="55" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6" style="54" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B1" s="44" t="s">
         <v>42</v>
@@ -2510,7 +2678,7 @@
         <v>4</v>
       </c>
       <c r="L1" s="35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M1" s="35" t="s">
         <v>5</v>
@@ -2527,55 +2695,61 @@
       <c r="Q1" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="R1" s="35" t="s">
-        <v>95</v>
+      <c r="R1" s="36" t="s">
+        <v>84</v>
       </c>
       <c r="S1" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="T1" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="35" t="s">
+      <c r="U1" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="U1" s="46" t="s">
+      <c r="V1" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="35" t="s">
+      <c r="W1" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="58" t="s">
+      <c r="X1" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="35" t="s">
+      <c r="Y1" s="35" t="s">
+        <v>344</v>
+      </c>
+      <c r="Z1" s="35" t="s">
+        <v>345</v>
+      </c>
+      <c r="AA1" s="35" t="s">
+        <v>348</v>
+      </c>
+      <c r="AB1" s="35" t="s">
+        <v>347</v>
+      </c>
+      <c r="AC1" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="Y1" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z1" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA1" s="36" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="60">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F2" s="42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G2" s="61" t="s">
         <v>9</v>
@@ -2601,1345 +2775,1420 @@
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N2" s="33" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="O2" s="30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P2" s="52" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="Q2" s="52" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="R2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="30" t="str">
-        <f t="shared" ref="S2:U18" si="2">SUBSTITUTE(C2, ".", " ")</f>
+        <v>297</v>
+      </c>
+      <c r="S2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="30" t="str">
+        <f t="shared" ref="T2:V18" si="2">SUBSTITUTE(C2, ".", " ")</f>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T2" s="30" t="str">
-        <f t="shared" ref="T2:U16" si="3">SUBSTITUTE(D2, ".", " ")</f>
+      <c r="U2" s="30" t="str">
+        <f t="shared" ref="U2:V16" si="3">SUBSTITUTE(D2, ".", " ")</f>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U2" s="30" t="str">
+      <c r="V2" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Combate</v>
       </c>
-      <c r="V2" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W2" s="59" t="str">
-        <f t="shared" ref="W2:W27" si="4">CONCATENATE("Key-INC-",A2)</f>
+      <c r="W2" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X2" s="59" t="str">
+        <f t="shared" ref="X2:X27" si="4">CONCATENATE("Key-INC-",A2)</f>
         <v>Key-INC-2</v>
       </c>
-      <c r="X2" s="29" t="s">
+      <c r="Y2" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z2" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA2" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="Y2" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z2" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA2" s="30" t="str">
-        <f t="shared" ref="AA2:AA35" si="5">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Building Fire Fighting System</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB2" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC2" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="60">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F3" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="G3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="33" t="str">
+        <f t="shared" ref="L3:M19" si="5">CONCATENATE("", C3)</f>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M3" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N3" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O3" s="33" t="str">
+        <f t="shared" ref="O3:O17" si="6">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F3),"."," ")," De "," de "))</f>
+        <v>Alarme</v>
+      </c>
+      <c r="P3" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q3" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="G3" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="33" t="str">
-        <f t="shared" ref="L3:M19" si="6">CONCATENATE("", C3)</f>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M3" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N3" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O3" s="33" t="str">
-        <f t="shared" ref="O3:O17" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F3),"."," ")," De "," de "))</f>
-        <v>Alarme</v>
-      </c>
-      <c r="P3" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q3" s="30" t="s">
-        <v>123</v>
-      </c>
       <c r="R3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="30" t="str">
+        <v>298</v>
+      </c>
+      <c r="S3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T3" s="30" t="str">
+      <c r="U3" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U3" s="30" t="str">
+      <c r="V3" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V3" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W3" s="59" t="str">
+      <c r="W3" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X3" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-3</v>
       </c>
-      <c r="X3" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y3" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z3" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA3" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Device that signals the existence of a condition or situation of danger.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y3" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z3" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA3" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB3" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC3" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="60">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F4" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M4" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N4" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O4" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Alarme Campainha</v>
+      </c>
+      <c r="P4" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q4" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="G4" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M4" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N4" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O4" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Alarme Campainha</v>
-      </c>
-      <c r="P4" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q4" s="30" t="s">
-        <v>126</v>
-      </c>
       <c r="R4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="30" t="str">
+        <v>299</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T4" s="30" t="str">
+      <c r="U4" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U4" s="30" t="str">
+      <c r="V4" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V4" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W4" s="59" t="str">
+      <c r="W4" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X4" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-4</v>
       </c>
-      <c r="X4" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y4" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z4" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA4" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Audible alarm.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y4" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z4" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA4" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB4" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC4" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="60">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F5" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M5" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N5" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O5" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Alarme Campainha Caixa</v>
+      </c>
+      <c r="P5" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q5" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="G5" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M5" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N5" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O5" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Alarme Campainha Caixa</v>
-      </c>
-      <c r="P5" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q5" s="30" t="s">
-        <v>129</v>
-      </c>
       <c r="R5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="30" t="str">
+        <v>300</v>
+      </c>
+      <c r="S5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T5" s="30" t="str">
+      <c r="U5" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U5" s="30" t="str">
+      <c r="V5" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V5" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W5" s="59" t="str">
+      <c r="W5" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X5" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-5</v>
       </c>
-      <c r="X5" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y5" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="Z5" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA5" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Alarm activation mechanism in which a protective glass needs to be broken to allow the button to be pressed.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y5" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z5" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA5" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB5" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC5" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="60">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F6" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="G6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M6" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N6" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O6" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Alarme Lumínico</v>
+      </c>
+      <c r="P6" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q6" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="G6" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M6" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N6" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O6" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Alarme Lumínico</v>
-      </c>
-      <c r="P6" s="30" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q6" s="30" t="s">
-        <v>132</v>
-      </c>
       <c r="R6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="30" t="str">
+        <v>301</v>
+      </c>
+      <c r="S6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T6" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T6" s="30" t="str">
+      <c r="U6" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U6" s="30" t="str">
+      <c r="V6" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V6" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W6" s="59" t="str">
+      <c r="W6" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X6" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-6</v>
       </c>
-      <c r="X6" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y6" s="29" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z6" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA6" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Visual light alarm.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y6" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z6" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA6" s="29" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB6" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC6" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="60">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F7" s="57" t="s">
+        <v>131</v>
+      </c>
+      <c r="G7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M7" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N7" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O7" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Alarme Caixa Manual</v>
+      </c>
+      <c r="P7" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q7" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="G7" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M7" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N7" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O7" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Alarme Caixa Manual</v>
-      </c>
-      <c r="P7" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q7" s="30" t="s">
-        <v>135</v>
-      </c>
       <c r="R7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="30" t="str">
+        <v>302</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T7" s="30" t="str">
+      <c r="U7" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U7" s="30" t="str">
+      <c r="V7" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V7" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W7" s="59" t="str">
+      <c r="W7" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X7" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-7</v>
       </c>
-      <c r="X7" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y7" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z7" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA7" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Alarm activation mechanism in which activation occurs by a pulling action.</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y7" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z7" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA7" s="29" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB7" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC7" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="60">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F8" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M8" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N8" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O8" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Alarme Detonador</v>
+      </c>
+      <c r="P8" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q8" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="G8" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M8" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N8" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O8" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Alarme Detonador</v>
-      </c>
-      <c r="P8" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q8" s="30" t="s">
-        <v>138</v>
-      </c>
       <c r="R8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="30" t="str">
+        <v>303</v>
+      </c>
+      <c r="S8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T8" s="30" t="str">
+      <c r="U8" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U8" s="30" t="str">
+      <c r="V8" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V8" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W8" s="59" t="str">
+      <c r="W8" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X8" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-8</v>
       </c>
-      <c r="X8" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y8" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="Z8" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA8" s="30" t="str">
+      <c r="Y8" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z8" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA8" s="29" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB8" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC8" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="60">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>292</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F9" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="G9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="33" t="str">
         <f t="shared" si="5"/>
-        <v>A coin-sized device that is used as a high warning signal to train train drivers.</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="60">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F9" s="57" t="s">
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M9" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O9" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Alarme Sirene</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="G9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M9" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N9" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O9" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Alarme Sirene</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q9" s="30" t="s">
-        <v>141</v>
-      </c>
       <c r="R9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="30" t="str">
+        <v>304</v>
+      </c>
+      <c r="S9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T9" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T9" s="30" t="str">
+      <c r="U9" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U9" s="30" t="str">
+      <c r="V9" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V9" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W9" s="59" t="str">
+      <c r="W9" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X9" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-9</v>
       </c>
-      <c r="X9" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y9" s="29" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z9" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA9" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Audible alarm produced by a siren.</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y9" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z9" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA9" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB9" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC9" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="60">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F10" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="G10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M10" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N10" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O10" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Alarme Apito</v>
+      </c>
+      <c r="P10" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q10" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="G10" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M10" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N10" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O10" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Alarme Apito</v>
-      </c>
-      <c r="P10" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q10" s="30" t="s">
-        <v>144</v>
-      </c>
       <c r="R10" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="30" t="str">
+        <v>305</v>
+      </c>
+      <c r="S10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T10" s="30" t="str">
+      <c r="U10" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U10" s="30" t="str">
+      <c r="V10" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Alarmes de Incêndio</v>
       </c>
-      <c r="V10" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W10" s="59" t="str">
+      <c r="W10" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X10" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-10</v>
       </c>
-      <c r="X10" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y10" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="Z10" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA10" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Audible alarm produced by a whistle.</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y10" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z10" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA10" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB10" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC10" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="60">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F11" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="G11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M11" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N11" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="O11" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Terminal Combate Fogo</v>
+      </c>
+      <c r="P11" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q11" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="G11" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M11" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N11" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="O11" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Terminal Combate Fogo</v>
-      </c>
-      <c r="P11" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q11" s="30" t="s">
-        <v>147</v>
-      </c>
       <c r="R11" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="30" t="str">
+        <v>306</v>
+      </c>
+      <c r="S11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T11" s="30" t="str">
+      <c r="U11" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U11" s="30" t="str">
+      <c r="V11" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V11" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W11" s="59" t="str">
+      <c r="W11" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X11" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-11</v>
       </c>
-      <c r="X11" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y11" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z11" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA11" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Fire suppression terminal has the purpose of providing a fluid (gas or liquid) that will suppress.</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y11" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z11" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA11" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB11" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC11" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="60">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F12" s="57" t="s">
+        <v>146</v>
+      </c>
+      <c r="G12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M12" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N12" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="O12" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Mangueira Entrada</v>
+      </c>
+      <c r="P12" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q12" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="G12" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L12" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M12" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N12" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="O12" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Mangueira Entrada</v>
-      </c>
-      <c r="P12" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q12" s="30" t="s">
-        <v>150</v>
-      </c>
       <c r="R12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="30" t="str">
+        <v>307</v>
+      </c>
+      <c r="S12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T12" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T12" s="30" t="str">
+      <c r="U12" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U12" s="30" t="str">
+      <c r="V12" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V12" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W12" s="59" t="str">
+      <c r="W12" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X12" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-12</v>
       </c>
-      <c r="X12" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y12" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z12" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA12" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Symmetrical pipe connection that joins two or more inlets into a single pipe.</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y12" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z12" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA12" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB12" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC12" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="60">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F13" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="G13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M13" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N13" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="O13" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Mangueira Carretel</v>
+      </c>
+      <c r="P13" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q13" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="G13" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L13" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M13" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N13" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="O13" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Mangueira Carretel</v>
-      </c>
-      <c r="P13" s="30" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q13" s="30" t="s">
-        <v>153</v>
-      </c>
       <c r="R13" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S13" s="30" t="str">
+        <v>308</v>
+      </c>
+      <c r="S13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T13" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T13" s="30" t="str">
+      <c r="U13" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U13" s="30" t="str">
+      <c r="V13" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V13" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W13" s="59" t="str">
+      <c r="W13" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X13" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-13</v>
       </c>
-      <c r="X13" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y13" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z13" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA13" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Support structure on which a hose can be wound.</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y13" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z13" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA13" s="29" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB13" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC13" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="60">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F14" s="57" t="s">
+        <v>152</v>
+      </c>
+      <c r="G14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M14" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N14" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="O14" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Mangueira Canhão</v>
+      </c>
+      <c r="P14" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q14" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="G14" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L14" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M14" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N14" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="O14" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Mangueira Canhão</v>
-      </c>
-      <c r="P14" s="30" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q14" s="30" t="s">
-        <v>156</v>
-      </c>
       <c r="R14" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="30" t="str">
+        <v>309</v>
+      </c>
+      <c r="S14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T14" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T14" s="30" t="str">
+      <c r="U14" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U14" s="30" t="str">
+      <c r="V14" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V14" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W14" s="59" t="str">
+      <c r="W14" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X14" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-14</v>
       </c>
-      <c r="X14" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y14" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z14" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA14" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Fire monitor.</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y14" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z14" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA14" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="AB14" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC14" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="60">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F15" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="33" t="str">
+        <f t="shared" ref="L15" si="7">CONCATENATE("", C15)</f>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M15" s="33" t="str">
+        <f t="shared" ref="M15" si="8">CONCATENATE("", D15)</f>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N15" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="O15" s="33" t="str">
+        <f t="shared" ref="O15" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F15),"."," ")," De "," de "))</f>
+        <v>Detetor de Fumaça</v>
+      </c>
+      <c r="P15" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q15" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="G15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15" s="33" t="str">
-        <f t="shared" ref="L15" si="8">CONCATENATE("", C15)</f>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M15" s="33" t="str">
-        <f t="shared" ref="M15" si="9">CONCATENATE("", D15)</f>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N15" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="O15" s="33" t="str">
-        <f t="shared" ref="O15" si="10">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F15),"."," ")," De "," de "))</f>
-        <v>Detetor de Fumaça</v>
-      </c>
-      <c r="P15" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q15" s="30" t="s">
-        <v>216</v>
-      </c>
       <c r="R15" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S15" s="30" t="str">
-        <f t="shared" ref="S15" si="11">SUBSTITUTE(C15, ".", " ")</f>
+        <v>310</v>
+      </c>
+      <c r="S15" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T15" s="30" t="str">
+        <f t="shared" ref="T15" si="10">SUBSTITUTE(C15, ".", " ")</f>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T15" s="30" t="str">
-        <f t="shared" ref="T15" si="12">SUBSTITUTE(D15, ".", " ")</f>
+      <c r="U15" s="30" t="str">
+        <f t="shared" ref="U15" si="11">SUBSTITUTE(D15, ".", " ")</f>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U15" s="30" t="str">
-        <f t="shared" ref="U15" si="13">SUBSTITUTE(E15, ".", " ")</f>
+      <c r="V15" s="30" t="str">
+        <f t="shared" ref="V15" si="12">SUBSTITUTE(E15, ".", " ")</f>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V15" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W15" s="59" t="str">
+      <c r="W15" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X15" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-15</v>
       </c>
-      <c r="X15" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y15" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="Z15" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA15" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Smoke detector.</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y15" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z15" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA15" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB15" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC15" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="60">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F16" s="57" t="s">
+        <v>155</v>
+      </c>
+      <c r="G16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M16" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N16" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="O16" s="33" t="str">
+        <f t="shared" si="6"/>
+        <v>Hidrante</v>
+      </c>
+      <c r="P16" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q16" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="G16" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L16" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M16" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N16" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="O16" s="33" t="str">
-        <f t="shared" si="7"/>
-        <v>Hidrante</v>
-      </c>
-      <c r="P16" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q16" s="30" t="s">
-        <v>159</v>
-      </c>
       <c r="R16" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" s="30" t="str">
+        <v>311</v>
+      </c>
+      <c r="S16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T16" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T16" s="30" t="str">
+      <c r="U16" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U16" s="30" t="str">
+      <c r="V16" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V16" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W16" s="59" t="str">
+      <c r="W16" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X16" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-16</v>
       </c>
-      <c r="X16" s="30" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y16" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="Z16" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA16" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>A device, installed in a pipe, through which a temporary supply of water can be supplied.</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y16" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z16" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA16" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB16" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC16" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="60">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F17" s="57" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G17" s="61" t="s">
         <v>9</v>
@@ -3957,170 +4206,180 @@
         <v>9</v>
       </c>
       <c r="L17" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M17" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N17" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="O17" s="33" t="str">
         <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M17" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N17" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="O17" s="33" t="str">
-        <f t="shared" si="7"/>
         <v>Sprinkler</v>
       </c>
       <c r="P17" s="30" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Q17" s="30" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="R17" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S17" s="30" t="str">
+        <v>312</v>
+      </c>
+      <c r="S17" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T17" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T17" s="30" t="str">
+      <c r="U17" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U17" s="30" t="str">
+      <c r="V17" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V17" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W17" s="59" t="str">
+      <c r="W17" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X17" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-17</v>
       </c>
-      <c r="X17" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y17" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="Z17" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA17" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>A device for spraying water from a pipe under pressure over an area.</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y17" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z17" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA17" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB17" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC17" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="60">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F18" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="G18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M18" s="33" t="str">
+        <f t="shared" si="5"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N18" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="O18" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="P18" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q18" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="G18" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L18" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M18" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N18" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="O18" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="P18" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q18" s="30" t="s">
-        <v>164</v>
-      </c>
       <c r="R18" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S18" s="30" t="str">
+        <v>313</v>
+      </c>
+      <c r="S18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T18" s="30" t="str">
+      <c r="U18" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U18" s="30" t="str">
+      <c r="V18" s="30" t="str">
         <f t="shared" si="2"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V18" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W18" s="59" t="str">
+      <c r="W18" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X18" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-18</v>
       </c>
-      <c r="X18" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y18" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z18" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA18" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Device connected to a sprinkler to divert the flow of water in a propagation pattern to cover what is needed.</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y18" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z18" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA18" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="AB18" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC18" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="60">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F19" s="42" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G19" s="61" t="s">
         <v>9</v>
@@ -4138,81 +4397,85 @@
         <v>9</v>
       </c>
       <c r="L19" s="33" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M19" s="33" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N19" s="33" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="O19" s="52" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="P19" s="52" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q19" s="30" t="str">
-        <f t="shared" ref="Q19" si="14">_xlfn.TRANSLATE(P19,"pt","es")</f>
-        <v>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</v>
+        <v>106</v>
+      </c>
+      <c r="Q19" s="30" t="s">
+        <v>330</v>
       </c>
       <c r="R19" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S19" s="30" t="str">
-        <f t="shared" ref="S19:U24" si="15">SUBSTITUTE(C19, ".", " ")</f>
+        <v>314</v>
+      </c>
+      <c r="S19" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T19" s="30" t="str">
+        <f t="shared" ref="T19:V24" si="13">SUBSTITUTE(C19, ".", " ")</f>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T19" s="30" t="str">
-        <f t="shared" si="15"/>
+      <c r="U19" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U19" s="30" t="str">
-        <f t="shared" si="15"/>
+      <c r="V19" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Peças de Incêndio</v>
       </c>
-      <c r="V19" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W19" s="59" t="str">
+      <c r="W19" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X19" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-19</v>
       </c>
-      <c r="X19" s="30" t="s">
+      <c r="Y19" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z19" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA19" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="Y19" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z19" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA19" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Water system accessory like brackets, hooks, pedestals, etc.</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB19" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC19" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="60">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>208</v>
+      </c>
+      <c r="F20" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="E20" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="F20" s="42" t="s">
-        <v>117</v>
-      </c>
       <c r="G20" s="61" t="s">
         <v>9</v>
       </c>
@@ -4229,80 +4492,84 @@
         <v>9</v>
       </c>
       <c r="L20" s="33" t="str">
-        <f t="shared" ref="L20:L23" si="16">CONCATENATE("", C20)</f>
+        <f t="shared" ref="L20:L23" si="14">CONCATENATE("", C20)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M20" s="33" t="str">
-        <f t="shared" ref="M20:M23" si="17">CONCATENATE("", D20)</f>
+        <f t="shared" ref="M20:M23" si="15">CONCATENATE("", D20)</f>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N20" s="33" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O20" s="52" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="P20" s="52" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q20" s="30" t="str">
-        <f>_xlfn.TRANSLATE(P20,"pt","es")</f>
-        <v>Cisterna Superior</v>
+        <v>100</v>
+      </c>
+      <c r="Q20" s="30" t="s">
+        <v>100</v>
       </c>
       <c r="R20" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S20" s="30" t="str">
-        <f t="shared" si="15"/>
+        <v>315</v>
+      </c>
+      <c r="S20" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T20" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T20" s="30" t="str">
-        <f t="shared" si="15"/>
+      <c r="U20" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U20" s="30" t="str">
-        <f t="shared" si="15"/>
+      <c r="V20" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Tubulação de Incêndio</v>
       </c>
-      <c r="V20" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W20" s="59" t="str">
+      <c r="W20" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X20" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-20</v>
       </c>
-      <c r="X20" s="29" t="s">
-        <v>250</v>
-      </c>
       <c r="Y20" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z20" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA20" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Upper Cistern</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+      <c r="Z20" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA20" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB20" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC20" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="60">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F21" s="42" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G21" s="61" t="s">
         <v>9</v>
@@ -4320,80 +4587,84 @@
         <v>9</v>
       </c>
       <c r="L21" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M21" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N21" s="33" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O21" s="52" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P21" s="52" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q21" s="30" t="str">
-        <f t="shared" ref="Q21:Q27" si="18">_xlfn.TRANSLATE(P21,"pt","es")</f>
-        <v>Cisterna intermedia</v>
+        <v>103</v>
+      </c>
+      <c r="Q21" s="30" t="s">
+        <v>331</v>
       </c>
       <c r="R21" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S21" s="30" t="str">
-        <f t="shared" si="15"/>
+        <v>316</v>
+      </c>
+      <c r="S21" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T21" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T21" s="30" t="str">
-        <f t="shared" si="15"/>
+      <c r="U21" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U21" s="30" t="str">
-        <f t="shared" si="15"/>
+      <c r="V21" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Tubulação de Incêndio</v>
       </c>
-      <c r="V21" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W21" s="59" t="str">
+      <c r="W21" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X21" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-21</v>
       </c>
-      <c r="X21" s="29" t="s">
-        <v>250</v>
-      </c>
       <c r="Y21" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z21" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA21" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Intermediate Cistern</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+      <c r="Z21" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA21" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB21" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC21" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="60">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G22" s="61" t="s">
         <v>9</v>
@@ -4411,80 +4682,84 @@
         <v>9</v>
       </c>
       <c r="L22" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M22" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N22" s="33" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O22" s="52" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P22" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q22" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Cisterna Inferior</v>
+        <v>101</v>
+      </c>
+      <c r="Q22" s="30" t="s">
+        <v>101</v>
       </c>
       <c r="R22" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S22" s="30" t="str">
-        <f t="shared" si="15"/>
+        <v>317</v>
+      </c>
+      <c r="S22" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T22" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T22" s="30" t="str">
-        <f t="shared" si="15"/>
+      <c r="U22" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U22" s="30" t="str">
-        <f t="shared" si="15"/>
+      <c r="V22" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Tubulação de Incêndio</v>
       </c>
-      <c r="V22" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W22" s="59" t="str">
+      <c r="W22" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X22" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-22</v>
       </c>
-      <c r="X22" s="29" t="s">
-        <v>250</v>
-      </c>
       <c r="Y22" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z22" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA22" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Lower Cistern</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>248</v>
+      </c>
+      <c r="Z22" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA22" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB22" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC22" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="60">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F23" s="42" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G23" s="61" t="s">
         <v>9</v>
@@ -4502,80 +4777,84 @@
         <v>9</v>
       </c>
       <c r="L23" s="33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M23" s="33" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N23" s="33" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O23" s="52" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P23" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q23" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Tubería de agua fría</v>
+        <v>102</v>
+      </c>
+      <c r="Q23" s="30" t="s">
+        <v>332</v>
       </c>
       <c r="R23" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S23" s="30" t="str">
-        <f t="shared" si="15"/>
+        <v>318</v>
+      </c>
+      <c r="S23" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T23" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T23" s="30" t="str">
-        <f t="shared" si="15"/>
+      <c r="U23" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U23" s="30" t="str">
-        <f t="shared" si="15"/>
+      <c r="V23" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Tubulação de Incêndio</v>
       </c>
-      <c r="V23" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W23" s="59" t="str">
+      <c r="W23" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X23" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-23</v>
       </c>
-      <c r="X23" s="29" t="s">
-        <v>250</v>
-      </c>
       <c r="Y23" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="Z23" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA23" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Cold Water Pipe</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Z23" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA23" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB23" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC23" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="60">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E24" s="42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F24" s="42" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G24" s="61" t="s">
         <v>9</v>
@@ -4593,171 +4872,179 @@
         <v>9</v>
       </c>
       <c r="L24" s="33" t="str">
-        <f t="shared" ref="L24:L26" si="19">CONCATENATE("", C24)</f>
+        <f t="shared" ref="L24:L26" si="16">CONCATENATE("", C24)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M24" s="33" t="str">
-        <f t="shared" ref="M24:M26" si="20">CONCATENATE("", D24)</f>
+        <f t="shared" ref="M24:M26" si="17">CONCATENATE("", D24)</f>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N24" s="33" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O24" s="52" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P24" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q24" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Tubería de agua fría</v>
+        <v>102</v>
+      </c>
+      <c r="Q24" s="30" t="s">
+        <v>332</v>
       </c>
       <c r="R24" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S24" s="30" t="str">
-        <f t="shared" ref="S24:S26" si="21">SUBSTITUTE(C24, ".", " ")</f>
+        <v>318</v>
+      </c>
+      <c r="S24" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T24" s="30" t="str">
+        <f t="shared" ref="T24:T26" si="18">SUBSTITUTE(C24, ".", " ")</f>
         <v>Sistemas Prediais</v>
       </c>
-      <c r="T24" s="30" t="str">
-        <f t="shared" si="15"/>
+      <c r="U24" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Sistema Incêndio</v>
       </c>
-      <c r="U24" s="30" t="str">
-        <f t="shared" si="15"/>
+      <c r="V24" s="30" t="str">
+        <f t="shared" si="13"/>
         <v>Tubulação de Incêndio</v>
       </c>
-      <c r="V24" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W24" s="59" t="str">
+      <c r="W24" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X24" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-24</v>
       </c>
-      <c r="X24" s="29" t="s">
-        <v>250</v>
-      </c>
       <c r="Y24" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="Z24" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA24" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Cold Water Pipe</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Z24" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA24" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="AB24" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC24" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="60">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="F25" s="42" t="s">
+        <v>224</v>
+      </c>
+      <c r="G25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L25" s="33" t="str">
+        <f t="shared" si="16"/>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M25" s="33" t="str">
+        <f t="shared" si="17"/>
+        <v>Sistemas.Passivos</v>
+      </c>
+      <c r="N25" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="O25" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="P25" s="52" t="s">
         <v>217</v>
       </c>
-      <c r="C25" s="42" t="s">
-        <v>218</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>233</v>
-      </c>
-      <c r="F25" s="42" t="s">
-        <v>226</v>
-      </c>
-      <c r="G25" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L25" s="33" t="str">
-        <f t="shared" si="19"/>
-        <v>De.Incêndio</v>
-      </c>
-      <c r="M25" s="33" t="str">
-        <f t="shared" si="20"/>
-        <v>Sistemas.Passivos</v>
-      </c>
-      <c r="N25" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="O25" s="52" t="s">
-        <v>224</v>
-      </c>
-      <c r="P25" s="52" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q25" s="30" t="str">
+      <c r="Q25" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="R25" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="S25" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T25" s="30" t="str">
         <f t="shared" si="18"/>
-        <v>La puerta cortafuegos que se cierra impide el paso del fuego y el humo.</v>
-      </c>
-      <c r="R25" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S25" s="30" t="str">
-        <f t="shared" si="21"/>
         <v>De Incêndio</v>
       </c>
-      <c r="T25" s="30" t="str">
-        <f t="shared" ref="T25:T27" si="22">SUBSTITUTE(D25, ".", " ")</f>
+      <c r="U25" s="30" t="str">
+        <f t="shared" ref="U25:U27" si="19">SUBSTITUTE(D25, ".", " ")</f>
         <v>Sistemas Passivos</v>
       </c>
-      <c r="U25" s="30" t="str">
-        <f t="shared" ref="U25:U27" si="23">SUBSTITUTE(E25, ".", " ")</f>
+      <c r="V25" s="30" t="str">
+        <f t="shared" ref="V25:V27" si="20">SUBSTITUTE(E25, ".", " ")</f>
         <v>De Selagem</v>
       </c>
-      <c r="V25" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W25" s="59" t="str">
+      <c r="W25" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X25" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-25</v>
       </c>
-      <c r="X25" s="29" t="s">
-        <v>220</v>
-      </c>
       <c r="Y25" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z25" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA25" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Fire door that closed prevents the passage of fire and smoke.</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>218</v>
+      </c>
+      <c r="Z25" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA25" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB25" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC25" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="60">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E26" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G26" s="61" t="s">
         <v>9</v>
@@ -4775,172 +5062,180 @@
         <v>9</v>
       </c>
       <c r="L26" s="33" t="str">
+        <f t="shared" si="16"/>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M26" s="33" t="str">
+        <f t="shared" si="17"/>
+        <v>Sistemas.Passivos</v>
+      </c>
+      <c r="N26" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="O26" s="52" t="s">
+        <v>221</v>
+      </c>
+      <c r="P26" s="52" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q26" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="R26" s="30" t="s">
+        <v>320</v>
+      </c>
+      <c r="S26" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T26" s="30" t="str">
+        <f t="shared" si="18"/>
+        <v>De Incêndio</v>
+      </c>
+      <c r="U26" s="30" t="str">
         <f t="shared" si="19"/>
-        <v>De.Incêndio</v>
-      </c>
-      <c r="M26" s="33" t="str">
+        <v>Sistemas Passivos</v>
+      </c>
+      <c r="V26" s="30" t="str">
         <f t="shared" si="20"/>
-        <v>Sistemas.Passivos</v>
-      </c>
-      <c r="N26" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="O26" s="52" t="s">
-        <v>223</v>
-      </c>
-      <c r="P26" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q26" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Muros y tabiques que limitan la propagación de las llamas gracias a sus propiedades de resistencia al fuego, diseñados específicamente para esta función.</v>
-      </c>
-      <c r="R26" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S26" s="30" t="str">
-        <f t="shared" si="21"/>
-        <v>De Incêndio</v>
-      </c>
-      <c r="T26" s="30" t="str">
-        <f t="shared" si="22"/>
-        <v>Sistemas Passivos</v>
-      </c>
-      <c r="U26" s="30" t="str">
-        <f t="shared" si="23"/>
         <v>De Selagem</v>
       </c>
-      <c r="V26" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W26" s="59" t="str">
+      <c r="W26" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X26" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-26</v>
       </c>
-      <c r="X26" s="29" t="s">
-        <v>246</v>
-      </c>
       <c r="Y26" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z26" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA26" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Walls and partitions that limit the spread of flames thanks to their fire resistance properties, designed specifically for this function.</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <v>244</v>
+      </c>
+      <c r="Z26" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA26" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB26" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC26" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="60">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E27" s="42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F27" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="G27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" s="33" t="str">
+        <f t="shared" ref="L27:L29" si="21">CONCATENATE("", C27)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M27" s="33" t="str">
+        <f t="shared" ref="M27:M29" si="22">CONCATENATE("", D27)</f>
+        <v>Sistemas.Passivos</v>
+      </c>
+      <c r="N27" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="O27" s="52" t="s">
         <v>227</v>
       </c>
-      <c r="G27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L27" s="33" t="str">
-        <f t="shared" ref="L27:L29" si="24">CONCATENATE("", C27)</f>
-        <v>De.Incêndio</v>
-      </c>
-      <c r="M27" s="33" t="str">
-        <f t="shared" ref="M27:M29" si="25">CONCATENATE("", D27)</f>
-        <v>Sistemas.Passivos</v>
-      </c>
-      <c r="N27" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="O27" s="52" t="s">
+      <c r="P27" s="52" t="s">
         <v>229</v>
       </c>
-      <c r="P27" s="52" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q27" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>Pozos y pasadizos verticales diseñados con sellado intumescente, volcadores sin humo y barreras cortafuego en cada planta.</v>
+      <c r="Q27" s="30" t="s">
+        <v>335</v>
       </c>
       <c r="R27" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S27" s="30" t="str">
-        <f t="shared" ref="S27:S29" si="26">SUBSTITUTE(C27, ".", " ")</f>
+        <v>321</v>
+      </c>
+      <c r="S27" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T27" s="30" t="str">
+        <f t="shared" ref="T27:T29" si="23">SUBSTITUTE(C27, ".", " ")</f>
         <v>De Incêndio</v>
       </c>
-      <c r="T27" s="30" t="str">
-        <f t="shared" si="22"/>
+      <c r="U27" s="30" t="str">
+        <f t="shared" si="19"/>
         <v>Sistemas Passivos</v>
       </c>
-      <c r="U27" s="30" t="str">
-        <f t="shared" si="23"/>
+      <c r="V27" s="30" t="str">
+        <f t="shared" si="20"/>
         <v>De Selagem</v>
       </c>
-      <c r="V27" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W27" s="59" t="str">
+      <c r="W27" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X27" s="59" t="str">
         <f t="shared" si="4"/>
         <v>Key-INC-27</v>
       </c>
-      <c r="X27" s="29" t="s">
-        <v>247</v>
-      </c>
       <c r="Y27" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z27" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA27" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Shafts and vertical passages designed with intumescent sealing, smoke-free dumpers and fire barriers on each floor.</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>245</v>
+      </c>
+      <c r="Z27" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA27" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB27" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC27" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="60">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="F28" s="42" t="s">
         <v>234</v>
       </c>
-      <c r="E28" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="F28" s="42" t="s">
-        <v>236</v>
-      </c>
       <c r="G28" s="61" t="s">
         <v>9</v>
       </c>
@@ -4957,81 +5252,85 @@
         <v>9</v>
       </c>
       <c r="L28" s="33" t="str">
-        <f t="shared" ref="L28" si="27">CONCATENATE("", C28)</f>
+        <f t="shared" ref="L28" si="24">CONCATENATE("", C28)</f>
         <v>De.Incêndio</v>
       </c>
       <c r="M28" s="33" t="str">
-        <f t="shared" ref="M28" si="28">CONCATENATE("", D28)</f>
+        <f t="shared" ref="M28" si="25">CONCATENATE("", D28)</f>
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N28" s="52" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O28" s="52" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="P28" s="63" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q28" s="30" t="str">
-        <f t="shared" ref="Q28:Q30" si="29">_xlfn.TRANSLATE(P28,"pt","es")</f>
-        <v>El colgante de aspersores es una ducha automática instalada en el techo con el chorro de agua hacia abajo.</v>
+        <v>241</v>
+      </c>
+      <c r="Q28" s="30" t="s">
+        <v>336</v>
       </c>
       <c r="R28" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S28" s="30" t="str">
-        <f t="shared" ref="S28" si="30">SUBSTITUTE(C28, ".", " ")</f>
+        <v>322</v>
+      </c>
+      <c r="S28" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T28" s="30" t="str">
+        <f t="shared" ref="T28" si="26">SUBSTITUTE(C28, ".", " ")</f>
         <v>De Incêndio</v>
       </c>
-      <c r="T28" s="30" t="str">
-        <f t="shared" ref="T28:T30" si="31">SUBSTITUTE(D28, ".", " ")</f>
+      <c r="U28" s="30" t="str">
+        <f t="shared" ref="U28:U30" si="27">SUBSTITUTE(D28, ".", " ")</f>
         <v>Sistemas Ativos</v>
       </c>
-      <c r="U28" s="30" t="str">
-        <f t="shared" ref="U28:U30" si="32">SUBSTITUTE(E28, ".", " ")</f>
+      <c r="V28" s="30" t="str">
+        <f t="shared" ref="V28:V30" si="28">SUBSTITUTE(E28, ".", " ")</f>
         <v>De Combate</v>
       </c>
-      <c r="V28" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W28" s="59" t="str">
-        <f t="shared" ref="W28:W30" si="33">CONCATENATE("Key-INC-",A28)</f>
+      <c r="W28" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X28" s="59" t="str">
+        <f t="shared" ref="X28:X30" si="29">CONCATENATE("Key-INC-",A28)</f>
         <v>Key-INC-28</v>
       </c>
-      <c r="X28" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y28" s="29" t="s">
+      <c r="Y28" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z28" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA28" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Sprinkler Pendant is an automatic shower installed on the ceiling with the water jet down.</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Z28" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA28" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB28" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC28" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="60">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E29" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="F29" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="F29" s="42" t="s">
-        <v>237</v>
-      </c>
       <c r="G29" s="61" t="s">
         <v>9</v>
       </c>
@@ -5048,80 +5347,84 @@
         <v>9</v>
       </c>
       <c r="L29" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="21"/>
         <v>De.Incêndio</v>
       </c>
       <c r="M29" s="33" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N29" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="O29" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="P29" s="63" t="s">
         <v>242</v>
       </c>
-      <c r="O29" s="52" t="s">
-        <v>240</v>
-      </c>
-      <c r="P29" s="63" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q29" s="30" t="str">
-        <f t="shared" ref="Q29" si="34">_xlfn.TRANSLATE(P29,"pt","es")</f>
-        <v>El rociador vertical es una ducha automática instalada en tuberías expuestas bajo el techo con el chorro de agua hacia arriba.</v>
+      <c r="Q29" s="30" t="s">
+        <v>337</v>
       </c>
       <c r="R29" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S29" s="30" t="str">
-        <f t="shared" si="26"/>
+        <v>323</v>
+      </c>
+      <c r="S29" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T29" s="30" t="str">
+        <f t="shared" si="23"/>
         <v>De Incêndio</v>
       </c>
-      <c r="T29" s="30" t="str">
-        <f t="shared" ref="T29" si="35">SUBSTITUTE(D29, ".", " ")</f>
+      <c r="U29" s="30" t="str">
+        <f t="shared" ref="U29" si="30">SUBSTITUTE(D29, ".", " ")</f>
         <v>Sistemas Ativos</v>
       </c>
-      <c r="U29" s="30" t="str">
-        <f t="shared" ref="U29" si="36">SUBSTITUTE(E29, ".", " ")</f>
+      <c r="V29" s="30" t="str">
+        <f t="shared" ref="V29" si="31">SUBSTITUTE(E29, ".", " ")</f>
         <v>De Combate</v>
       </c>
-      <c r="V29" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W29" s="59" t="str">
-        <f t="shared" ref="W29" si="37">CONCATENATE("Key-INC-",A29)</f>
+      <c r="W29" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X29" s="59" t="str">
+        <f t="shared" ref="X29" si="32">CONCATENATE("Key-INC-",A29)</f>
         <v>Key-INC-29</v>
       </c>
-      <c r="X29" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y29" s="29" t="s">
+      <c r="Y29" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z29" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA29" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Upright Sprinkler is an automatic shower installed in exposed piping below the ceiling with the water jet up.</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Z29" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA29" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB29" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC29" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="60">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F30" s="42" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G30" s="61" t="s">
         <v>9</v>
@@ -5139,80 +5442,84 @@
         <v>9</v>
       </c>
       <c r="L30" s="33" t="str">
-        <f t="shared" ref="L30" si="38">CONCATENATE("", C30)</f>
+        <f t="shared" ref="L30" si="33">CONCATENATE("", C30)</f>
         <v>De.Incêndio</v>
       </c>
       <c r="M30" s="33" t="str">
-        <f t="shared" ref="M30" si="39">CONCATENATE("", D30)</f>
+        <f t="shared" ref="M30" si="34">CONCATENATE("", D30)</f>
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N30" s="52" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="O30" s="52" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P30" s="63" t="s">
-        <v>245</v>
-      </c>
-      <c r="Q30" s="30" t="str">
+        <v>243</v>
+      </c>
+      <c r="Q30" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="R30" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="S30" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T30" s="30" t="str">
+        <f t="shared" ref="T30" si="35">SUBSTITUTE(C30, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="U30" s="30" t="str">
+        <f t="shared" si="27"/>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="V30" s="30" t="str">
+        <f t="shared" si="28"/>
+        <v>De Combate</v>
+      </c>
+      <c r="W30" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X30" s="59" t="str">
         <f t="shared" si="29"/>
-        <v>El rociador lateral es una ducha automática instalada en las paredes, ideal para pasillos.</v>
-      </c>
-      <c r="R30" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S30" s="30" t="str">
-        <f t="shared" ref="S30" si="40">SUBSTITUTE(C30, ".", " ")</f>
-        <v>De Incêndio</v>
-      </c>
-      <c r="T30" s="30" t="str">
-        <f t="shared" si="31"/>
-        <v>Sistemas Ativos</v>
-      </c>
-      <c r="U30" s="30" t="str">
-        <f t="shared" si="32"/>
-        <v>De Combate</v>
-      </c>
-      <c r="V30" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W30" s="59" t="str">
-        <f t="shared" si="33"/>
         <v>Key-INC-30</v>
       </c>
-      <c r="X30" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y30" s="29" t="s">
+      <c r="Y30" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z30" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA30" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Side Sprinkler is an automatic shower installed on walls, ideal for corridors.</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Z30" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA30" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB30" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC30" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="60">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F31" s="42" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G31" s="61" t="s">
         <v>9</v>
@@ -5230,81 +5537,85 @@
         <v>9</v>
       </c>
       <c r="L31" s="33" t="str">
-        <f t="shared" ref="L31" si="41">CONCATENATE("", C31)</f>
+        <f t="shared" ref="L31" si="36">CONCATENATE("", C31)</f>
         <v>De.Incêndio</v>
       </c>
       <c r="M31" s="33" t="str">
-        <f t="shared" ref="M31" si="42">CONCATENATE("", D31)</f>
+        <f t="shared" ref="M31" si="37">CONCATENATE("", D31)</f>
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N31" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="O31" s="52" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="P31" s="63" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q31" s="30" t="str">
-        <f t="shared" ref="Q31" si="43">_xlfn.TRANSLATE(P31,"pt","es")</f>
-        <v>Detecta partículas muy pequeñas de humo en incendios de combustión rápida.</v>
+        <v>283</v>
+      </c>
+      <c r="Q31" s="30" t="s">
+        <v>339</v>
       </c>
       <c r="R31" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S31" s="30" t="str">
-        <f t="shared" ref="S31" si="44">SUBSTITUTE(C31, ".", " ")</f>
+        <v>325</v>
+      </c>
+      <c r="S31" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T31" s="30" t="str">
+        <f t="shared" ref="T31" si="38">SUBSTITUTE(C31, ".", " ")</f>
         <v>De Incêndio</v>
       </c>
-      <c r="T31" s="30" t="str">
-        <f t="shared" ref="T31" si="45">SUBSTITUTE(D31, ".", " ")</f>
+      <c r="U31" s="30" t="str">
+        <f t="shared" ref="U31" si="39">SUBSTITUTE(D31, ".", " ")</f>
         <v>Sistemas Ativos</v>
       </c>
-      <c r="U31" s="30" t="str">
-        <f t="shared" ref="U31" si="46">SUBSTITUTE(E31, ".", " ")</f>
+      <c r="V31" s="30" t="str">
+        <f t="shared" ref="V31" si="40">SUBSTITUTE(E31, ".", " ")</f>
         <v>De Detecção</v>
       </c>
-      <c r="V31" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W31" s="59" t="str">
-        <f t="shared" ref="W31" si="47">CONCATENATE("Key-INC-",A31)</f>
+      <c r="W31" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X31" s="59" t="str">
+        <f t="shared" ref="X31" si="41">CONCATENATE("Key-INC-",A31)</f>
         <v>Key-INC-31</v>
       </c>
-      <c r="X31" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y31" s="29" t="s">
+      <c r="Y31" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z31" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA31" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Detects very small particles of smoke in fast-burning fires.</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Z31" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA31" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB31" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC31" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="60">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E32" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="F32" s="42" t="s">
         <v>270</v>
       </c>
-      <c r="F32" s="42" t="s">
-        <v>272</v>
-      </c>
       <c r="G32" s="61" t="s">
         <v>9</v>
       </c>
@@ -5321,80 +5632,84 @@
         <v>9</v>
       </c>
       <c r="L32" s="33" t="str">
-        <f t="shared" ref="L32:L33" si="48">CONCATENATE("", C32)</f>
+        <f t="shared" ref="L32:L33" si="42">CONCATENATE("", C32)</f>
         <v>De.Incêndio</v>
       </c>
       <c r="M32" s="33" t="str">
-        <f t="shared" ref="M32:M33" si="49">CONCATENATE("", D32)</f>
+        <f t="shared" ref="M32:M33" si="43">CONCATENATE("", D32)</f>
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N32" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="O32" s="52" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="P32" s="63" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q32" s="30" t="str">
-        <f t="shared" ref="Q32:Q33" si="50">_xlfn.TRANSLATE(P32,"pt","es")</f>
-        <v>Detecta el humo dispersando la luz en una cámara interna. Más efectivo en incendios latentes (humo denso). Es el tipo más común en edificios residenciales y comerciales.</v>
+        <v>282</v>
+      </c>
+      <c r="Q32" s="30" t="s">
+        <v>340</v>
       </c>
       <c r="R32" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S32" s="30" t="str">
-        <f t="shared" ref="S32:S33" si="51">SUBSTITUTE(C32, ".", " ")</f>
+        <v>326</v>
+      </c>
+      <c r="S32" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T32" s="30" t="str">
+        <f t="shared" ref="T32:T33" si="44">SUBSTITUTE(C32, ".", " ")</f>
         <v>De Incêndio</v>
       </c>
-      <c r="T32" s="30" t="str">
-        <f t="shared" ref="T32:T33" si="52">SUBSTITUTE(D32, ".", " ")</f>
+      <c r="U32" s="30" t="str">
+        <f t="shared" ref="U32:U33" si="45">SUBSTITUTE(D32, ".", " ")</f>
         <v>Sistemas Ativos</v>
       </c>
-      <c r="U32" s="30" t="str">
-        <f t="shared" ref="U32:U33" si="53">SUBSTITUTE(E32, ".", " ")</f>
+      <c r="V32" s="30" t="str">
+        <f t="shared" ref="V32:V33" si="46">SUBSTITUTE(E32, ".", " ")</f>
         <v>De Detecção</v>
       </c>
-      <c r="V32" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W32" s="59" t="str">
-        <f t="shared" ref="W32:W33" si="54">CONCATENATE("Key-INC-",A32)</f>
+      <c r="W32" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X32" s="59" t="str">
+        <f t="shared" ref="X32:X33" si="47">CONCATENATE("Key-INC-",A32)</f>
         <v>Key-INC-32</v>
       </c>
-      <c r="X32" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y32" s="29" t="s">
+      <c r="Y32" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z32" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA32" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>It detects smoke by scattering light in an internal chamber. Most effective on smoldering fires (dense smoke). It is the most common type in residential and commercial buildings.</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Z32" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA32" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB32" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC32" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="60">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G33" s="61" t="s">
         <v>9</v>
@@ -5412,80 +5727,84 @@
         <v>9</v>
       </c>
       <c r="L33" s="33" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="42"/>
         <v>De.Incêndio</v>
       </c>
       <c r="M33" s="33" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="43"/>
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N33" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="O33" s="52" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="P33" s="63" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q33" s="30" t="str">
-        <f t="shared" si="50"/>
-        <v>Detecta el uso de una red de tuberías que succiona continuamente aire del entorno. Detecta partículas muy pequeñas, permitiendo una detección temprana. Ideal para centros de datos, museos, bibliotecas y entornos críticos.</v>
+        <v>281</v>
+      </c>
+      <c r="Q33" s="30" t="s">
+        <v>341</v>
       </c>
       <c r="R33" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S33" s="30" t="str">
-        <f t="shared" si="51"/>
+        <v>327</v>
+      </c>
+      <c r="S33" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T33" s="30" t="str">
+        <f t="shared" si="44"/>
         <v>De Incêndio</v>
       </c>
-      <c r="T33" s="30" t="str">
-        <f t="shared" si="52"/>
+      <c r="U33" s="30" t="str">
+        <f t="shared" si="45"/>
         <v>Sistemas Ativos</v>
       </c>
-      <c r="U33" s="30" t="str">
-        <f t="shared" si="53"/>
+      <c r="V33" s="30" t="str">
+        <f t="shared" si="46"/>
         <v>De Detecção</v>
       </c>
-      <c r="V33" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W33" s="59" t="str">
-        <f t="shared" si="54"/>
+      <c r="W33" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X33" s="59" t="str">
+        <f t="shared" si="47"/>
         <v>Key-INC-33</v>
       </c>
-      <c r="X33" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y33" s="29" t="s">
+      <c r="Y33" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z33" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA33" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>It detects using a network of pipes that continuously sucks in air from the environment. Detects very small particles, allowing early detection. Ideal for data centers, museums, libraries, and critical environments.</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Z33" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA33" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB33" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC33" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="60">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F34" s="42" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G34" s="61" t="s">
         <v>9</v>
@@ -5503,80 +5822,84 @@
         <v>9</v>
       </c>
       <c r="L34" s="33" t="str">
-        <f t="shared" ref="L34" si="55">CONCATENATE("", C34)</f>
+        <f t="shared" ref="L34" si="48">CONCATENATE("", C34)</f>
         <v>De.Incêndio</v>
       </c>
       <c r="M34" s="33" t="str">
-        <f t="shared" ref="M34" si="56">CONCATENATE("", D34)</f>
+        <f t="shared" ref="M34" si="49">CONCATENATE("", D34)</f>
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N34" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="O34" s="52" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P34" s="63" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q34" s="30" t="str">
-        <f t="shared" ref="Q34" si="57">_xlfn.TRANSLATE(P34,"pt","es")</f>
-        <v>Detecta gracias a un haz de luz (láser o infrarrojo) entre el emisor y el receptor.</v>
+        <v>280</v>
+      </c>
+      <c r="Q34" s="30" t="s">
+        <v>342</v>
       </c>
       <c r="R34" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S34" s="30" t="str">
-        <f t="shared" ref="S34" si="58">SUBSTITUTE(C34, ".", " ")</f>
+        <v>328</v>
+      </c>
+      <c r="S34" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T34" s="30" t="str">
+        <f t="shared" ref="T34" si="50">SUBSTITUTE(C34, ".", " ")</f>
         <v>De Incêndio</v>
       </c>
-      <c r="T34" s="30" t="str">
-        <f t="shared" ref="T34" si="59">SUBSTITUTE(D34, ".", " ")</f>
+      <c r="U34" s="30" t="str">
+        <f t="shared" ref="U34" si="51">SUBSTITUTE(D34, ".", " ")</f>
         <v>Sistemas Ativos</v>
       </c>
-      <c r="U34" s="30" t="str">
-        <f t="shared" ref="U34" si="60">SUBSTITUTE(E34, ".", " ")</f>
+      <c r="V34" s="30" t="str">
+        <f t="shared" ref="V34" si="52">SUBSTITUTE(E34, ".", " ")</f>
         <v>De Detecção</v>
       </c>
-      <c r="V34" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W34" s="59" t="str">
-        <f t="shared" ref="W34" si="61">CONCATENATE("Key-INC-",A34)</f>
+      <c r="W34" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X34" s="59" t="str">
+        <f t="shared" ref="X34" si="53">CONCATENATE("Key-INC-",A34)</f>
         <v>Key-INC-34</v>
       </c>
-      <c r="X34" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y34" s="29" t="s">
+      <c r="Y34" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z34" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA34" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>It detects thanks to a beam of light (laser or infrared) between emitter and receiver.</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Z34" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA34" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB34" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC34" s="30" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="60">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E35" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F35" s="42" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G35" s="61" t="s">
         <v>9</v>
@@ -5594,116 +5917,125 @@
         <v>9</v>
       </c>
       <c r="L35" s="33" t="str">
-        <f t="shared" ref="L35" si="62">CONCATENATE("", C35)</f>
+        <f t="shared" ref="L35" si="54">CONCATENATE("", C35)</f>
         <v>De.Incêndio</v>
       </c>
       <c r="M35" s="33" t="str">
-        <f t="shared" ref="M35" si="63">CONCATENATE("", D35)</f>
+        <f t="shared" ref="M35" si="55">CONCATENATE("", D35)</f>
         <v>Sistemas.Ativos</v>
       </c>
       <c r="N35" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="O35" s="52" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P35" s="63" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q35" s="30" t="str">
-        <f t="shared" ref="Q35" si="64">_xlfn.TRANSLATE(P35,"pt","es")</f>
-        <v>Detector que integra detección de humo y calor en el mismo dispositivo. Aumenta la fiabilidad, estando indicado para entornos industriales o con variaciones de temperatura.</v>
+        <v>279</v>
+      </c>
+      <c r="Q35" s="30" t="s">
+        <v>343</v>
       </c>
       <c r="R35" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="S35" s="30" t="str">
-        <f t="shared" ref="S35" si="65">SUBSTITUTE(C35, ".", " ")</f>
+        <v>329</v>
+      </c>
+      <c r="S35" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T35" s="30" t="str">
+        <f t="shared" ref="T35" si="56">SUBSTITUTE(C35, ".", " ")</f>
         <v>De Incêndio</v>
       </c>
-      <c r="T35" s="30" t="str">
-        <f t="shared" ref="T35" si="66">SUBSTITUTE(D35, ".", " ")</f>
+      <c r="U35" s="30" t="str">
+        <f t="shared" ref="U35" si="57">SUBSTITUTE(D35, ".", " ")</f>
         <v>Sistemas Ativos</v>
       </c>
-      <c r="U35" s="30" t="str">
-        <f t="shared" ref="U35" si="67">SUBSTITUTE(E35, ".", " ")</f>
+      <c r="V35" s="30" t="str">
+        <f t="shared" ref="V35" si="58">SUBSTITUTE(E35, ".", " ")</f>
         <v>De Detecção</v>
       </c>
-      <c r="V35" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="W35" s="59" t="str">
-        <f t="shared" ref="W35" si="68">CONCATENATE("Key-INC-",A35)</f>
+      <c r="W35" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X35" s="59" t="str">
+        <f t="shared" ref="X35" si="59">CONCATENATE("Key-INC-",A35)</f>
         <v>Key-INC-35</v>
       </c>
-      <c r="X35" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y35" s="29" t="s">
+      <c r="Y35" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z35" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA35" s="30" t="str">
-        <f t="shared" si="5"/>
-        <v>Detector that integrates smoke and heat detection in the same device. Increases reliability, being indicated for industrial environments or with temperature variations.</v>
+      <c r="Z35" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AA35" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB35" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC35" s="30" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA883">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC883">
     <sortCondition ref="F2:F883"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B35 AA2:AA35">
-    <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B35">
+    <cfRule type="cellIs" dxfId="25" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="22" priority="1514"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1516"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F2 F19:F1048576">
-    <cfRule type="duplicateValues" dxfId="21" priority="1536"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1538"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="20" priority="1558"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1560"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36:F1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1486"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="1507"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1488"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1509"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O16:O18 A1:D1 F1:O1 Q1:X1 Z1:AA1 E3:F15 L3:O15 Q3:Q18 X3:Y18 AB3:XFD18 F16:F18 L16:M18 E16:E19 N16:N19">
-    <cfRule type="cellIs" dxfId="15" priority="78" operator="equal">
+  <conditionalFormatting sqref="O16:O18 A1:D1 F1:O1 E3:F15 L3:O15 Q3:Q18 AD3:XFD18 F16:F18 L16:M18 E16:E19 N16:N19 Y3:Y18 Q1:Z1 AA3:AA18 AB1:AC1">
+    <cfRule type="cellIs" dxfId="17" priority="80" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O18">
-    <cfRule type="duplicateValues" dxfId="14" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O19:O27">
-    <cfRule type="duplicateValues" dxfId="13" priority="1565"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1567"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O28:O35">
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2">
-    <cfRule type="duplicateValues" dxfId="11" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S35">
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
+  <conditionalFormatting sqref="T2:T35">
+    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X19">
-    <cfRule type="cellIs" dxfId="9" priority="30" operator="equal">
+  <conditionalFormatting sqref="Y19">
+    <cfRule type="cellIs" dxfId="11" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X28:X35">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+  <conditionalFormatting sqref="R2:R35">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y28:Y35">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6113,10 +6445,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C2" s="53" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D2" s="50" t="s">
         <v>9</v>
@@ -6128,7 +6460,7 @@
         <v>77</v>
       </c>
       <c r="G2" s="23" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H2" s="49" t="s">
         <v>9</v>
@@ -6172,28 +6504,28 @@
         <v>3</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D3" s="50" t="s">
         <v>82</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G3" s="23" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H3" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J3" s="49" t="s">
         <v>9</v>
@@ -6211,7 +6543,7 @@
         <v>9</v>
       </c>
       <c r="O3" s="24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P3" s="49" t="s">
         <v>9</v>
@@ -6231,28 +6563,28 @@
         <v>4</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D4" s="50" t="s">
         <v>82</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="23" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H4" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J4" s="49" t="s">
         <v>9</v>
@@ -6270,7 +6602,7 @@
         <v>9</v>
       </c>
       <c r="O4" s="24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P4" s="49" t="s">
         <v>9</v>
@@ -6290,58 +6622,58 @@
         <v>5</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G5" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H5" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J5" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K5" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L5" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M5" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N5" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N5" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O5" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P5" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R5" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6349,58 +6681,58 @@
         <v>6</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H6" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J6" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L6" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M6" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N6" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N6" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O6" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P6" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R6" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S6" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6408,58 +6740,58 @@
         <v>7</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D7" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H7" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J7" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K7" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L7" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M7" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N7" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N7" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O7" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P7" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q7" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R7" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S7" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6467,58 +6799,58 @@
         <v>8</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F8" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H8" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J8" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K8" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L8" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M8" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N8" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N8" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O8" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P8" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q8" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R8" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S8" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6526,58 +6858,58 @@
         <v>9</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C9" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D9" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F9" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H9" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J9" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K9" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L9" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M9" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N9" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N9" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O9" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P9" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q9" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R9" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S9" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6585,58 +6917,58 @@
         <v>10</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C10" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D10" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F10" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H10" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J10" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K10" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L10" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M10" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N10" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O10" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P10" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q10" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R10" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S10" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6644,58 +6976,58 @@
         <v>11</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C11" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D11" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F11" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H11" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J11" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K11" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L11" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M11" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N11" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N11" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O11" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P11" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q11" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R11" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S11" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6703,58 +7035,58 @@
         <v>12</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D12" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F12" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H12" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J12" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L12" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M12" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N12" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N12" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O12" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P12" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R12" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S12" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6762,58 +7094,58 @@
         <v>13</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F13" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H13" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J13" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K13" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L13" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M13" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N13" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N13" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O13" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P13" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q13" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R13" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S13" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6821,58 +7153,58 @@
         <v>14</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D14" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F14" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H14" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J14" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L14" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M14" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N14" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N14" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O14" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P14" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q14" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R14" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S14" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6880,58 +7212,58 @@
         <v>15</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D15" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F15" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H15" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J15" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K15" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L15" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M15" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N15" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N15" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O15" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P15" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q15" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R15" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S15" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6939,58 +7271,58 @@
         <v>16</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D16" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F16" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H16" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J16" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L16" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M16" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N16" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N16" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O16" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P16" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q16" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R16" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S16" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -6998,58 +7330,58 @@
         <v>17</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D17" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H17" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J17" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K17" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L17" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M17" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N17" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N17" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O17" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P17" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q17" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R17" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S17" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7057,58 +7389,58 @@
         <v>18</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D18" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F18" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H18" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J18" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K18" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L18" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M18" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N18" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N18" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O18" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P18" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q18" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R18" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S18" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7116,58 +7448,58 @@
         <v>19</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D19" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F19" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H19" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J19" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L19" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M19" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N19" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N19" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O19" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P19" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q19" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R19" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S19" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7175,58 +7507,58 @@
         <v>20</v>
       </c>
       <c r="B20" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="34" t="s">
         <v>263</v>
-      </c>
-      <c r="C20" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="D20" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="34" t="s">
-        <v>265</v>
       </c>
       <c r="F20" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H20" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I20" s="24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J20" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K20" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L20" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M20" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="N20" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="N20" s="49" t="s">
-        <v>100</v>
-      </c>
       <c r="O20" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P20" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q20" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R20" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S20" s="24" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7234,58 +7566,58 @@
         <v>21</v>
       </c>
       <c r="B21" s="47" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E21" s="34" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F21" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H21" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J21" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K21" s="24" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="L21" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M21" s="24" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N21" s="49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O21" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P21" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q21" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R21" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S21" s="24" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7293,58 +7625,58 @@
         <v>22</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D22" s="50" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F22" s="22" t="s">
         <v>77</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H22" s="49" t="s">
         <v>77</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J22" s="49" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="L22" s="49" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="M22" s="24" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N22" s="49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O22" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="P22" s="49" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q22" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R22" s="49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S22" s="24" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/Versão5/SIS/Ontologia_Incendio.xlsx
+++ b/Versão5/SIS/Ontologia_Incendio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66DA67A-C43A-44D9-A329-2347F90F88D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BF4CB4-DB95-42C3-90E5-F4C7B6A0B644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="353">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1112,13 +1112,25 @@
     <t>Parâmetro Rvt</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Atributo IFC</t>
   </si>
   <si>
     <t>Classe IFC</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
   </si>
 </sst>
 </file>
@@ -1209,7 +1221,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1348,6 +1360,12 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1461,7 +1479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1650,11 +1668,129 @@
     <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="35">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1727,14 +1863,6 @@
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -1886,14 +2014,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2328,15 +2448,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" style="56" customWidth="1"/>
-    <col min="2" max="2" width="40.15234375" style="56" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="56"/>
+    <col min="1" max="1" width="8.7109375" style="56" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="56" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2347,7 +2467,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2358,7 +2478,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -2369,7 +2489,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2380,7 +2500,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2392,7 +2512,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2404,7 +2524,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2415,7 +2535,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2426,7 +2546,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2437,7 +2557,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2448,7 +2568,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2459,7 +2579,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2470,7 +2590,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2481,7 +2601,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2492,7 +2612,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2503,7 +2623,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2514,7 +2634,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -2525,19 +2645,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46253.810137615743</v>
+        <v>46260.362275925923</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2548,7 +2668,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2559,7 +2679,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2570,7 +2690,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -2581,7 +2701,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -2592,7 +2712,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>86</v>
       </c>
@@ -2612,38 +2732,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC35"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC36"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.3828125" style="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.921875" style="62" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.4609375" style="54" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.3828125" style="54" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.23046875" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.15234375" style="54" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="80.921875" style="54" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="86.15234375" style="54" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="80.4609375" style="54" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.15234375" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.4609375" style="54" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.07421875" style="54" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.53515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.07421875" style="54" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="59.53515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.765625" style="54" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="28.765625" style="55" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6" style="54" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3.84375" style="54" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="54"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" style="62" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10" style="54" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="111.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="118.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="110" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10" style="54" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="81.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" style="54" customWidth="1"/>
+    <col min="27" max="27" width="28.7109375" style="55" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.5703125" style="54" customWidth="1"/>
+    <col min="29" max="29" width="6.140625" style="54" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
         <v>91</v>
       </c>
@@ -2723,16 +2843,16 @@
         <v>345</v>
       </c>
       <c r="AA1" s="35" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AB1" s="35" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AC1" s="35" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="60">
         <v>2</v>
       </c>
@@ -2814,20 +2934,20 @@
       <c r="Y2" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="Z2" s="29" t="s">
-        <v>346</v>
+      <c r="Z2" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA2" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="AB2" s="29" t="s">
-        <v>346</v>
+      <c r="AB2" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="60">
         <v>3</v>
       </c>
@@ -2910,20 +3030,20 @@
       <c r="Y3" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z3" s="29" t="s">
-        <v>346</v>
+      <c r="Z3" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA3" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="AB3" s="29" t="s">
-        <v>346</v>
+      <c r="AB3" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC3" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="60">
         <v>4</v>
       </c>
@@ -3006,20 +3126,20 @@
       <c r="Y4" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z4" s="29" t="s">
-        <v>346</v>
+      <c r="Z4" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA4" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AB4" s="29" t="s">
-        <v>346</v>
+      <c r="AB4" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC4" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
         <v>5</v>
       </c>
@@ -3102,20 +3222,20 @@
       <c r="Y5" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z5" s="29" t="s">
-        <v>346</v>
+      <c r="Z5" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA5" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="AB5" s="29" t="s">
-        <v>346</v>
+      <c r="AB5" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC5" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="60">
         <v>6</v>
       </c>
@@ -3198,20 +3318,20 @@
       <c r="Y6" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z6" s="29" t="s">
-        <v>346</v>
+      <c r="Z6" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA6" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="AB6" s="29" t="s">
-        <v>346</v>
+      <c r="AB6" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC6" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="60">
         <v>7</v>
       </c>
@@ -3294,20 +3414,20 @@
       <c r="Y7" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z7" s="29" t="s">
-        <v>346</v>
+      <c r="Z7" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA7" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="AB7" s="29" t="s">
-        <v>346</v>
+      <c r="AB7" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC7" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="60">
         <v>8</v>
       </c>
@@ -3390,20 +3510,20 @@
       <c r="Y8" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z8" s="29" t="s">
-        <v>346</v>
+      <c r="Z8" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA8" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="AB8" s="29" t="s">
-        <v>346</v>
+      <c r="AB8" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC8" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="60">
         <v>9</v>
       </c>
@@ -3486,20 +3606,20 @@
       <c r="Y9" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z9" s="29" t="s">
-        <v>346</v>
+      <c r="Z9" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA9" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="AB9" s="29" t="s">
-        <v>346</v>
+      <c r="AB9" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC9" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="60">
         <v>10</v>
       </c>
@@ -3582,20 +3702,20 @@
       <c r="Y10" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z10" s="29" t="s">
-        <v>346</v>
+      <c r="Z10" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA10" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="AB10" s="29" t="s">
-        <v>346</v>
+      <c r="AB10" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC10" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="60">
         <v>11</v>
       </c>
@@ -3678,20 +3798,20 @@
       <c r="Y11" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z11" s="29" t="s">
-        <v>346</v>
+      <c r="Z11" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA11" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="AB11" s="29" t="s">
-        <v>346</v>
+      <c r="AB11" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC11" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="60">
         <v>12</v>
       </c>
@@ -3774,20 +3894,20 @@
       <c r="Y12" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z12" s="29" t="s">
-        <v>346</v>
+      <c r="Z12" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA12" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="AB12" s="29" t="s">
-        <v>346</v>
+      <c r="AB12" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC12" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="60">
         <v>13</v>
       </c>
@@ -3870,20 +3990,20 @@
       <c r="Y13" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z13" s="29" t="s">
-        <v>346</v>
+      <c r="Z13" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA13" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB13" s="29" t="s">
-        <v>346</v>
+      <c r="AB13" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC13" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="60">
         <v>14</v>
       </c>
@@ -3966,20 +4086,20 @@
       <c r="Y14" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="Z14" s="29" t="s">
-        <v>346</v>
+      <c r="Z14" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA14" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="AB14" s="29" t="s">
-        <v>346</v>
+      <c r="AB14" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC14" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="60">
         <v>15</v>
       </c>
@@ -4062,20 +4182,20 @@
       <c r="Y15" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z15" s="29" t="s">
-        <v>346</v>
+      <c r="Z15" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA15" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="AB15" s="29" t="s">
-        <v>346</v>
+      <c r="AB15" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC15" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="60">
         <v>16</v>
       </c>
@@ -4158,20 +4278,20 @@
       <c r="Y16" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z16" s="29" t="s">
-        <v>346</v>
+      <c r="Z16" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA16" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="AB16" s="29" t="s">
-        <v>346</v>
+      <c r="AB16" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC16" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="60">
         <v>17</v>
       </c>
@@ -4254,20 +4374,20 @@
       <c r="Y17" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="Z17" s="29" t="s">
-        <v>346</v>
+      <c r="Z17" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA17" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="AB17" s="29" t="s">
-        <v>346</v>
+      <c r="AB17" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC17" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="60">
         <v>18</v>
       </c>
@@ -4349,20 +4469,20 @@
       <c r="Y18" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="Z18" s="29" t="s">
-        <v>346</v>
+      <c r="Z18" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA18" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="AB18" s="29" t="s">
-        <v>346</v>
+      <c r="AB18" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC18" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="60">
         <v>19</v>
       </c>
@@ -4444,20 +4564,20 @@
       <c r="Y19" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="Z19" s="29" t="s">
-        <v>346</v>
+      <c r="Z19" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA19" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="AB19" s="29" t="s">
-        <v>346</v>
+      <c r="AB19" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC19" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="60">
         <v>20</v>
       </c>
@@ -4539,20 +4659,20 @@
       <c r="Y20" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="Z20" s="29" t="s">
-        <v>346</v>
+      <c r="Z20" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA20" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB20" s="29" t="s">
-        <v>346</v>
+      <c r="AB20" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC20" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="60">
         <v>21</v>
       </c>
@@ -4634,20 +4754,20 @@
       <c r="Y21" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="Z21" s="29" t="s">
-        <v>346</v>
+      <c r="Z21" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA21" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB21" s="29" t="s">
-        <v>346</v>
+      <c r="AB21" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC21" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="60">
         <v>22</v>
       </c>
@@ -4729,20 +4849,20 @@
       <c r="Y22" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="Z22" s="29" t="s">
-        <v>346</v>
+      <c r="Z22" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA22" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB22" s="29" t="s">
-        <v>346</v>
+      <c r="AB22" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC22" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="60">
         <v>23</v>
       </c>
@@ -4824,20 +4944,20 @@
       <c r="Y23" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="Z23" s="29" t="s">
-        <v>346</v>
+      <c r="Z23" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA23" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="AB23" s="29" t="s">
-        <v>346</v>
+      <c r="AB23" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC23" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="60">
         <v>24</v>
       </c>
@@ -4919,20 +5039,20 @@
       <c r="Y24" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="Z24" s="29" t="s">
-        <v>346</v>
+      <c r="Z24" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA24" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="AB24" s="29" t="s">
-        <v>346</v>
+      <c r="AB24" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC24" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="60">
         <v>25</v>
       </c>
@@ -5014,20 +5134,20 @@
       <c r="Y25" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="Z25" s="29" t="s">
-        <v>346</v>
+      <c r="Z25" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA25" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="AB25" s="29" t="s">
-        <v>346</v>
+      <c r="AB25" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC25" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="60">
         <v>26</v>
       </c>
@@ -5109,20 +5229,20 @@
       <c r="Y26" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="Z26" s="29" t="s">
-        <v>346</v>
+      <c r="Z26" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA26" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="AB26" s="29" t="s">
-        <v>346</v>
+      <c r="AB26" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC26" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="60">
         <v>27</v>
       </c>
@@ -5204,20 +5324,20 @@
       <c r="Y27" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="Z27" s="29" t="s">
-        <v>346</v>
+      <c r="Z27" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA27" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="AB27" s="29" t="s">
-        <v>346</v>
+      <c r="AB27" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC27" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="60">
         <v>28</v>
       </c>
@@ -5299,20 +5419,20 @@
       <c r="Y28" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z28" s="29" t="s">
-        <v>346</v>
+      <c r="Z28" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA28" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB28" s="29" t="s">
-        <v>346</v>
+      <c r="AB28" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC28" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="60">
         <v>29</v>
       </c>
@@ -5394,20 +5514,20 @@
       <c r="Y29" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z29" s="29" t="s">
-        <v>346</v>
+      <c r="Z29" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA29" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB29" s="29" t="s">
-        <v>346</v>
+      <c r="AB29" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC29" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="60">
         <v>30</v>
       </c>
@@ -5489,20 +5609,20 @@
       <c r="Y30" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z30" s="29" t="s">
-        <v>346</v>
+      <c r="Z30" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA30" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB30" s="29" t="s">
-        <v>346</v>
+      <c r="AB30" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC30" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="60">
         <v>31</v>
       </c>
@@ -5584,20 +5704,20 @@
       <c r="Y31" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z31" s="29" t="s">
-        <v>346</v>
+      <c r="Z31" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA31" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB31" s="29" t="s">
-        <v>346</v>
+      <c r="AB31" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC31" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="60">
         <v>32</v>
       </c>
@@ -5679,20 +5799,20 @@
       <c r="Y32" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z32" s="29" t="s">
-        <v>346</v>
+      <c r="Z32" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA32" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB32" s="29" t="s">
-        <v>346</v>
+      <c r="AB32" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC32" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="60">
         <v>33</v>
       </c>
@@ -5774,20 +5894,20 @@
       <c r="Y33" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z33" s="29" t="s">
-        <v>346</v>
+      <c r="Z33" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA33" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB33" s="29" t="s">
-        <v>346</v>
+      <c r="AB33" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC33" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="60">
         <v>34</v>
       </c>
@@ -5869,20 +5989,20 @@
       <c r="Y34" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z34" s="29" t="s">
-        <v>346</v>
+      <c r="Z34" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA34" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB34" s="29" t="s">
-        <v>346</v>
+      <c r="AB34" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC34" s="30" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="60">
         <v>35</v>
       </c>
@@ -5943,7 +6063,7 @@
         <v>9</v>
       </c>
       <c r="T35" s="30" t="str">
-        <f t="shared" ref="T35" si="56">SUBSTITUTE(C35, ".", " ")</f>
+        <f t="shared" ref="T35:V36" si="56">SUBSTITUTE(C35, ".", " ")</f>
         <v>De Incêndio</v>
       </c>
       <c r="U35" s="30" t="str">
@@ -5958,23 +6078,122 @@
         <v>220</v>
       </c>
       <c r="X35" s="59" t="str">
-        <f t="shared" ref="X35" si="59">CONCATENATE("Key-INC-",A35)</f>
+        <f t="shared" ref="X35:X36" si="59">CONCATENATE("Key-INC-",A35)</f>
         <v>Key-INC-35</v>
       </c>
       <c r="Y35" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z35" s="29" t="s">
-        <v>346</v>
+      <c r="Z35" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AA35" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB35" s="29" t="s">
-        <v>346</v>
+      <c r="AB35" s="65" t="s">
+        <v>9</v>
       </c>
       <c r="AC35" s="30" t="s">
         <v>203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="60">
+        <v>36</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C36" s="67" t="s">
+        <v>348</v>
+      </c>
+      <c r="D36" s="67" t="s">
+        <v>349</v>
+      </c>
+      <c r="E36" s="67" t="s">
+        <v>350</v>
+      </c>
+      <c r="F36" s="67" t="s">
+        <v>351</v>
+      </c>
+      <c r="G36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L36" s="33" t="str">
+        <f t="shared" ref="L36:O36" si="60">SUBSTITUTE(CONCATENATE("", C36), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M36" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N36" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="O36" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P36" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q36" s="64" t="str">
+        <f t="shared" ref="Q36" si="61">_xlfn.TRANSLATE(P36,"pt","es")</f>
+        <v>Aplicación Revit</v>
+      </c>
+      <c r="R36" s="64" t="str">
+        <f t="shared" ref="R36" si="62">_xlfn.TRANSLATE(P36,"pt","en")</f>
+        <v>Revit App</v>
+      </c>
+      <c r="S36" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T36" s="30" t="str">
+        <f t="shared" si="56"/>
+        <v>De API</v>
+      </c>
+      <c r="U36" s="30" t="str">
+        <f t="shared" si="56"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V36" s="63" t="str">
+        <f t="shared" si="56"/>
+        <v>Macros</v>
+      </c>
+      <c r="W36" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X36" s="59" t="str">
+        <f t="shared" si="59"/>
+        <v>Key-INC-36</v>
+      </c>
+      <c r="Y36" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z36" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA36" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB36" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC36" s="65" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -5982,62 +6201,82 @@
     <sortCondition ref="F2:F883"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B35">
-    <cfRule type="cellIs" dxfId="25" priority="8" operator="equal">
+  <conditionalFormatting sqref="A2:B35 A36">
+    <cfRule type="cellIs" dxfId="0" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="24" priority="1516"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="1526"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F2 F19:F1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="1538"/>
+  <conditionalFormatting sqref="F1:F2 F19:F35 F37:F1048576">
+    <cfRule type="duplicateValues" dxfId="33" priority="1548"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="22" priority="1560"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1570"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36:F1048576">
-    <cfRule type="duplicateValues" dxfId="21" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1488"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="1509"/>
+  <conditionalFormatting sqref="F37:F1048576">
+    <cfRule type="duplicateValues" dxfId="31" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1498"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1519"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O16:O18 A1:D1 F1:O1 E3:F15 L3:O15 Q3:Q18 AD3:XFD18 F16:F18 L16:M18 E16:E19 N16:N19 Y3:Y18 Q1:Z1 AA3:AA18 AB1:AC1">
-    <cfRule type="cellIs" dxfId="17" priority="80" operator="equal">
+  <conditionalFormatting sqref="O16:O18 A1:D1 F1:O1 Q1:Z1 AB1:AC1 E3:F15 L3:O15 Q3:Q18 AA3:AA18 AD3:XFD18 F16:F18 L16:M18 E16:E19 N16:N19">
+    <cfRule type="cellIs" dxfId="27" priority="90" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O18">
-    <cfRule type="duplicateValues" dxfId="16" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O19:O27">
-    <cfRule type="duplicateValues" dxfId="15" priority="1567"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O28:O35">
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2">
-    <cfRule type="duplicateValues" dxfId="13" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T35">
-    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
+  <conditionalFormatting sqref="R2:R35">
+    <cfRule type="cellIs" dxfId="22" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y19">
-    <cfRule type="cellIs" dxfId="11" priority="32" operator="equal">
+  <conditionalFormatting sqref="T2:T35">
+    <cfRule type="cellIs" dxfId="21" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R35">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+  <conditionalFormatting sqref="Y3:Y19">
+    <cfRule type="cellIs" dxfId="20" priority="42" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y28:Y35">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B36">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F36">
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q36">
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R36">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -6050,15 +6289,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -6123,7 +6362,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -6188,7 +6427,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -6255,7 +6494,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6271,15 +6510,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -6302,7 +6541,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -6331,22 +6570,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="5" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6358,30 +6597,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S22"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3828125" customWidth="1"/>
-    <col min="3" max="3" width="10.3828125" customWidth="1"/>
-    <col min="4" max="4" width="7.84375" customWidth="1"/>
-    <col min="5" max="5" width="7.53515625" customWidth="1"/>
-    <col min="6" max="6" width="5.15234375" customWidth="1"/>
-    <col min="7" max="7" width="56.15234375" customWidth="1"/>
-    <col min="8" max="8" width="5.15234375" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="56.140625" customWidth="1"/>
+    <col min="8" max="8" width="5.140625" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="6.84375" customWidth="1"/>
-    <col min="11" max="11" width="18.69140625" customWidth="1"/>
-    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.53515625" customWidth="1"/>
-    <col min="14" max="14" width="6.84375" customWidth="1"/>
-    <col min="15" max="15" width="33.53515625" customWidth="1"/>
-    <col min="16" max="16" width="4.69140625" customWidth="1"/>
-    <col min="17" max="17" width="42.84375" customWidth="1"/>
-    <col min="18" max="18" width="6.69140625" customWidth="1"/>
-    <col min="19" max="19" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5703125" customWidth="1"/>
+    <col min="14" max="14" width="6.85546875" customWidth="1"/>
+    <col min="15" max="15" width="33.5703125" customWidth="1"/>
+    <col min="16" max="16" width="4.7109375" customWidth="1"/>
+    <col min="17" max="17" width="42.85546875" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" customWidth="1"/>
+    <col min="19" max="19" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -6440,7 +6679,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -6499,7 +6738,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>3</v>
       </c>
@@ -6558,7 +6797,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>4</v>
       </c>
@@ -6617,7 +6856,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>5</v>
       </c>
@@ -6676,7 +6915,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>6</v>
       </c>
@@ -6735,7 +6974,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>7</v>
       </c>
@@ -6794,7 +7033,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>8</v>
       </c>
@@ -6853,7 +7092,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>9</v>
       </c>
@@ -6912,7 +7151,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>10</v>
       </c>
@@ -6971,7 +7210,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20">
         <v>11</v>
       </c>
@@ -7030,7 +7269,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>12</v>
       </c>
@@ -7089,7 +7328,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20">
         <v>13</v>
       </c>
@@ -7148,7 +7387,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <v>14</v>
       </c>
@@ -7207,7 +7446,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>15</v>
       </c>
@@ -7266,7 +7505,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>16</v>
       </c>
@@ -7325,7 +7564,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20">
         <v>17</v>
       </c>
@@ -7384,7 +7623,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
         <v>18</v>
       </c>
@@ -7443,7 +7682,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20">
         <v>19</v>
       </c>
@@ -7502,7 +7741,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20">
         <v>20</v>
       </c>
@@ -7561,7 +7800,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20">
         <v>21</v>
       </c>
@@ -7620,7 +7859,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20">
         <v>22</v>
       </c>
@@ -7682,7 +7921,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Versão5/SIS/Ontologia_Incendio.xlsx
+++ b/Versão5/SIS/Ontologia_Incendio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BF4CB4-DB95-42C3-90E5-F4C7B6A0B644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DA7961-5218-4C95-9168-EBE2FA5BE542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -1684,113 +1684,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="34">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1863,14 +1757,6 @@
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2014,6 +1900,112 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2448,15 +2440,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="56" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="56" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="56"/>
+    <col min="1" max="1" width="8.69140625" style="56" customWidth="1"/>
+    <col min="2" max="2" width="40.15234375" style="56" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2467,7 +2459,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2478,7 +2470,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -2489,7 +2481,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2500,7 +2492,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2512,7 +2504,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2524,7 +2516,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2535,7 +2527,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2546,7 +2538,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2557,7 +2549,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2568,7 +2560,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2579,7 +2571,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2590,7 +2582,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2601,7 +2593,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2612,7 +2604,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2623,7 +2615,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2634,7 +2626,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -2645,19 +2637,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46260.362275925923</v>
+        <v>46264.570475347224</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2668,7 +2660,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2679,7 +2671,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2690,7 +2682,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -2701,7 +2693,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -2712,7 +2704,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>86</v>
       </c>
@@ -2733,37 +2725,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC36"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="54" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.3828125" style="54" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="62" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.15234375" style="54" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" style="54" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="111.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="118.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="111.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="118.3828125" style="54" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="110" style="54" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="54" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="81.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" style="54" customWidth="1"/>
-    <col min="27" max="27" width="28.7109375" style="55" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.5703125" style="54" customWidth="1"/>
-    <col min="29" max="29" width="6.140625" style="54" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="54"/>
+    <col min="21" max="21" width="10.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="81.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.69140625" style="54" customWidth="1"/>
+    <col min="27" max="27" width="28.69140625" style="55" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.53515625" style="54" customWidth="1"/>
+    <col min="29" max="29" width="6.15234375" style="54" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
         <v>91</v>
       </c>
@@ -2852,7 +2844,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="60">
         <v>2</v>
       </c>
@@ -2947,7 +2939,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="60">
         <v>3</v>
       </c>
@@ -3043,7 +3035,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="60">
         <v>4</v>
       </c>
@@ -3139,7 +3131,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="60">
         <v>5</v>
       </c>
@@ -3235,7 +3227,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="60">
         <v>6</v>
       </c>
@@ -3331,7 +3323,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="60">
         <v>7</v>
       </c>
@@ -3427,7 +3419,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="60">
         <v>8</v>
       </c>
@@ -3523,7 +3515,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="60">
         <v>9</v>
       </c>
@@ -3619,7 +3611,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="60">
         <v>10</v>
       </c>
@@ -3715,7 +3707,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="60">
         <v>11</v>
       </c>
@@ -3811,7 +3803,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="60">
         <v>12</v>
       </c>
@@ -3907,7 +3899,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="60">
         <v>13</v>
       </c>
@@ -4003,7 +3995,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="60">
         <v>14</v>
       </c>
@@ -4099,7 +4091,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="60">
         <v>15</v>
       </c>
@@ -4195,7 +4187,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="60">
         <v>16</v>
       </c>
@@ -4291,7 +4283,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="60">
         <v>17</v>
       </c>
@@ -4387,7 +4379,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="60">
         <v>18</v>
       </c>
@@ -4482,7 +4474,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="60">
         <v>19</v>
       </c>
@@ -4577,7 +4569,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="60">
         <v>20</v>
       </c>
@@ -4672,7 +4664,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="60">
         <v>21</v>
       </c>
@@ -4767,7 +4759,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="60">
         <v>22</v>
       </c>
@@ -4862,7 +4854,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="60">
         <v>23</v>
       </c>
@@ -4957,7 +4949,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="60">
         <v>24</v>
       </c>
@@ -5052,7 +5044,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="60">
         <v>25</v>
       </c>
@@ -5147,7 +5139,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="60">
         <v>26</v>
       </c>
@@ -5242,7 +5234,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="60">
         <v>27</v>
       </c>
@@ -5337,7 +5329,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="60">
         <v>28</v>
       </c>
@@ -5432,7 +5424,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="60">
         <v>29</v>
       </c>
@@ -5527,7 +5519,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="60">
         <v>30</v>
       </c>
@@ -5622,7 +5614,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="60">
         <v>31</v>
       </c>
@@ -5717,7 +5709,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="60">
         <v>32</v>
       </c>
@@ -5812,7 +5804,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="60">
         <v>33</v>
       </c>
@@ -5907,7 +5899,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="60">
         <v>34</v>
       </c>
@@ -6002,7 +5994,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="60">
         <v>35</v>
       </c>
@@ -6097,7 +6089,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="36" spans="1:29" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:29" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="60">
         <v>36</v>
       </c>
@@ -6108,10 +6100,10 @@
         <v>348</v>
       </c>
       <c r="D36" s="67" t="s">
+        <v>350</v>
+      </c>
+      <c r="E36" s="67" t="s">
         <v>349</v>
-      </c>
-      <c r="E36" s="67" t="s">
-        <v>350</v>
       </c>
       <c r="F36" s="67" t="s">
         <v>351</v>
@@ -6137,11 +6129,11 @@
       </c>
       <c r="M36" s="33" t="str">
         <f t="shared" si="60"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N36" s="33" t="str">
         <f t="shared" si="60"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O36" s="33" t="str">
         <f t="shared" si="60"/>
@@ -6167,11 +6159,11 @@
       </c>
       <c r="U36" s="30" t="str">
         <f t="shared" si="56"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V36" s="63" t="str">
         <f t="shared" si="56"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W36" s="30" t="s">
         <v>220</v>
@@ -6201,82 +6193,77 @@
     <sortCondition ref="F2:F883"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B35 A36">
-    <cfRule type="cellIs" dxfId="0" priority="18" operator="equal">
+  <conditionalFormatting sqref="A2:B36">
+    <cfRule type="cellIs" dxfId="33" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="34" priority="1526"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1526"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F2 F19:F35 F37:F1048576">
-    <cfRule type="duplicateValues" dxfId="33" priority="1548"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1548"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="32" priority="1570"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1570"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F36">
+    <cfRule type="duplicateValues" dxfId="29" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F37:F1048576">
-    <cfRule type="duplicateValues" dxfId="31" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="285"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="1498"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="1519"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1498"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O16:O18 A1:D1 F1:O1 Q1:Z1 AB1:AC1 E3:F15 L3:O15 Q3:Q18 AA3:AA18 AD3:XFD18 F16:F18 L16:M18 E16:E19 N16:N19">
-    <cfRule type="cellIs" dxfId="27" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="90" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O18">
-    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O19:O27">
-    <cfRule type="duplicateValues" dxfId="25" priority="1577"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O28:O35">
-    <cfRule type="duplicateValues" dxfId="24" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2">
-    <cfRule type="duplicateValues" dxfId="23" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q36">
+    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R35">
-    <cfRule type="cellIs" dxfId="22" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R36">
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="T2:T35">
-    <cfRule type="cellIs" dxfId="21" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y3:Y19">
-    <cfRule type="cellIs" dxfId="20" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="42" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y28:Y35">
-    <cfRule type="cellIs" dxfId="19" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B36">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q36">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R36">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -6289,15 +6276,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -6362,7 +6349,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -6427,7 +6414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -6494,7 +6481,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6510,15 +6497,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -6541,7 +6528,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -6570,22 +6557,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="16" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6597,30 +6584,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S22"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" customWidth="1"/>
-    <col min="7" max="7" width="56.140625" customWidth="1"/>
-    <col min="8" max="8" width="5.140625" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" customWidth="1"/>
+    <col min="3" max="3" width="10.3828125" customWidth="1"/>
+    <col min="4" max="4" width="7.84375" customWidth="1"/>
+    <col min="5" max="5" width="7.53515625" customWidth="1"/>
+    <col min="6" max="6" width="5.15234375" customWidth="1"/>
+    <col min="7" max="7" width="56.15234375" customWidth="1"/>
+    <col min="8" max="8" width="5.15234375" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" customWidth="1"/>
-    <col min="15" max="15" width="33.5703125" customWidth="1"/>
-    <col min="16" max="16" width="4.7109375" customWidth="1"/>
-    <col min="17" max="17" width="42.85546875" customWidth="1"/>
-    <col min="18" max="18" width="6.7109375" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.84375" customWidth="1"/>
+    <col min="11" max="11" width="18.69140625" customWidth="1"/>
+    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.53515625" customWidth="1"/>
+    <col min="14" max="14" width="6.84375" customWidth="1"/>
+    <col min="15" max="15" width="33.53515625" customWidth="1"/>
+    <col min="16" max="16" width="4.69140625" customWidth="1"/>
+    <col min="17" max="17" width="42.84375" customWidth="1"/>
+    <col min="18" max="18" width="6.69140625" customWidth="1"/>
+    <col min="19" max="19" width="6.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -6679,7 +6666,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -6738,7 +6725,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>3</v>
       </c>
@@ -6797,7 +6784,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>4</v>
       </c>
@@ -6856,7 +6843,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>5</v>
       </c>
@@ -6915,7 +6902,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20">
         <v>6</v>
       </c>
@@ -6974,7 +6961,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20">
         <v>7</v>
       </c>
@@ -7033,7 +7020,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20">
         <v>8</v>
       </c>
@@ -7092,7 +7079,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20">
         <v>9</v>
       </c>
@@ -7151,7 +7138,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20">
         <v>10</v>
       </c>
@@ -7210,7 +7197,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20">
         <v>11</v>
       </c>
@@ -7269,7 +7256,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20">
         <v>12</v>
       </c>
@@ -7328,7 +7315,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="20">
         <v>13</v>
       </c>
@@ -7387,7 +7374,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="20">
         <v>14</v>
       </c>
@@ -7446,7 +7433,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20">
         <v>15</v>
       </c>
@@ -7505,7 +7492,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20">
         <v>16</v>
       </c>
@@ -7564,7 +7551,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="20">
         <v>17</v>
       </c>
@@ -7623,7 +7610,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20">
         <v>18</v>
       </c>
@@ -7682,7 +7669,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20">
         <v>19</v>
       </c>
@@ -7741,7 +7728,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="20">
         <v>20</v>
       </c>
@@ -7800,7 +7787,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="20">
         <v>21</v>
       </c>
@@ -7859,7 +7846,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="20">
         <v>22</v>
       </c>
@@ -7921,7 +7908,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Versão5/SIS/Ontologia_Incendio.xlsx
+++ b/Versão5/SIS/Ontologia_Incendio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DA7961-5218-4C95-9168-EBE2FA5BE542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243A7FDF-332C-4E7E-A37E-696CE058AFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="373">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1127,10 +1127,70 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -1479,7 +1539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1668,9 +1728,6 @@
     <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1684,7 +1741,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="27">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1785,6 +1842,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1840,84 +1905,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2440,15 +2427,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" style="56" customWidth="1"/>
-    <col min="2" max="2" width="40.15234375" style="56" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="56"/>
+    <col min="1" max="1" width="8.7109375" style="56" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="56" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2459,7 +2446,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2470,7 +2457,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -2481,7 +2468,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2492,7 +2479,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2504,7 +2491,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2516,7 +2503,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2527,7 +2514,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2538,7 +2525,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2549,7 +2536,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2560,7 +2547,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2571,7 +2558,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2582,7 +2569,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2593,7 +2580,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2604,7 +2591,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2615,7 +2602,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2626,7 +2613,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -2637,19 +2624,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46264.570475347224</v>
+        <v>46268.700811458337</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2660,7 +2647,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2671,7 +2658,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2682,7 +2669,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -2693,7 +2680,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -2704,7 +2691,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>86</v>
       </c>
@@ -2724,38 +2711,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC36"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD40"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="54" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="54" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.3828125" style="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="62" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.15234375" style="54" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="54" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" style="54" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.3828125" style="54" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.69140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.69140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="111.53515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="118.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="111.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="118.42578125" style="54" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="110" style="54" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="54" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.3828125" style="54" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.3828125" style="54" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.69140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.69140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="81.69140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.69140625" style="54" customWidth="1"/>
-    <col min="27" max="27" width="28.69140625" style="55" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.53515625" style="54" customWidth="1"/>
-    <col min="29" max="29" width="6.15234375" style="54" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="54"/>
+    <col min="21" max="21" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.85546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="81.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" style="54" customWidth="1"/>
+    <col min="27" max="27" width="28.7109375" style="55" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6" style="54" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.5703125" style="54" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="2.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
         <v>91</v>
       </c>
@@ -2843,8 +2831,11 @@
       <c r="AC1" s="35" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD1" s="35" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="60">
         <v>2</v>
       </c>
@@ -2926,20 +2917,23 @@
       <c r="Y2" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="Z2" s="65" t="s">
+      <c r="Z2" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA2" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="AB2" s="65" t="s">
+      <c r="AB2" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD2" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="60">
         <v>3</v>
       </c>
@@ -3022,20 +3016,23 @@
       <c r="Y3" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z3" s="65" t="s">
+      <c r="Z3" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="AB3" s="65" t="s">
+      <c r="AB3" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC3" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD3" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="60">
         <v>4</v>
       </c>
@@ -3118,20 +3115,23 @@
       <c r="Y4" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z4" s="65" t="s">
+      <c r="Z4" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AB4" s="65" t="s">
+      <c r="AB4" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD4" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="60">
         <v>5</v>
       </c>
@@ -3214,20 +3214,23 @@
       <c r="Y5" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z5" s="65" t="s">
+      <c r="Z5" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="AB5" s="65" t="s">
+      <c r="AB5" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD5" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="60">
         <v>6</v>
       </c>
@@ -3310,20 +3313,23 @@
       <c r="Y6" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z6" s="65" t="s">
+      <c r="Z6" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="AB6" s="65" t="s">
+      <c r="AB6" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC6" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD6" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="60">
         <v>7</v>
       </c>
@@ -3406,20 +3412,23 @@
       <c r="Y7" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z7" s="65" t="s">
+      <c r="Z7" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA7" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="AB7" s="65" t="s">
+      <c r="AB7" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC7" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD7" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="60">
         <v>8</v>
       </c>
@@ -3502,20 +3511,23 @@
       <c r="Y8" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z8" s="65" t="s">
+      <c r="Z8" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA8" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="AB8" s="65" t="s">
+      <c r="AB8" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD8" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="60">
         <v>9</v>
       </c>
@@ -3598,20 +3610,23 @@
       <c r="Y9" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z9" s="65" t="s">
+      <c r="Z9" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA9" s="29" t="s">
         <v>176</v>
       </c>
-      <c r="AB9" s="65" t="s">
+      <c r="AB9" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC9" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD9" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="60">
         <v>10</v>
       </c>
@@ -3694,20 +3709,23 @@
       <c r="Y10" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="Z10" s="65" t="s">
+      <c r="Z10" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA10" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="AB10" s="65" t="s">
+      <c r="AB10" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD10" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="60">
         <v>11</v>
       </c>
@@ -3790,20 +3808,23 @@
       <c r="Y11" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z11" s="65" t="s">
+      <c r="Z11" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="AB11" s="65" t="s">
+      <c r="AB11" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC11" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD11" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="60">
         <v>12</v>
       </c>
@@ -3886,20 +3907,23 @@
       <c r="Y12" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z12" s="65" t="s">
+      <c r="Z12" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="AB12" s="65" t="s">
+      <c r="AB12" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC12" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD12" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="60">
         <v>13</v>
       </c>
@@ -3982,20 +4006,23 @@
       <c r="Y13" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z13" s="65" t="s">
+      <c r="Z13" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="AB13" s="65" t="s">
+      <c r="AB13" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC13" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD13" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="60">
         <v>14</v>
       </c>
@@ -4078,20 +4105,23 @@
       <c r="Y14" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="Z14" s="65" t="s">
+      <c r="Z14" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="AB14" s="65" t="s">
+      <c r="AB14" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC14" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD14" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="60">
         <v>15</v>
       </c>
@@ -4174,20 +4204,23 @@
       <c r="Y15" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z15" s="65" t="s">
+      <c r="Z15" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="AB15" s="65" t="s">
+      <c r="AB15" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC15" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD15" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="60">
         <v>16</v>
       </c>
@@ -4270,20 +4303,23 @@
       <c r="Y16" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="Z16" s="65" t="s">
+      <c r="Z16" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="AB16" s="65" t="s">
+      <c r="AB16" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC16" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD16" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="60">
         <v>17</v>
       </c>
@@ -4366,20 +4402,23 @@
       <c r="Y17" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="Z17" s="65" t="s">
+      <c r="Z17" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="AB17" s="65" t="s">
+      <c r="AB17" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC17" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD17" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="60">
         <v>18</v>
       </c>
@@ -4461,20 +4500,23 @@
       <c r="Y18" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="Z18" s="65" t="s">
+      <c r="Z18" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="AB18" s="65" t="s">
+      <c r="AB18" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC18" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD18" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="60">
         <v>19</v>
       </c>
@@ -4556,20 +4598,23 @@
       <c r="Y19" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="Z19" s="65" t="s">
+      <c r="Z19" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="AB19" s="65" t="s">
+      <c r="AB19" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC19" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD19" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="60">
         <v>20</v>
       </c>
@@ -4651,20 +4696,23 @@
       <c r="Y20" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="Z20" s="65" t="s">
+      <c r="Z20" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA20" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB20" s="65" t="s">
+      <c r="AB20" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC20" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD20" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="60">
         <v>21</v>
       </c>
@@ -4746,20 +4794,23 @@
       <c r="Y21" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="Z21" s="65" t="s">
+      <c r="Z21" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA21" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB21" s="65" t="s">
+      <c r="AB21" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC21" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD21" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="60">
         <v>22</v>
       </c>
@@ -4841,20 +4892,23 @@
       <c r="Y22" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="Z22" s="65" t="s">
+      <c r="Z22" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA22" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="AB22" s="65" t="s">
+      <c r="AB22" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC22" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD22" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="60">
         <v>23</v>
       </c>
@@ -4936,20 +4990,23 @@
       <c r="Y23" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="Z23" s="65" t="s">
+      <c r="Z23" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA23" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="AB23" s="65" t="s">
+      <c r="AB23" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC23" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD23" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="60">
         <v>24</v>
       </c>
@@ -5031,20 +5088,23 @@
       <c r="Y24" s="29" t="s">
         <v>248</v>
       </c>
-      <c r="Z24" s="65" t="s">
+      <c r="Z24" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA24" s="29" t="s">
         <v>246</v>
       </c>
-      <c r="AB24" s="65" t="s">
+      <c r="AB24" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC24" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD24" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="60">
         <v>25</v>
       </c>
@@ -5126,20 +5186,23 @@
       <c r="Y25" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="Z25" s="65" t="s">
+      <c r="Z25" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA25" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="AB25" s="65" t="s">
+      <c r="AB25" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC25" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD25" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="60">
         <v>26</v>
       </c>
@@ -5221,20 +5284,23 @@
       <c r="Y26" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="Z26" s="65" t="s">
+      <c r="Z26" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA26" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="AB26" s="65" t="s">
+      <c r="AB26" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC26" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD26" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="60">
         <v>27</v>
       </c>
@@ -5316,20 +5382,23 @@
       <c r="Y27" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="Z27" s="65" t="s">
+      <c r="Z27" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA27" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="AB27" s="65" t="s">
+      <c r="AB27" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC27" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD27" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="60">
         <v>28</v>
       </c>
@@ -5411,20 +5480,23 @@
       <c r="Y28" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z28" s="65" t="s">
+      <c r="Z28" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA28" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB28" s="65" t="s">
+      <c r="AB28" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC28" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD28" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="60">
         <v>29</v>
       </c>
@@ -5506,20 +5578,23 @@
       <c r="Y29" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z29" s="65" t="s">
+      <c r="Z29" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA29" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB29" s="65" t="s">
+      <c r="AB29" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC29" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD29" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="60">
         <v>30</v>
       </c>
@@ -5601,20 +5676,23 @@
       <c r="Y30" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z30" s="65" t="s">
+      <c r="Z30" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA30" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB30" s="65" t="s">
+      <c r="AB30" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC30" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD30" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="60">
         <v>31</v>
       </c>
@@ -5696,20 +5774,23 @@
       <c r="Y31" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z31" s="65" t="s">
+      <c r="Z31" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA31" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB31" s="65" t="s">
+      <c r="AB31" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC31" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD31" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="60">
         <v>32</v>
       </c>
@@ -5791,20 +5872,23 @@
       <c r="Y32" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z32" s="65" t="s">
+      <c r="Z32" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA32" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB32" s="65" t="s">
+      <c r="AB32" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC32" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD32" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="60">
         <v>33</v>
       </c>
@@ -5886,20 +5970,23 @@
       <c r="Y33" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z33" s="65" t="s">
+      <c r="Z33" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA33" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB33" s="65" t="s">
+      <c r="AB33" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC33" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD33" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="60">
         <v>34</v>
       </c>
@@ -5981,20 +6068,23 @@
       <c r="Y34" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z34" s="65" t="s">
+      <c r="Z34" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA34" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB34" s="65" t="s">
+      <c r="AB34" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC34" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD34" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="60">
         <v>35</v>
       </c>
@@ -6055,7 +6145,7 @@
         <v>9</v>
       </c>
       <c r="T35" s="30" t="str">
-        <f t="shared" ref="T35:V36" si="56">SUBSTITUTE(C35, ".", " ")</f>
+        <f t="shared" ref="T35:V40" si="56">SUBSTITUTE(C35, ".", " ")</f>
         <v>De Incêndio</v>
       </c>
       <c r="U35" s="30" t="str">
@@ -6070,42 +6160,45 @@
         <v>220</v>
       </c>
       <c r="X35" s="59" t="str">
-        <f t="shared" ref="X35:X36" si="59">CONCATENATE("Key-INC-",A35)</f>
+        <f t="shared" ref="X35:X40" si="59">CONCATENATE("Key-INC-",A35)</f>
         <v>Key-INC-35</v>
       </c>
       <c r="Y35" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="Z35" s="65" t="s">
+      <c r="Z35" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA35" s="29" t="s">
         <v>247</v>
       </c>
-      <c r="AB35" s="65" t="s">
+      <c r="AB35" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC35" s="30" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="36" spans="1:29" s="66" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD35" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="60">
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C36" s="67" t="s">
+      <c r="C36" s="66" t="s">
         <v>348</v>
       </c>
-      <c r="D36" s="67" t="s">
+      <c r="D36" s="66" t="s">
         <v>350</v>
       </c>
-      <c r="E36" s="67" t="s">
+      <c r="E36" s="66" t="s">
         <v>349</v>
       </c>
-      <c r="F36" s="67" t="s">
+      <c r="F36" s="66" t="s">
         <v>351</v>
       </c>
       <c r="G36" s="61" t="s">
@@ -6124,7 +6217,7 @@
         <v>9</v>
       </c>
       <c r="L36" s="33" t="str">
-        <f t="shared" ref="L36:O36" si="60">SUBSTITUTE(CONCATENATE("", C36), ".", " ")</f>
+        <f t="shared" ref="L36:O40" si="60">SUBSTITUTE(CONCATENATE("", C36), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M36" s="33" t="str">
@@ -6137,18 +6230,16 @@
       </c>
       <c r="O36" s="33" t="str">
         <f t="shared" si="60"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P36" s="30" t="s">
         <v>352</v>
       </c>
-      <c r="Q36" s="64" t="str">
-        <f t="shared" ref="Q36" si="61">_xlfn.TRANSLATE(P36,"pt","es")</f>
-        <v>Aplicación Revit</v>
-      </c>
-      <c r="R36" s="64" t="str">
-        <f t="shared" ref="R36" si="62">_xlfn.TRANSLATE(P36,"pt","en")</f>
-        <v>Revit App</v>
+      <c r="Q36" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="R36" s="30" t="s">
+        <v>354</v>
       </c>
       <c r="S36" s="30" t="s">
         <v>9</v>
@@ -6172,19 +6263,422 @@
         <f t="shared" si="59"/>
         <v>Key-INC-36</v>
       </c>
-      <c r="Y36" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z36" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA36" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB36" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC36" s="65" t="s">
+      <c r="Y36" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z36" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA36" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB36" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC36" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD36" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="60">
+        <v>37</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C37" s="66" t="s">
+        <v>348</v>
+      </c>
+      <c r="D37" s="66" t="s">
+        <v>350</v>
+      </c>
+      <c r="E37" s="66" t="s">
+        <v>349</v>
+      </c>
+      <c r="F37" s="66" t="s">
+        <v>355</v>
+      </c>
+      <c r="G37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L37" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="M37" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="N37" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O37" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P37" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q37" s="30" t="s">
+        <v>357</v>
+      </c>
+      <c r="R37" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="S37" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T37" s="30" t="str">
+        <f t="shared" si="56"/>
+        <v>De API</v>
+      </c>
+      <c r="U37" s="30" t="str">
+        <f t="shared" si="56"/>
+        <v>Macros</v>
+      </c>
+      <c r="V37" s="63" t="str">
+        <f t="shared" si="56"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W37" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X37" s="59" t="str">
+        <f t="shared" si="59"/>
+        <v>Key-INC-37</v>
+      </c>
+      <c r="Y37" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z37" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA37" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB37" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC37" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD37" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="60">
+        <v>38</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C38" s="66" t="s">
+        <v>348</v>
+      </c>
+      <c r="D38" s="66" t="s">
+        <v>350</v>
+      </c>
+      <c r="E38" s="66" t="s">
+        <v>349</v>
+      </c>
+      <c r="F38" s="66" t="s">
+        <v>359</v>
+      </c>
+      <c r="G38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L38" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="M38" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="N38" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O38" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P38" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q38" s="30" t="s">
+        <v>361</v>
+      </c>
+      <c r="R38" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="S38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T38" s="30" t="str">
+        <f t="shared" si="56"/>
+        <v>De API</v>
+      </c>
+      <c r="U38" s="30" t="str">
+        <f t="shared" si="56"/>
+        <v>Macros</v>
+      </c>
+      <c r="V38" s="63" t="str">
+        <f t="shared" si="56"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W38" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X38" s="59" t="str">
+        <f t="shared" si="59"/>
+        <v>Key-INC-38</v>
+      </c>
+      <c r="Y38" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z38" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA38" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB38" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC38" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD38" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="60">
+        <v>39</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C39" s="66" t="s">
+        <v>348</v>
+      </c>
+      <c r="D39" s="66" t="s">
+        <v>350</v>
+      </c>
+      <c r="E39" s="66" t="s">
+        <v>349</v>
+      </c>
+      <c r="F39" s="66" t="s">
+        <v>363</v>
+      </c>
+      <c r="G39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L39" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="M39" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="N39" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O39" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P39" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q39" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="R39" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="S39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T39" s="30" t="str">
+        <f t="shared" si="56"/>
+        <v>De API</v>
+      </c>
+      <c r="U39" s="30" t="str">
+        <f t="shared" si="56"/>
+        <v>Macros</v>
+      </c>
+      <c r="V39" s="63" t="str">
+        <f t="shared" si="56"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W39" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X39" s="59" t="str">
+        <f t="shared" si="59"/>
+        <v>Key-INC-39</v>
+      </c>
+      <c r="Y39" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z39" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA39" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB39" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC39" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD39" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="60">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C40" s="66" t="s">
+        <v>348</v>
+      </c>
+      <c r="D40" s="66" t="s">
+        <v>350</v>
+      </c>
+      <c r="E40" s="66" t="s">
+        <v>367</v>
+      </c>
+      <c r="F40" s="66" t="s">
+        <v>368</v>
+      </c>
+      <c r="G40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L40" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>De API</v>
+      </c>
+      <c r="M40" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Macros</v>
+      </c>
+      <c r="N40" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O40" s="33" t="str">
+        <f t="shared" si="60"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P40" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q40" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="R40" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="S40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T40" s="30" t="str">
+        <f t="shared" si="56"/>
+        <v>De API</v>
+      </c>
+      <c r="U40" s="30" t="str">
+        <f t="shared" si="56"/>
+        <v>Macros</v>
+      </c>
+      <c r="V40" s="63" t="str">
+        <f t="shared" si="56"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W40" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X40" s="59" t="str">
+        <f t="shared" si="59"/>
+        <v>Key-INC-40</v>
+      </c>
+      <c r="Y40" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z40" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA40" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB40" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC40" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD40" s="64" t="s">
         <v>9</v>
       </c>
     </row>
@@ -6193,75 +6687,66 @@
     <sortCondition ref="F2:F883"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B36">
-    <cfRule type="cellIs" dxfId="33" priority="5" operator="equal">
+  <conditionalFormatting sqref="A2:B40">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E40:F40">
+    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="32" priority="1526"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1530"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F2 F19:F35 F37:F1048576">
-    <cfRule type="duplicateValues" dxfId="31" priority="1548"/>
+  <conditionalFormatting sqref="F1:F2 F19:F35 F41:F1048576">
+    <cfRule type="duplicateValues" dxfId="23" priority="1552"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="30" priority="1570"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1574"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36">
-    <cfRule type="duplicateValues" dxfId="29" priority="6"/>
+  <conditionalFormatting sqref="F36:F39">
+    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37:F1048576">
-    <cfRule type="duplicateValues" dxfId="28" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="285"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="1498"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="1519"/>
+  <conditionalFormatting sqref="F41:F1048576">
+    <cfRule type="duplicateValues" dxfId="20" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1502"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1523"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O16:O18 A1:D1 F1:O1 Q1:Z1 AB1:AC1 E3:F15 L3:O15 Q3:Q18 AA3:AA18 AD3:XFD18 F16:F18 L16:M18 E16:E19 N16:N19">
-    <cfRule type="cellIs" dxfId="24" priority="90" operator="equal">
+  <conditionalFormatting sqref="O16:O18 A1:D1 F1:O1 Q1:Z1 AB1:AD1 E3:F15 L3:O15 Q3:Q18 AA3:AA18 AE3:XFD18 F16:F18 L16:M18 E16:E19 N16:N19">
+    <cfRule type="cellIs" dxfId="16" priority="94" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O18">
-    <cfRule type="duplicateValues" dxfId="23" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O19:O27">
-    <cfRule type="duplicateValues" dxfId="22" priority="1577"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O28:O35">
-    <cfRule type="duplicateValues" dxfId="21" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2">
-    <cfRule type="duplicateValues" dxfId="20" priority="49"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q36">
-    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R35">
-    <cfRule type="cellIs" dxfId="15" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R36">
-    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="T2:T35">
-    <cfRule type="cellIs" dxfId="10" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="28" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y3:Y19">
-    <cfRule type="cellIs" dxfId="9" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="46" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y28:Y35">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6276,15 +6761,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -6349,7 +6834,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -6414,7 +6899,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -6497,15 +6982,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -6528,7 +7013,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -6584,30 +7069,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S22"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3828125" customWidth="1"/>
-    <col min="3" max="3" width="10.3828125" customWidth="1"/>
-    <col min="4" max="4" width="7.84375" customWidth="1"/>
-    <col min="5" max="5" width="7.53515625" customWidth="1"/>
-    <col min="6" max="6" width="5.15234375" customWidth="1"/>
-    <col min="7" max="7" width="56.15234375" customWidth="1"/>
-    <col min="8" max="8" width="5.15234375" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" customWidth="1"/>
+    <col min="7" max="7" width="56.140625" customWidth="1"/>
+    <col min="8" max="8" width="5.140625" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="6.84375" customWidth="1"/>
-    <col min="11" max="11" width="18.69140625" customWidth="1"/>
-    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.53515625" customWidth="1"/>
-    <col min="14" max="14" width="6.84375" customWidth="1"/>
-    <col min="15" max="15" width="33.53515625" customWidth="1"/>
-    <col min="16" max="16" width="4.69140625" customWidth="1"/>
-    <col min="17" max="17" width="42.84375" customWidth="1"/>
-    <col min="18" max="18" width="6.69140625" customWidth="1"/>
-    <col min="19" max="19" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.85546875" customWidth="1"/>
+    <col min="11" max="11" width="18.7109375" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5703125" customWidth="1"/>
+    <col min="14" max="14" width="6.85546875" customWidth="1"/>
+    <col min="15" max="15" width="33.5703125" customWidth="1"/>
+    <col min="16" max="16" width="4.7109375" customWidth="1"/>
+    <col min="17" max="17" width="42.85546875" customWidth="1"/>
+    <col min="18" max="18" width="6.7109375" customWidth="1"/>
+    <col min="19" max="19" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -6666,7 +7151,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -6725,7 +7210,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20">
         <v>3</v>
       </c>
@@ -6784,7 +7269,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>4</v>
       </c>
@@ -6843,7 +7328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20">
         <v>5</v>
       </c>
@@ -6902,7 +7387,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20">
         <v>6</v>
       </c>
@@ -6961,7 +7446,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20">
         <v>7</v>
       </c>
@@ -7020,7 +7505,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20">
         <v>8</v>
       </c>
@@ -7079,7 +7564,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="20">
         <v>9</v>
       </c>
@@ -7138,7 +7623,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>10</v>
       </c>
@@ -7197,7 +7682,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20">
         <v>11</v>
       </c>
@@ -7256,7 +7741,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>12</v>
       </c>
@@ -7315,7 +7800,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="20">
         <v>13</v>
       </c>
@@ -7374,7 +7859,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="20">
         <v>14</v>
       </c>
@@ -7433,7 +7918,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20">
         <v>15</v>
       </c>
@@ -7492,7 +7977,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="20">
         <v>16</v>
       </c>
@@ -7551,7 +8036,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="20">
         <v>17</v>
       </c>
@@ -7610,7 +8095,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="20">
         <v>18</v>
       </c>
@@ -7669,7 +8154,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="20">
         <v>19</v>
       </c>
@@ -7728,7 +8213,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="20">
         <v>20</v>
       </c>
@@ -7787,7 +8272,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="20">
         <v>21</v>
       </c>
@@ -7846,7 +8331,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="20">
         <v>22</v>
       </c>

--- a/Versão5/SIS/Ontologia_Incendio.xlsx
+++ b/Versão5/SIS/Ontologia_Incendio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243A7FDF-332C-4E7E-A37E-696CE058AFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FB1303-3B67-4A83-8513-CB1BD25AF0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="421">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1191,6 +1191,150 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>De.Materialidade</t>
+  </si>
+  <si>
+    <t>Materialidades</t>
+  </si>
+  <si>
+    <t>Materiais</t>
+  </si>
+  <si>
+    <t>Tubo.de.Aço</t>
+  </si>
+  <si>
+    <t>Tubo de aço para canalizações.</t>
+  </si>
+  <si>
+    <t>Tubería de acero para fontanería.</t>
+  </si>
+  <si>
+    <t>Steel pipe for plumbing.</t>
+  </si>
+  <si>
+    <t>Instalações</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_PipeMaterials ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial ]</t>
+  </si>
+  <si>
+    <t>[ 0M.20.20.01.01 ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.Aço.Costura</t>
+  </si>
+  <si>
+    <t>Tubo de aço com costura (especificações NBR 5580 ou NBR 5590).</t>
+  </si>
+  <si>
+    <t>Tubería de acero soldada (especificaciones NBR 5580 o NBR 5590).</t>
+  </si>
+  <si>
+    <t>Welded steel pipe (NBR 5580 or NBR 5590 specifications).</t>
+  </si>
+  <si>
+    <t>Tubo.de.Cobre</t>
+  </si>
+  <si>
+    <t>Tubo de cobre para redes de água quente ou gás.</t>
+  </si>
+  <si>
+    <t>Tubería de cobre para agua caliente o redes de gas.</t>
+  </si>
+  <si>
+    <t>Copper pipe for hot water or gas networks.</t>
+  </si>
+  <si>
+    <t>[ 0M.20.20.05 ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.FoFo</t>
+  </si>
+  <si>
+    <t>Tubo de Ferro Fundido para redes de agua e esgoto de saneamento básico.</t>
+  </si>
+  <si>
+    <t>Tubería de hierro fundido para redes de agua y alcantarillado de saneamiento básico.</t>
+  </si>
+  <si>
+    <t>Cast Iron Pipe for water and sewage networks of basic sanitation.</t>
+  </si>
+  <si>
+    <t>[ 0M.20.20.01.07.03 ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.Latão</t>
+  </si>
+  <si>
+    <t>Tubo de latão para redes de água.</t>
+  </si>
+  <si>
+    <t>Tubería de latón para redes de agua.</t>
+  </si>
+  <si>
+    <t>Brass pipe for water networks.</t>
+  </si>
+  <si>
+    <t>[ 0M.20.20.05.01 ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.PEAD</t>
+  </si>
+  <si>
+    <t>Tubo de termofusão PEAD (Polietileno de Alta Densidade).</t>
+  </si>
+  <si>
+    <t>Tubo de termofusión HDPE (Polietileno de Alta Densidad).</t>
+  </si>
+  <si>
+    <t>HDPE (High Density Polyethylene) thermofusion tube.</t>
+  </si>
+  <si>
+    <t>[ 0M.20.60.07.09 ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.PVC</t>
+  </si>
+  <si>
+    <t>Tubo de PVC (Policloreto de Vinila) para redes de agua e esgoto doméstica.</t>
+  </si>
+  <si>
+    <t>Tubería de PVC (cloruro de polivinilo) para redes domésticas de agua y alcantarillado.</t>
+  </si>
+  <si>
+    <t>PVC (Polyvinyl Chloride) pipe for domestic water and sewage networks.</t>
+  </si>
+  <si>
+    <t>[ 0M.20.60.07.16 ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.PVCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tubo de PVC Orientado (Policloreto de Vinila). Material mais resistente que PVC normal para redes de água e esgoto. </t>
+  </si>
+  <si>
+    <t>Tubería de PVC orientada (cloruro de polivinilo). Material más resistente que el PVC normal para redes de agua y alcantarillado.</t>
+  </si>
+  <si>
+    <t>Oriented PVC Pipe (Polyvinyl Chloride). Material more resistant than normal PVC for water and sewage networks.</t>
+  </si>
+  <si>
+    <t>Tubo.Multicamada</t>
+  </si>
+  <si>
+    <t>Tubo composto por uma camada interna de plástico (PEX), uma camada intermediária de alumínio contínuo (Al) e uma camada externa de plástico protetor. Tubo flexível conectado por crimpagem.</t>
+  </si>
+  <si>
+    <t>Tubo compuesto por una capa interior de plástico (PEX), una capa intermedia de aluminio continuo (Al) y una capa exterior de plástico protector. Tubo flexible conectado mediante crimping.</t>
+  </si>
+  <si>
+    <t>Tube composed of an inner layer of plastic (PEX), a middle layer of continuous aluminium (Al) and an outer layer of protective plastic. Flexible tube connected by crimping.</t>
   </si>
 </sst>
 </file>
@@ -1539,7 +1683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1737,11 +1881,14 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="42">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1895,6 +2042,156 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2427,15 +2724,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="56" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="56" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="56"/>
+    <col min="1" max="1" width="8.69140625" style="56" customWidth="1"/>
+    <col min="2" max="2" width="40.15234375" style="56" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="41" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>44</v>
       </c>
@@ -2446,7 +2743,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>46</v>
       </c>
@@ -2457,7 +2754,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>48</v>
       </c>
@@ -2468,7 +2765,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>49</v>
       </c>
@@ -2479,7 +2776,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>50</v>
       </c>
@@ -2491,7 +2788,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>51</v>
       </c>
@@ -2503,7 +2800,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -2514,7 +2811,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="37" t="s">
         <v>54</v>
       </c>
@@ -2525,7 +2822,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>55</v>
       </c>
@@ -2536,7 +2833,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>57</v>
       </c>
@@ -2547,7 +2844,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>59</v>
       </c>
@@ -2558,7 +2855,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>60</v>
       </c>
@@ -2569,7 +2866,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
@@ -2580,7 +2877,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>62</v>
       </c>
@@ -2591,7 +2888,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>63</v>
       </c>
@@ -2602,7 +2899,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>64</v>
       </c>
@@ -2613,7 +2910,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -2624,19 +2921,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="15">
         <f ca="1">NOW()</f>
-        <v>46268.700811458337</v>
+        <v>46270.887386805553</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
@@ -2647,7 +2944,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
@@ -2658,7 +2955,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>70</v>
       </c>
@@ -2669,7 +2966,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>71</v>
       </c>
@@ -2680,7 +2977,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>72</v>
       </c>
@@ -2691,7 +2988,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="38" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>86</v>
       </c>
@@ -2711,39 +3008,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AD40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AD49"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="54" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.3828125" style="54" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="62" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.15234375" style="54" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" style="54" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="111.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="118.42578125" style="54" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="111.53515625" style="54" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="118.3828125" style="54" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="110" style="54" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="54" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.42578125" style="54" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.85546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="81.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" style="54" customWidth="1"/>
-    <col min="27" max="27" width="28.7109375" style="55" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.3828125" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="81.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.69140625" style="54" customWidth="1"/>
+    <col min="27" max="27" width="23.23046875" style="55" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="54" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.5703125" style="54" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="2.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="54"/>
+    <col min="29" max="29" width="8.84375" style="54" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="2.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.15234375" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="43" t="s">
         <v>91</v>
       </c>
@@ -2835,24 +3132,24 @@
         <v>372</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="60">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C2" s="42" t="s">
-        <v>292</v>
+      <c r="C2" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>113</v>
+        <v>374</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F2" s="57" t="s">
+        <v>376</v>
       </c>
       <c r="G2" s="61" t="s">
         <v>9</v>
@@ -2870,87 +3167,89 @@
         <v>9</v>
       </c>
       <c r="L2" s="33" t="str">
-        <f t="shared" ref="L2" si="0">CONCATENATE("", C2)</f>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" ref="L2:O10" si="0">SUBSTITUTE(CONCATENATE("", C2), ".", " ")</f>
+        <v>De Materialidade</v>
       </c>
       <c r="M2" s="33" t="str">
-        <f t="shared" ref="M2" si="1">CONCATENATE("", D2)</f>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N2" s="33" t="s">
-        <v>199</v>
-      </c>
-      <c r="O2" s="30" t="s">
-        <v>198</v>
-      </c>
-      <c r="P2" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q2" s="52" t="s">
-        <v>205</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N2" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O2" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Tubo de Aço</v>
+      </c>
+      <c r="P2" s="67" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q2" s="30" t="s">
+        <v>378</v>
       </c>
       <c r="R2" s="30" t="s">
-        <v>297</v>
+        <v>379</v>
       </c>
       <c r="S2" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T2" s="30" t="str">
-        <f t="shared" ref="T2:V18" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Sistemas Prediais</v>
+        <f t="shared" ref="T2:V10" si="1">SUBSTITUTE(C2, ".", " ")</f>
+        <v>De Materialidade</v>
       </c>
       <c r="U2" s="30" t="str">
-        <f t="shared" ref="U2:V16" si="3">SUBSTITUTE(D2, ".", " ")</f>
-        <v>Sistema Incêndio</v>
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
       </c>
       <c r="V2" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema Combate</v>
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
       </c>
       <c r="W2" s="30" t="s">
-        <v>220</v>
+        <v>380</v>
       </c>
       <c r="X2" s="59" t="str">
-        <f t="shared" ref="X2:X27" si="4">CONCATENATE("Key-INC-",A2)</f>
+        <f t="shared" ref="X2:X49" si="2">CONCATENATE("Key-INC-",A2)</f>
         <v>Key-INC-2</v>
       </c>
-      <c r="Y2" s="29" t="s">
-        <v>105</v>
+      <c r="Y2" s="30" t="s">
+        <v>381</v>
       </c>
       <c r="Z2" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="29" t="s">
-        <v>107</v>
+      <c r="AA2" s="30" t="s">
+        <v>382</v>
       </c>
       <c r="AB2" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="30" t="s">
-        <v>203</v>
+        <v>383</v>
       </c>
       <c r="AD2" s="64" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="60">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C3" s="42" t="s">
-        <v>292</v>
+      <c r="C3" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>113</v>
+        <v>374</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>206</v>
+        <v>375</v>
       </c>
       <c r="F3" s="57" t="s">
-        <v>119</v>
+        <v>384</v>
       </c>
       <c r="G3" s="61" t="s">
         <v>9</v>
@@ -2968,88 +3267,89 @@
         <v>9</v>
       </c>
       <c r="L3" s="33" t="str">
-        <f t="shared" ref="L3:M19" si="5">CONCATENATE("", C3)</f>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M3" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N3" s="33" t="s">
-        <v>200</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N3" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
       </c>
       <c r="O3" s="33" t="str">
-        <f t="shared" ref="O3:O17" si="6">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F3),"."," ")," De "," de "))</f>
-        <v>Alarme</v>
-      </c>
-      <c r="P3" s="30" t="s">
-        <v>120</v>
+        <f t="shared" si="0"/>
+        <v>Tubo de Aço Costura</v>
+      </c>
+      <c r="P3" s="67" t="s">
+        <v>385</v>
       </c>
       <c r="Q3" s="30" t="s">
-        <v>121</v>
+        <v>386</v>
       </c>
       <c r="R3" s="30" t="s">
-        <v>298</v>
+        <v>387</v>
       </c>
       <c r="S3" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T3" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U3" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V3" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W3" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="X3" s="59" t="str">
         <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U3" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema Incêndio</v>
-      </c>
-      <c r="V3" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="W3" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="X3" s="59" t="str">
-        <f t="shared" si="4"/>
         <v>Key-INC-3</v>
       </c>
       <c r="Y3" s="30" t="s">
-        <v>164</v>
+        <v>381</v>
       </c>
       <c r="Z3" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="AA3" s="29" t="s">
-        <v>170</v>
+      <c r="AA3" s="30" t="s">
+        <v>382</v>
       </c>
       <c r="AB3" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC3" s="30" t="s">
-        <v>203</v>
+        <v>383</v>
       </c>
       <c r="AD3" s="64" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="60">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C4" s="42" t="s">
-        <v>292</v>
+      <c r="C4" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>113</v>
+        <v>374</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>206</v>
+        <v>375</v>
       </c>
       <c r="F4" s="57" t="s">
-        <v>122</v>
+        <v>388</v>
       </c>
       <c r="G4" s="61" t="s">
         <v>9</v>
@@ -3067,88 +3367,89 @@
         <v>9</v>
       </c>
       <c r="L4" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M4" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N4" s="33" t="s">
-        <v>200</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N4" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
       </c>
       <c r="O4" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Alarme Campainha</v>
-      </c>
-      <c r="P4" s="30" t="s">
-        <v>123</v>
+        <f t="shared" si="0"/>
+        <v>Tubo de Cobre</v>
+      </c>
+      <c r="P4" s="67" t="s">
+        <v>389</v>
       </c>
       <c r="Q4" s="30" t="s">
-        <v>124</v>
+        <v>390</v>
       </c>
       <c r="R4" s="30" t="s">
-        <v>299</v>
+        <v>391</v>
       </c>
       <c r="S4" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T4" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U4" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V4" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W4" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="X4" s="59" t="str">
         <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U4" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema Incêndio</v>
-      </c>
-      <c r="V4" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="W4" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="X4" s="59" t="str">
-        <f t="shared" si="4"/>
         <v>Key-INC-4</v>
       </c>
       <c r="Y4" s="30" t="s">
-        <v>164</v>
+        <v>381</v>
       </c>
       <c r="Z4" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="AA4" s="29" t="s">
-        <v>171</v>
+      <c r="AA4" s="30" t="s">
+        <v>382</v>
       </c>
       <c r="AB4" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="30" t="s">
-        <v>203</v>
+        <v>392</v>
       </c>
       <c r="AD4" s="64" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="60">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C5" s="42" t="s">
-        <v>292</v>
+      <c r="C5" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>113</v>
+        <v>374</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>206</v>
+        <v>375</v>
       </c>
       <c r="F5" s="57" t="s">
-        <v>125</v>
+        <v>393</v>
       </c>
       <c r="G5" s="61" t="s">
         <v>9</v>
@@ -3166,88 +3467,89 @@
         <v>9</v>
       </c>
       <c r="L5" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M5" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N5" s="33" t="s">
-        <v>200</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N5" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
       </c>
       <c r="O5" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Alarme Campainha Caixa</v>
-      </c>
-      <c r="P5" s="30" t="s">
-        <v>126</v>
+        <f t="shared" si="0"/>
+        <v>Tubo de FoFo</v>
+      </c>
+      <c r="P5" s="67" t="s">
+        <v>394</v>
       </c>
       <c r="Q5" s="30" t="s">
-        <v>127</v>
+        <v>395</v>
       </c>
       <c r="R5" s="30" t="s">
-        <v>300</v>
+        <v>396</v>
       </c>
       <c r="S5" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T5" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U5" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V5" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W5" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="X5" s="59" t="str">
         <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U5" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema Incêndio</v>
-      </c>
-      <c r="V5" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="W5" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="X5" s="59" t="str">
-        <f t="shared" si="4"/>
         <v>Key-INC-5</v>
       </c>
       <c r="Y5" s="30" t="s">
-        <v>164</v>
+        <v>381</v>
       </c>
       <c r="Z5" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="AA5" s="29" t="s">
-        <v>172</v>
+      <c r="AA5" s="30" t="s">
+        <v>382</v>
       </c>
       <c r="AB5" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="30" t="s">
-        <v>203</v>
+        <v>397</v>
       </c>
       <c r="AD5" s="64" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="60">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C6" s="42" t="s">
-        <v>292</v>
+      <c r="C6" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>113</v>
+        <v>374</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>206</v>
+        <v>375</v>
       </c>
       <c r="F6" s="57" t="s">
-        <v>128</v>
+        <v>398</v>
       </c>
       <c r="G6" s="61" t="s">
         <v>9</v>
@@ -3265,88 +3567,89 @@
         <v>9</v>
       </c>
       <c r="L6" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M6" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N6" s="33" t="s">
-        <v>200</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N6" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
       </c>
       <c r="O6" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Alarme Lumínico</v>
-      </c>
-      <c r="P6" s="30" t="s">
-        <v>129</v>
+        <f t="shared" si="0"/>
+        <v>Tubo de Latão</v>
+      </c>
+      <c r="P6" s="67" t="s">
+        <v>399</v>
       </c>
       <c r="Q6" s="30" t="s">
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="R6" s="30" t="s">
-        <v>301</v>
+        <v>401</v>
       </c>
       <c r="S6" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T6" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U6" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V6" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W6" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="X6" s="59" t="str">
         <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U6" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema Incêndio</v>
-      </c>
-      <c r="V6" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="W6" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="X6" s="59" t="str">
-        <f t="shared" si="4"/>
         <v>Key-INC-6</v>
       </c>
       <c r="Y6" s="30" t="s">
-        <v>164</v>
+        <v>381</v>
       </c>
       <c r="Z6" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="AA6" s="29" t="s">
-        <v>173</v>
+      <c r="AA6" s="30" t="s">
+        <v>382</v>
       </c>
       <c r="AB6" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC6" s="30" t="s">
-        <v>203</v>
+        <v>402</v>
       </c>
       <c r="AD6" s="64" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="60">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C7" s="42" t="s">
-        <v>292</v>
+      <c r="C7" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>113</v>
+        <v>374</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>206</v>
+        <v>375</v>
       </c>
       <c r="F7" s="57" t="s">
-        <v>131</v>
+        <v>403</v>
       </c>
       <c r="G7" s="61" t="s">
         <v>9</v>
@@ -3364,88 +3667,89 @@
         <v>9</v>
       </c>
       <c r="L7" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M7" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N7" s="33" t="s">
-        <v>200</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N7" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
       </c>
       <c r="O7" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Alarme Caixa Manual</v>
-      </c>
-      <c r="P7" s="30" t="s">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>Tubo de PEAD</v>
+      </c>
+      <c r="P7" s="67" t="s">
+        <v>404</v>
       </c>
       <c r="Q7" s="30" t="s">
-        <v>133</v>
+        <v>405</v>
       </c>
       <c r="R7" s="30" t="s">
-        <v>302</v>
+        <v>406</v>
       </c>
       <c r="S7" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T7" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U7" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V7" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W7" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="X7" s="59" t="str">
         <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U7" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema Incêndio</v>
-      </c>
-      <c r="V7" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="W7" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="X7" s="59" t="str">
-        <f t="shared" si="4"/>
         <v>Key-INC-7</v>
       </c>
       <c r="Y7" s="30" t="s">
-        <v>164</v>
+        <v>381</v>
       </c>
       <c r="Z7" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="AA7" s="29" t="s">
-        <v>174</v>
+      <c r="AA7" s="30" t="s">
+        <v>382</v>
       </c>
       <c r="AB7" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC7" s="30" t="s">
-        <v>203</v>
+        <v>407</v>
       </c>
       <c r="AD7" s="64" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="60">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C8" s="42" t="s">
-        <v>292</v>
+      <c r="C8" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>113</v>
+        <v>374</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>206</v>
+        <v>375</v>
       </c>
       <c r="F8" s="57" t="s">
-        <v>134</v>
+        <v>408</v>
       </c>
       <c r="G8" s="61" t="s">
         <v>9</v>
@@ -3463,88 +3767,89 @@
         <v>9</v>
       </c>
       <c r="L8" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M8" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N8" s="33" t="s">
-        <v>200</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N8" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
       </c>
       <c r="O8" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Alarme Detonador</v>
-      </c>
-      <c r="P8" s="30" t="s">
-        <v>135</v>
+        <f t="shared" si="0"/>
+        <v>Tubo de PVC</v>
+      </c>
+      <c r="P8" s="67" t="s">
+        <v>409</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>136</v>
+        <v>410</v>
       </c>
       <c r="R8" s="30" t="s">
-        <v>303</v>
+        <v>411</v>
       </c>
       <c r="S8" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T8" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U8" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V8" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W8" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="X8" s="59" t="str">
         <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U8" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema Incêndio</v>
-      </c>
-      <c r="V8" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="W8" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="X8" s="59" t="str">
-        <f t="shared" si="4"/>
         <v>Key-INC-8</v>
       </c>
       <c r="Y8" s="30" t="s">
-        <v>164</v>
+        <v>381</v>
       </c>
       <c r="Z8" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="AA8" s="29" t="s">
-        <v>175</v>
+      <c r="AA8" s="30" t="s">
+        <v>382</v>
       </c>
       <c r="AB8" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="30" t="s">
-        <v>203</v>
+        <v>412</v>
       </c>
       <c r="AD8" s="64" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="60">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C9" s="42" t="s">
-        <v>292</v>
+      <c r="C9" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>113</v>
+        <v>374</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>206</v>
+        <v>375</v>
       </c>
       <c r="F9" s="57" t="s">
-        <v>137</v>
+        <v>413</v>
       </c>
       <c r="G9" s="61" t="s">
         <v>9</v>
@@ -3562,88 +3867,89 @@
         <v>9</v>
       </c>
       <c r="L9" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M9" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N9" s="33" t="s">
-        <v>200</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N9" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
       </c>
       <c r="O9" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Alarme Sirene</v>
-      </c>
-      <c r="P9" s="30" t="s">
-        <v>138</v>
+        <f t="shared" si="0"/>
+        <v>Tubo de PVCO</v>
+      </c>
+      <c r="P9" s="67" t="s">
+        <v>414</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>139</v>
+        <v>415</v>
       </c>
       <c r="R9" s="30" t="s">
-        <v>304</v>
+        <v>416</v>
       </c>
       <c r="S9" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T9" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U9" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V9" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W9" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="X9" s="59" t="str">
         <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U9" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema Incêndio</v>
-      </c>
-      <c r="V9" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="W9" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="X9" s="59" t="str">
-        <f t="shared" si="4"/>
         <v>Key-INC-9</v>
       </c>
       <c r="Y9" s="30" t="s">
-        <v>164</v>
+        <v>381</v>
       </c>
       <c r="Z9" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="AA9" s="29" t="s">
-        <v>176</v>
+      <c r="AA9" s="30" t="s">
+        <v>382</v>
       </c>
       <c r="AB9" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC9" s="30" t="s">
-        <v>203</v>
+        <v>412</v>
       </c>
       <c r="AD9" s="64" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="60">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C10" s="42" t="s">
-        <v>292</v>
+      <c r="C10" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>113</v>
+        <v>374</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>206</v>
+        <v>375</v>
       </c>
       <c r="F10" s="57" t="s">
-        <v>140</v>
+        <v>417</v>
       </c>
       <c r="G10" s="61" t="s">
         <v>9</v>
@@ -3661,71 +3967,72 @@
         <v>9</v>
       </c>
       <c r="L10" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M10" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N10" s="33" t="s">
-        <v>200</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N10" s="33" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
       </c>
       <c r="O10" s="33" t="str">
-        <f t="shared" si="6"/>
-        <v>Alarme Apito</v>
-      </c>
-      <c r="P10" s="30" t="s">
-        <v>141</v>
+        <f t="shared" si="0"/>
+        <v>Tubo Multicamada</v>
+      </c>
+      <c r="P10" s="67" t="s">
+        <v>418</v>
       </c>
       <c r="Q10" s="30" t="s">
-        <v>142</v>
+        <v>419</v>
       </c>
       <c r="R10" s="30" t="s">
-        <v>305</v>
+        <v>420</v>
       </c>
       <c r="S10" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T10" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U10" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="V10" s="30" t="str">
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
+      </c>
+      <c r="W10" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="X10" s="59" t="str">
         <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U10" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema Incêndio</v>
-      </c>
-      <c r="V10" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Alarmes de Incêndio</v>
-      </c>
-      <c r="W10" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="X10" s="59" t="str">
-        <f t="shared" si="4"/>
         <v>Key-INC-10</v>
       </c>
       <c r="Y10" s="30" t="s">
-        <v>164</v>
+        <v>381</v>
       </c>
       <c r="Z10" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="AA10" s="29" t="s">
-        <v>177</v>
+      <c r="AA10" s="30" t="s">
+        <v>382</v>
       </c>
       <c r="AB10" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="30" t="s">
-        <v>203</v>
+        <v>407</v>
       </c>
       <c r="AD10" s="64" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="60">
         <v>11</v>
       </c>
@@ -3738,11 +4045,11 @@
       <c r="D11" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F11" s="57" t="s">
-        <v>143</v>
+      <c r="E11" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>113</v>
       </c>
       <c r="G11" s="61" t="s">
         <v>9</v>
@@ -3760,59 +4067,58 @@
         <v>9</v>
       </c>
       <c r="L11" s="33" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="L11" si="3">CONCATENATE("", C11)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M11" s="33" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="M11" si="4">CONCATENATE("", D11)</f>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N11" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="O11" s="33" t="str">
+        <v>199</v>
+      </c>
+      <c r="O11" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="P11" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q11" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="R11" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="S11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="30" t="str">
+        <f t="shared" ref="T11:V27" si="5">SUBSTITUTE(C11, ".", " ")</f>
+        <v>Sistemas Prediais</v>
+      </c>
+      <c r="U11" s="30" t="str">
+        <f t="shared" ref="U11:V25" si="6">SUBSTITUTE(D11, ".", " ")</f>
+        <v>Sistema Incêndio</v>
+      </c>
+      <c r="V11" s="30" t="str">
         <f t="shared" si="6"/>
-        <v>Terminal Combate Fogo</v>
-      </c>
-      <c r="P11" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q11" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="R11" s="30" t="s">
-        <v>306</v>
-      </c>
-      <c r="S11" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T11" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U11" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema Incêndio</v>
-      </c>
-      <c r="V11" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Peças de Incêndio</v>
+        <v>Sistema Combate</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X11" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-11</v>
       </c>
-      <c r="Y11" s="30" t="s">
-        <v>165</v>
+      <c r="Y11" s="29" t="s">
+        <v>105</v>
       </c>
       <c r="Z11" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="29" t="s">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="AB11" s="64" t="s">
         <v>9</v>
@@ -3824,7 +4130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="60">
         <v>12</v>
       </c>
@@ -3838,10 +4144,10 @@
         <v>113</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F12" s="57" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="G12" s="61" t="s">
         <v>9</v>
@@ -3859,59 +4165,59 @@
         <v>9</v>
       </c>
       <c r="L12" s="33" t="str">
+        <f t="shared" ref="L12:M28" si="7">CONCATENATE("", C12)</f>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M12" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N12" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O12" s="33" t="str">
+        <f t="shared" ref="O12:O26" si="8">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F12),"."," ")," De "," de "))</f>
+        <v>Alarme</v>
+      </c>
+      <c r="P12" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q12" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="R12" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="S12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T12" s="30" t="str">
         <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M12" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N12" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="O12" s="33" t="str">
+        <v>Sistemas Prediais</v>
+      </c>
+      <c r="U12" s="30" t="str">
         <f t="shared" si="6"/>
-        <v>Mangueira Entrada</v>
-      </c>
-      <c r="P12" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q12" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="R12" s="30" t="s">
-        <v>307</v>
-      </c>
-      <c r="S12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T12" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U12" s="30" t="str">
-        <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V12" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="6"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="W12" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X12" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-12</v>
       </c>
       <c r="Y12" s="30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z12" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="29" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="AB12" s="64" t="s">
         <v>9</v>
@@ -3923,7 +4229,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="60">
         <v>13</v>
       </c>
@@ -3937,10 +4243,10 @@
         <v>113</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F13" s="57" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="G13" s="61" t="s">
         <v>9</v>
@@ -3958,59 +4264,59 @@
         <v>9</v>
       </c>
       <c r="L13" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M13" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N13" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O13" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>Alarme Campainha</v>
+      </c>
+      <c r="P13" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q13" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="R13" s="30" t="s">
+        <v>299</v>
+      </c>
+      <c r="S13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T13" s="30" t="str">
         <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M13" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N13" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="O13" s="33" t="str">
+        <v>Sistemas Prediais</v>
+      </c>
+      <c r="U13" s="30" t="str">
         <f t="shared" si="6"/>
-        <v>Mangueira Carretel</v>
-      </c>
-      <c r="P13" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q13" s="30" t="s">
-        <v>151</v>
-      </c>
-      <c r="R13" s="30" t="s">
-        <v>308</v>
-      </c>
-      <c r="S13" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T13" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U13" s="30" t="str">
-        <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V13" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="6"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="W13" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X13" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-13</v>
       </c>
       <c r="Y13" s="30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z13" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="29" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="AB13" s="64" t="s">
         <v>9</v>
@@ -4022,7 +4328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="60">
         <v>14</v>
       </c>
@@ -4036,10 +4342,10 @@
         <v>113</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F14" s="57" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="G14" s="61" t="s">
         <v>9</v>
@@ -4057,59 +4363,59 @@
         <v>9</v>
       </c>
       <c r="L14" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M14" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N14" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O14" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>Alarme Campainha Caixa</v>
+      </c>
+      <c r="P14" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q14" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="R14" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="S14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T14" s="30" t="str">
         <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M14" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N14" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="O14" s="33" t="str">
+        <v>Sistemas Prediais</v>
+      </c>
+      <c r="U14" s="30" t="str">
         <f t="shared" si="6"/>
-        <v>Mangueira Canhão</v>
-      </c>
-      <c r="P14" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q14" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="R14" s="30" t="s">
-        <v>309</v>
-      </c>
-      <c r="S14" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T14" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U14" s="30" t="str">
-        <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V14" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="6"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="W14" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X14" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-14</v>
       </c>
       <c r="Y14" s="30" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Z14" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="29" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AB14" s="64" t="s">
         <v>9</v>
@@ -4121,7 +4427,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="60">
         <v>15</v>
       </c>
@@ -4135,10 +4441,10 @@
         <v>113</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F15" s="57" t="s">
-        <v>212</v>
+        <v>128</v>
       </c>
       <c r="G15" s="61" t="s">
         <v>9</v>
@@ -4156,59 +4462,59 @@
         <v>9</v>
       </c>
       <c r="L15" s="33" t="str">
-        <f t="shared" ref="L15" si="7">CONCATENATE("", C15)</f>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M15" s="33" t="str">
-        <f t="shared" ref="M15" si="8">CONCATENATE("", D15)</f>
+        <f t="shared" si="7"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N15" s="33" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="O15" s="33" t="str">
-        <f t="shared" ref="O15" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F15),"."," ")," De "," de "))</f>
-        <v>Detetor de Fumaça</v>
+        <f t="shared" si="8"/>
+        <v>Alarme Lumínico</v>
       </c>
       <c r="P15" s="30" t="s">
-        <v>213</v>
+        <v>129</v>
       </c>
       <c r="Q15" s="30" t="s">
-        <v>214</v>
+        <v>130</v>
       </c>
       <c r="R15" s="30" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="S15" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T15" s="30" t="str">
-        <f t="shared" ref="T15" si="10">SUBSTITUTE(C15, ".", " ")</f>
+        <f t="shared" si="5"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="U15" s="30" t="str">
-        <f t="shared" ref="U15" si="11">SUBSTITUTE(D15, ".", " ")</f>
+        <f t="shared" si="6"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V15" s="30" t="str">
-        <f t="shared" ref="V15" si="12">SUBSTITUTE(E15, ".", " ")</f>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="6"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="W15" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X15" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-15</v>
       </c>
       <c r="Y15" s="30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z15" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="29" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AB15" s="64" t="s">
         <v>9</v>
@@ -4220,7 +4526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="60">
         <v>16</v>
       </c>
@@ -4234,10 +4540,10 @@
         <v>113</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F16" s="57" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="G16" s="61" t="s">
         <v>9</v>
@@ -4255,59 +4561,59 @@
         <v>9</v>
       </c>
       <c r="L16" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M16" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N16" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O16" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>Alarme Caixa Manual</v>
+      </c>
+      <c r="P16" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q16" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="R16" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="S16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T16" s="30" t="str">
         <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M16" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N16" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="O16" s="33" t="str">
+        <v>Sistemas Prediais</v>
+      </c>
+      <c r="U16" s="30" t="str">
         <f t="shared" si="6"/>
-        <v>Hidrante</v>
-      </c>
-      <c r="P16" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q16" s="30" t="s">
-        <v>157</v>
-      </c>
-      <c r="R16" s="30" t="s">
-        <v>311</v>
-      </c>
-      <c r="S16" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T16" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U16" s="30" t="str">
-        <f t="shared" si="3"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V16" s="30" t="str">
-        <f t="shared" si="3"/>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="6"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="W16" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X16" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-16</v>
       </c>
       <c r="Y16" s="30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z16" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="29" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="AB16" s="64" t="s">
         <v>9</v>
@@ -4319,7 +4625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="60">
         <v>17</v>
       </c>
@@ -4333,10 +4639,10 @@
         <v>113</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F17" s="57" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="G17" s="61" t="s">
         <v>9</v>
@@ -4354,59 +4660,59 @@
         <v>9</v>
       </c>
       <c r="L17" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M17" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N17" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O17" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>Alarme Detonador</v>
+      </c>
+      <c r="P17" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q17" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="R17" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="S17" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T17" s="30" t="str">
         <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M17" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N17" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="O17" s="33" t="str">
+        <v>Sistemas Prediais</v>
+      </c>
+      <c r="U17" s="30" t="str">
         <f t="shared" si="6"/>
-        <v>Sprinkler</v>
-      </c>
-      <c r="P17" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q17" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="R17" s="30" t="s">
-        <v>312</v>
-      </c>
-      <c r="S17" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T17" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Sistemas Prediais</v>
-      </c>
-      <c r="U17" s="30" t="str">
-        <f t="shared" si="2"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V17" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="6"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="W17" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X17" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-17</v>
       </c>
       <c r="Y17" s="30" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Z17" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="29" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="AB17" s="64" t="s">
         <v>9</v>
@@ -4418,7 +4724,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="60">
         <v>18</v>
       </c>
@@ -4432,10 +4738,10 @@
         <v>113</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F18" s="57" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="G18" s="61" t="s">
         <v>9</v>
@@ -4453,58 +4759,59 @@
         <v>9</v>
       </c>
       <c r="L18" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M18" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N18" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O18" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>Alarme Sirene</v>
+      </c>
+      <c r="P18" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q18" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="R18" s="30" t="s">
+        <v>304</v>
+      </c>
+      <c r="S18" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="30" t="str">
         <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M18" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N18" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="O18" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="P18" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q18" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="R18" s="30" t="s">
-        <v>313</v>
-      </c>
-      <c r="S18" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T18" s="30" t="str">
-        <f t="shared" si="2"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="U18" s="30" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V18" s="30" t="str">
-        <f t="shared" si="2"/>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="6"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="W18" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X18" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-18</v>
       </c>
       <c r="Y18" s="30" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Z18" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="29" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="AB18" s="64" t="s">
         <v>9</v>
@@ -4516,7 +4823,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="60">
         <v>19</v>
       </c>
@@ -4530,10 +4837,10 @@
         <v>113</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F19" s="42" t="s">
-        <v>163</v>
+        <v>206</v>
+      </c>
+      <c r="F19" s="57" t="s">
+        <v>140</v>
       </c>
       <c r="G19" s="61" t="s">
         <v>9</v>
@@ -4551,58 +4858,59 @@
         <v>9</v>
       </c>
       <c r="L19" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M19" s="33" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N19" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="O19" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>Alarme Apito</v>
+      </c>
+      <c r="P19" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q19" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="R19" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="S19" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T19" s="30" t="str">
         <f t="shared" si="5"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M19" s="33" t="str">
-        <f t="shared" si="5"/>
-        <v>Sistema.Incêndio</v>
-      </c>
-      <c r="N19" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="O19" s="52" t="s">
-        <v>191</v>
-      </c>
-      <c r="P19" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q19" s="30" t="s">
-        <v>330</v>
-      </c>
-      <c r="R19" s="30" t="s">
-        <v>314</v>
-      </c>
-      <c r="S19" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T19" s="30" t="str">
-        <f t="shared" ref="T19:V24" si="13">SUBSTITUTE(C19, ".", " ")</f>
         <v>Sistemas Prediais</v>
       </c>
       <c r="U19" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V19" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Peças de Incêndio</v>
+        <f t="shared" si="6"/>
+        <v>Alarmes de Incêndio</v>
       </c>
       <c r="W19" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X19" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-19</v>
       </c>
       <c r="Y19" s="30" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Z19" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="29" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="AB19" s="64" t="s">
         <v>9</v>
@@ -4614,7 +4922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="60">
         <v>20</v>
       </c>
@@ -4627,11 +4935,11 @@
       <c r="D20" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E20" s="42" t="s">
-        <v>208</v>
-      </c>
-      <c r="F20" s="42" t="s">
-        <v>115</v>
+      <c r="E20" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F20" s="57" t="s">
+        <v>143</v>
       </c>
       <c r="G20" s="61" t="s">
         <v>9</v>
@@ -4649,58 +4957,59 @@
         <v>9</v>
       </c>
       <c r="L20" s="33" t="str">
-        <f t="shared" ref="L20:L23" si="14">CONCATENATE("", C20)</f>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M20" s="33" t="str">
-        <f t="shared" ref="M20:M23" si="15">CONCATENATE("", D20)</f>
+        <f t="shared" si="7"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N20" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O20" s="52" t="s">
-        <v>192</v>
-      </c>
-      <c r="P20" s="52" t="s">
-        <v>100</v>
+        <v>201</v>
+      </c>
+      <c r="O20" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>Terminal Combate Fogo</v>
+      </c>
+      <c r="P20" s="30" t="s">
+        <v>144</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="R20" s="30" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="S20" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T20" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="5"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="U20" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V20" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Tubulação de Incêndio</v>
+        <f t="shared" si="6"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="W20" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X20" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-20</v>
       </c>
-      <c r="Y20" s="29" t="s">
-        <v>248</v>
+      <c r="Y20" s="30" t="s">
+        <v>165</v>
       </c>
       <c r="Z20" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA20" s="29" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="AB20" s="64" t="s">
         <v>9</v>
@@ -4712,7 +5021,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="60">
         <v>21</v>
       </c>
@@ -4725,11 +5034,11 @@
       <c r="D21" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E21" s="42" t="s">
-        <v>208</v>
-      </c>
-      <c r="F21" s="42" t="s">
-        <v>209</v>
+      <c r="E21" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F21" s="57" t="s">
+        <v>146</v>
       </c>
       <c r="G21" s="61" t="s">
         <v>9</v>
@@ -4747,58 +5056,59 @@
         <v>9</v>
       </c>
       <c r="L21" s="33" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M21" s="33" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="7"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N21" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O21" s="52" t="s">
-        <v>193</v>
-      </c>
-      <c r="P21" s="52" t="s">
-        <v>103</v>
+        <v>201</v>
+      </c>
+      <c r="O21" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>Mangueira Entrada</v>
+      </c>
+      <c r="P21" s="30" t="s">
+        <v>147</v>
       </c>
       <c r="Q21" s="30" t="s">
-        <v>331</v>
+        <v>148</v>
       </c>
       <c r="R21" s="30" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="S21" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T21" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="5"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="U21" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V21" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Tubulação de Incêndio</v>
+        <f t="shared" si="6"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="W21" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X21" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-21</v>
       </c>
-      <c r="Y21" s="29" t="s">
-        <v>248</v>
+      <c r="Y21" s="30" t="s">
+        <v>165</v>
       </c>
       <c r="Z21" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA21" s="29" t="s">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="AB21" s="64" t="s">
         <v>9</v>
@@ -4810,7 +5120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="60">
         <v>22</v>
       </c>
@@ -4823,11 +5133,11 @@
       <c r="D22" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E22" s="42" t="s">
-        <v>208</v>
-      </c>
-      <c r="F22" s="42" t="s">
-        <v>116</v>
+      <c r="E22" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F22" s="57" t="s">
+        <v>149</v>
       </c>
       <c r="G22" s="61" t="s">
         <v>9</v>
@@ -4845,58 +5155,59 @@
         <v>9</v>
       </c>
       <c r="L22" s="33" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M22" s="33" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="7"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N22" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O22" s="52" t="s">
-        <v>194</v>
-      </c>
-      <c r="P22" s="52" t="s">
-        <v>101</v>
+        <v>201</v>
+      </c>
+      <c r="O22" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>Mangueira Carretel</v>
+      </c>
+      <c r="P22" s="30" t="s">
+        <v>150</v>
       </c>
       <c r="Q22" s="30" t="s">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="R22" s="30" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="S22" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T22" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="5"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="U22" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V22" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Tubulação de Incêndio</v>
+        <f t="shared" si="6"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="W22" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X22" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-22</v>
       </c>
-      <c r="Y22" s="29" t="s">
-        <v>248</v>
+      <c r="Y22" s="30" t="s">
+        <v>165</v>
       </c>
       <c r="Z22" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA22" s="29" t="s">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="AB22" s="64" t="s">
         <v>9</v>
@@ -4908,7 +5219,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="60">
         <v>23</v>
       </c>
@@ -4921,11 +5232,11 @@
       <c r="D23" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E23" s="42" t="s">
-        <v>208</v>
-      </c>
-      <c r="F23" s="42" t="s">
-        <v>117</v>
+      <c r="E23" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F23" s="57" t="s">
+        <v>152</v>
       </c>
       <c r="G23" s="61" t="s">
         <v>9</v>
@@ -4943,58 +5254,59 @@
         <v>9</v>
       </c>
       <c r="L23" s="33" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M23" s="33" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="7"/>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N23" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O23" s="52" t="s">
-        <v>195</v>
-      </c>
-      <c r="P23" s="52" t="s">
-        <v>102</v>
+        <v>201</v>
+      </c>
+      <c r="O23" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>Mangueira Canhão</v>
+      </c>
+      <c r="P23" s="30" t="s">
+        <v>153</v>
       </c>
       <c r="Q23" s="30" t="s">
-        <v>332</v>
+        <v>154</v>
       </c>
       <c r="R23" s="30" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="S23" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T23" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="5"/>
         <v>Sistemas Prediais</v>
       </c>
       <c r="U23" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V23" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Tubulação de Incêndio</v>
+        <f t="shared" si="6"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="W23" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X23" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-23</v>
       </c>
-      <c r="Y23" s="29" t="s">
-        <v>248</v>
+      <c r="Y23" s="30" t="s">
+        <v>166</v>
       </c>
       <c r="Z23" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA23" s="29" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="AB23" s="64" t="s">
         <v>9</v>
@@ -5006,7 +5318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="60">
         <v>24</v>
       </c>
@@ -5019,11 +5331,11 @@
       <c r="D24" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E24" s="42" t="s">
-        <v>208</v>
-      </c>
-      <c r="F24" s="42" t="s">
-        <v>169</v>
+      <c r="E24" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F24" s="57" t="s">
+        <v>212</v>
       </c>
       <c r="G24" s="61" t="s">
         <v>9</v>
@@ -5041,58 +5353,59 @@
         <v>9</v>
       </c>
       <c r="L24" s="33" t="str">
-        <f t="shared" ref="L24:L26" si="16">CONCATENATE("", C24)</f>
+        <f t="shared" ref="L24" si="9">CONCATENATE("", C24)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M24" s="33" t="str">
-        <f t="shared" ref="M24:M26" si="17">CONCATENATE("", D24)</f>
+        <f t="shared" ref="M24" si="10">CONCATENATE("", D24)</f>
         <v>Sistema.Incêndio</v>
       </c>
       <c r="N24" s="33" t="s">
-        <v>202</v>
-      </c>
-      <c r="O24" s="52" t="s">
-        <v>196</v>
-      </c>
-      <c r="P24" s="52" t="s">
-        <v>102</v>
+        <v>201</v>
+      </c>
+      <c r="O24" s="33" t="str">
+        <f t="shared" ref="O24" si="11">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F24),"."," ")," De "," de "))</f>
+        <v>Detetor de Fumaça</v>
+      </c>
+      <c r="P24" s="30" t="s">
+        <v>213</v>
       </c>
       <c r="Q24" s="30" t="s">
-        <v>332</v>
+        <v>214</v>
       </c>
       <c r="R24" s="30" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="S24" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T24" s="30" t="str">
-        <f t="shared" ref="T24:T26" si="18">SUBSTITUTE(C24, ".", " ")</f>
+        <f t="shared" ref="T24" si="12">SUBSTITUTE(C24, ".", " ")</f>
         <v>Sistemas Prediais</v>
       </c>
       <c r="U24" s="30" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="U24" si="13">SUBSTITUTE(D24, ".", " ")</f>
         <v>Sistema Incêndio</v>
       </c>
       <c r="V24" s="30" t="str">
-        <f t="shared" si="13"/>
-        <v>Tubulação de Incêndio</v>
+        <f t="shared" ref="V24" si="14">SUBSTITUTE(E24, ".", " ")</f>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="W24" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X24" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-24</v>
       </c>
-      <c r="Y24" s="29" t="s">
-        <v>248</v>
+      <c r="Y24" s="30" t="s">
+        <v>165</v>
       </c>
       <c r="Z24" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA24" s="29" t="s">
-        <v>246</v>
+        <v>181</v>
       </c>
       <c r="AB24" s="64" t="s">
         <v>9</v>
@@ -5104,24 +5417,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="60">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>216</v>
+        <v>292</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>231</v>
-      </c>
-      <c r="F25" s="42" t="s">
-        <v>224</v>
+        <v>113</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F25" s="57" t="s">
+        <v>155</v>
       </c>
       <c r="G25" s="61" t="s">
         <v>9</v>
@@ -5139,58 +5452,59 @@
         <v>9</v>
       </c>
       <c r="L25" s="33" t="str">
-        <f t="shared" si="16"/>
-        <v>De.Incêndio</v>
+        <f t="shared" si="7"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M25" s="33" t="str">
-        <f t="shared" si="17"/>
-        <v>Sistemas.Passivos</v>
+        <f t="shared" si="7"/>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N25" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="O25" s="52" t="s">
-        <v>222</v>
-      </c>
-      <c r="P25" s="52" t="s">
-        <v>217</v>
+        <v>201</v>
+      </c>
+      <c r="O25" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>Hidrante</v>
+      </c>
+      <c r="P25" s="30" t="s">
+        <v>156</v>
       </c>
       <c r="Q25" s="30" t="s">
-        <v>333</v>
+        <v>157</v>
       </c>
       <c r="R25" s="30" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="S25" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T25" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>De Incêndio</v>
+        <f t="shared" si="5"/>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="U25" s="30" t="str">
-        <f t="shared" ref="U25:U27" si="19">SUBSTITUTE(D25, ".", " ")</f>
-        <v>Sistemas Passivos</v>
+        <f t="shared" si="6"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="V25" s="30" t="str">
-        <f t="shared" ref="V25:V27" si="20">SUBSTITUTE(E25, ".", " ")</f>
-        <v>De Selagem</v>
+        <f t="shared" si="6"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="W25" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X25" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-25</v>
       </c>
-      <c r="Y25" s="29" t="s">
-        <v>218</v>
+      <c r="Y25" s="30" t="s">
+        <v>165</v>
       </c>
       <c r="Z25" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA25" s="29" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="AB25" s="64" t="s">
         <v>9</v>
@@ -5202,24 +5516,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="60">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>216</v>
+        <v>292</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E26" s="42" t="s">
-        <v>231</v>
-      </c>
-      <c r="F26" s="42" t="s">
-        <v>223</v>
+        <v>113</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F26" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="G26" s="61" t="s">
         <v>9</v>
@@ -5237,58 +5551,59 @@
         <v>9</v>
       </c>
       <c r="L26" s="33" t="str">
-        <f t="shared" si="16"/>
-        <v>De.Incêndio</v>
+        <f t="shared" si="7"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M26" s="33" t="str">
-        <f t="shared" si="17"/>
-        <v>Sistemas.Passivos</v>
+        <f t="shared" si="7"/>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N26" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="O26" s="52" t="s">
-        <v>221</v>
-      </c>
-      <c r="P26" s="52" t="s">
-        <v>228</v>
+        <v>201</v>
+      </c>
+      <c r="O26" s="33" t="str">
+        <f t="shared" si="8"/>
+        <v>Sprinkler</v>
+      </c>
+      <c r="P26" s="30" t="s">
+        <v>158</v>
       </c>
       <c r="Q26" s="30" t="s">
-        <v>334</v>
+        <v>159</v>
       </c>
       <c r="R26" s="30" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="S26" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T26" s="30" t="str">
-        <f t="shared" si="18"/>
-        <v>De Incêndio</v>
+        <f t="shared" si="5"/>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="U26" s="30" t="str">
-        <f t="shared" si="19"/>
-        <v>Sistemas Passivos</v>
+        <f t="shared" si="5"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="V26" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De Selagem</v>
+        <f t="shared" si="5"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="W26" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X26" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-26</v>
       </c>
-      <c r="Y26" s="29" t="s">
-        <v>244</v>
+      <c r="Y26" s="30" t="s">
+        <v>167</v>
       </c>
       <c r="Z26" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA26" s="29" t="s">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="AB26" s="64" t="s">
         <v>9</v>
@@ -5300,24 +5615,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="60">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>216</v>
+        <v>292</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>231</v>
-      </c>
-      <c r="F27" s="42" t="s">
-        <v>225</v>
+        <v>113</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F27" s="57" t="s">
+        <v>160</v>
       </c>
       <c r="G27" s="61" t="s">
         <v>9</v>
@@ -5335,58 +5650,58 @@
         <v>9</v>
       </c>
       <c r="L27" s="33" t="str">
-        <f t="shared" ref="L27:L29" si="21">CONCATENATE("", C27)</f>
-        <v>De.Incêndio</v>
+        <f t="shared" si="7"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M27" s="33" t="str">
-        <f t="shared" ref="M27:M29" si="22">CONCATENATE("", D27)</f>
-        <v>Sistemas.Passivos</v>
+        <f t="shared" si="7"/>
+        <v>Sistema.Incêndio</v>
       </c>
       <c r="N27" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="O27" s="52" t="s">
-        <v>227</v>
-      </c>
-      <c r="P27" s="52" t="s">
-        <v>229</v>
+        <v>201</v>
+      </c>
+      <c r="O27" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="P27" s="30" t="s">
+        <v>161</v>
       </c>
       <c r="Q27" s="30" t="s">
-        <v>335</v>
+        <v>162</v>
       </c>
       <c r="R27" s="30" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="S27" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T27" s="30" t="str">
-        <f t="shared" ref="T27:T29" si="23">SUBSTITUTE(C27, ".", " ")</f>
-        <v>De Incêndio</v>
+        <f t="shared" si="5"/>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="U27" s="30" t="str">
-        <f t="shared" si="19"/>
-        <v>Sistemas Passivos</v>
+        <f t="shared" si="5"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="V27" s="30" t="str">
-        <f t="shared" si="20"/>
-        <v>De Selagem</v>
+        <f t="shared" si="5"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="W27" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X27" s="59" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-27</v>
       </c>
-      <c r="Y27" s="29" t="s">
-        <v>245</v>
+      <c r="Y27" s="30" t="s">
+        <v>167</v>
       </c>
       <c r="Z27" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA27" s="29" t="s">
-        <v>9</v>
+        <v>183</v>
       </c>
       <c r="AB27" s="64" t="s">
         <v>9</v>
@@ -5398,24 +5713,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="60">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>216</v>
+        <v>292</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="E28" s="42" t="s">
-        <v>233</v>
+        <v>113</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="F28" s="42" t="s">
-        <v>234</v>
+        <v>163</v>
       </c>
       <c r="G28" s="61" t="s">
         <v>9</v>
@@ -5433,58 +5748,58 @@
         <v>9</v>
       </c>
       <c r="L28" s="33" t="str">
-        <f t="shared" ref="L28" si="24">CONCATENATE("", C28)</f>
-        <v>De.Incêndio</v>
+        <f t="shared" si="7"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M28" s="33" t="str">
-        <f t="shared" ref="M28" si="25">CONCATENATE("", D28)</f>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N28" s="52" t="s">
-        <v>240</v>
+        <f t="shared" si="7"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N28" s="33" t="s">
+        <v>201</v>
       </c>
       <c r="O28" s="52" t="s">
-        <v>237</v>
-      </c>
-      <c r="P28" s="63" t="s">
-        <v>241</v>
+        <v>191</v>
+      </c>
+      <c r="P28" s="52" t="s">
+        <v>106</v>
       </c>
       <c r="Q28" s="30" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="R28" s="30" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="S28" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T28" s="30" t="str">
-        <f t="shared" ref="T28" si="26">SUBSTITUTE(C28, ".", " ")</f>
-        <v>De Incêndio</v>
+        <f t="shared" ref="T28:V33" si="15">SUBSTITUTE(C28, ".", " ")</f>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="U28" s="30" t="str">
-        <f t="shared" ref="U28:U30" si="27">SUBSTITUTE(D28, ".", " ")</f>
-        <v>Sistemas Ativos</v>
+        <f t="shared" si="15"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="V28" s="30" t="str">
-        <f t="shared" ref="V28:V30" si="28">SUBSTITUTE(E28, ".", " ")</f>
-        <v>De Combate</v>
+        <f t="shared" si="15"/>
+        <v>Peças de Incêndio</v>
       </c>
       <c r="W28" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X28" s="59" t="str">
-        <f t="shared" ref="X28:X30" si="29">CONCATENATE("Key-INC-",A28)</f>
+        <f t="shared" si="2"/>
         <v>Key-INC-28</v>
       </c>
       <c r="Y28" s="30" t="s">
-        <v>249</v>
+        <v>166</v>
       </c>
       <c r="Z28" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA28" s="29" t="s">
-        <v>247</v>
+        <v>168</v>
       </c>
       <c r="AB28" s="64" t="s">
         <v>9</v>
@@ -5496,24 +5811,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="60">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>216</v>
+        <v>292</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>232</v>
+        <v>113</v>
       </c>
       <c r="E29" s="42" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>235</v>
+        <v>115</v>
       </c>
       <c r="G29" s="61" t="s">
         <v>9</v>
@@ -5531,58 +5846,58 @@
         <v>9</v>
       </c>
       <c r="L29" s="33" t="str">
-        <f t="shared" si="21"/>
-        <v>De.Incêndio</v>
+        <f t="shared" ref="L29:L32" si="16">CONCATENATE("", C29)</f>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M29" s="33" t="str">
-        <f t="shared" si="22"/>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N29" s="52" t="s">
-        <v>240</v>
+        <f t="shared" ref="M29:M32" si="17">CONCATENATE("", D29)</f>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N29" s="33" t="s">
+        <v>202</v>
       </c>
       <c r="O29" s="52" t="s">
-        <v>238</v>
-      </c>
-      <c r="P29" s="63" t="s">
-        <v>242</v>
+        <v>192</v>
+      </c>
+      <c r="P29" s="52" t="s">
+        <v>100</v>
       </c>
       <c r="Q29" s="30" t="s">
-        <v>337</v>
+        <v>100</v>
       </c>
       <c r="R29" s="30" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="S29" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T29" s="30" t="str">
-        <f t="shared" si="23"/>
-        <v>De Incêndio</v>
+        <f t="shared" si="15"/>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="U29" s="30" t="str">
-        <f t="shared" ref="U29" si="30">SUBSTITUTE(D29, ".", " ")</f>
-        <v>Sistemas Ativos</v>
+        <f t="shared" si="15"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="V29" s="30" t="str">
-        <f t="shared" ref="V29" si="31">SUBSTITUTE(E29, ".", " ")</f>
-        <v>De Combate</v>
+        <f t="shared" si="15"/>
+        <v>Tubulação de Incêndio</v>
       </c>
       <c r="W29" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X29" s="59" t="str">
-        <f t="shared" ref="X29" si="32">CONCATENATE("Key-INC-",A29)</f>
+        <f t="shared" si="2"/>
         <v>Key-INC-29</v>
       </c>
-      <c r="Y29" s="30" t="s">
-        <v>249</v>
+      <c r="Y29" s="29" t="s">
+        <v>248</v>
       </c>
       <c r="Z29" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA29" s="29" t="s">
-        <v>247</v>
+        <v>104</v>
       </c>
       <c r="AB29" s="64" t="s">
         <v>9</v>
@@ -5594,24 +5909,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="60">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>216</v>
+        <v>292</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>232</v>
+        <v>113</v>
       </c>
       <c r="E30" s="42" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="F30" s="42" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="G30" s="61" t="s">
         <v>9</v>
@@ -5629,58 +5944,58 @@
         <v>9</v>
       </c>
       <c r="L30" s="33" t="str">
-        <f t="shared" ref="L30" si="33">CONCATENATE("", C30)</f>
-        <v>De.Incêndio</v>
+        <f t="shared" si="16"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M30" s="33" t="str">
-        <f t="shared" ref="M30" si="34">CONCATENATE("", D30)</f>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N30" s="52" t="s">
-        <v>240</v>
+        <f t="shared" si="17"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N30" s="33" t="s">
+        <v>202</v>
       </c>
       <c r="O30" s="52" t="s">
-        <v>239</v>
-      </c>
-      <c r="P30" s="63" t="s">
-        <v>243</v>
+        <v>193</v>
+      </c>
+      <c r="P30" s="52" t="s">
+        <v>103</v>
       </c>
       <c r="Q30" s="30" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="R30" s="30" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="S30" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T30" s="30" t="str">
-        <f t="shared" ref="T30" si="35">SUBSTITUTE(C30, ".", " ")</f>
-        <v>De Incêndio</v>
+        <f t="shared" si="15"/>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="U30" s="30" t="str">
-        <f t="shared" si="27"/>
-        <v>Sistemas Ativos</v>
+        <f t="shared" si="15"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="V30" s="30" t="str">
-        <f t="shared" si="28"/>
-        <v>De Combate</v>
+        <f t="shared" si="15"/>
+        <v>Tubulação de Incêndio</v>
       </c>
       <c r="W30" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X30" s="59" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-30</v>
       </c>
-      <c r="Y30" s="30" t="s">
-        <v>249</v>
+      <c r="Y30" s="29" t="s">
+        <v>248</v>
       </c>
       <c r="Z30" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA30" s="29" t="s">
-        <v>247</v>
+        <v>104</v>
       </c>
       <c r="AB30" s="64" t="s">
         <v>9</v>
@@ -5692,24 +6007,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="60">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>216</v>
+        <v>292</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>232</v>
+        <v>113</v>
       </c>
       <c r="E31" s="42" t="s">
-        <v>268</v>
+        <v>208</v>
       </c>
       <c r="F31" s="42" t="s">
-        <v>269</v>
+        <v>116</v>
       </c>
       <c r="G31" s="61" t="s">
         <v>9</v>
@@ -5727,58 +6042,58 @@
         <v>9</v>
       </c>
       <c r="L31" s="33" t="str">
-        <f t="shared" ref="L31" si="36">CONCATENATE("", C31)</f>
-        <v>De.Incêndio</v>
+        <f t="shared" si="16"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M31" s="33" t="str">
-        <f t="shared" ref="M31" si="37">CONCATENATE("", D31)</f>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N31" s="52" t="s">
-        <v>267</v>
+        <f t="shared" si="17"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N31" s="33" t="s">
+        <v>202</v>
       </c>
       <c r="O31" s="52" t="s">
-        <v>274</v>
-      </c>
-      <c r="P31" s="63" t="s">
-        <v>283</v>
+        <v>194</v>
+      </c>
+      <c r="P31" s="52" t="s">
+        <v>101</v>
       </c>
       <c r="Q31" s="30" t="s">
-        <v>339</v>
+        <v>101</v>
       </c>
       <c r="R31" s="30" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="S31" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T31" s="30" t="str">
-        <f t="shared" ref="T31" si="38">SUBSTITUTE(C31, ".", " ")</f>
-        <v>De Incêndio</v>
+        <f t="shared" si="15"/>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="U31" s="30" t="str">
-        <f t="shared" ref="U31" si="39">SUBSTITUTE(D31, ".", " ")</f>
-        <v>Sistemas Ativos</v>
+        <f t="shared" si="15"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="V31" s="30" t="str">
-        <f t="shared" ref="V31" si="40">SUBSTITUTE(E31, ".", " ")</f>
-        <v>De Detecção</v>
+        <f t="shared" si="15"/>
+        <v>Tubulação de Incêndio</v>
       </c>
       <c r="W31" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X31" s="59" t="str">
-        <f t="shared" ref="X31" si="41">CONCATENATE("Key-INC-",A31)</f>
+        <f t="shared" si="2"/>
         <v>Key-INC-31</v>
       </c>
-      <c r="Y31" s="30" t="s">
-        <v>249</v>
+      <c r="Y31" s="29" t="s">
+        <v>248</v>
       </c>
       <c r="Z31" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA31" s="29" t="s">
-        <v>247</v>
+        <v>104</v>
       </c>
       <c r="AB31" s="64" t="s">
         <v>9</v>
@@ -5790,24 +6105,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="60">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>216</v>
+        <v>292</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>232</v>
+        <v>113</v>
       </c>
       <c r="E32" s="42" t="s">
-        <v>268</v>
+        <v>208</v>
       </c>
       <c r="F32" s="42" t="s">
-        <v>270</v>
+        <v>117</v>
       </c>
       <c r="G32" s="61" t="s">
         <v>9</v>
@@ -5825,58 +6140,58 @@
         <v>9</v>
       </c>
       <c r="L32" s="33" t="str">
-        <f t="shared" ref="L32:L33" si="42">CONCATENATE("", C32)</f>
-        <v>De.Incêndio</v>
+        <f t="shared" si="16"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M32" s="33" t="str">
-        <f t="shared" ref="M32:M33" si="43">CONCATENATE("", D32)</f>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N32" s="52" t="s">
-        <v>267</v>
+        <f t="shared" si="17"/>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N32" s="33" t="s">
+        <v>202</v>
       </c>
       <c r="O32" s="52" t="s">
-        <v>275</v>
-      </c>
-      <c r="P32" s="63" t="s">
-        <v>282</v>
+        <v>195</v>
+      </c>
+      <c r="P32" s="52" t="s">
+        <v>102</v>
       </c>
       <c r="Q32" s="30" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="R32" s="30" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="S32" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T32" s="30" t="str">
-        <f t="shared" ref="T32:T33" si="44">SUBSTITUTE(C32, ".", " ")</f>
-        <v>De Incêndio</v>
+        <f t="shared" si="15"/>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="U32" s="30" t="str">
-        <f t="shared" ref="U32:U33" si="45">SUBSTITUTE(D32, ".", " ")</f>
-        <v>Sistemas Ativos</v>
+        <f t="shared" si="15"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="V32" s="30" t="str">
-        <f t="shared" ref="V32:V33" si="46">SUBSTITUTE(E32, ".", " ")</f>
-        <v>De Detecção</v>
+        <f t="shared" si="15"/>
+        <v>Tubulação de Incêndio</v>
       </c>
       <c r="W32" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X32" s="59" t="str">
-        <f t="shared" ref="X32:X33" si="47">CONCATENATE("Key-INC-",A32)</f>
+        <f t="shared" si="2"/>
         <v>Key-INC-32</v>
       </c>
-      <c r="Y32" s="30" t="s">
-        <v>249</v>
+      <c r="Y32" s="29" t="s">
+        <v>248</v>
       </c>
       <c r="Z32" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA32" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AB32" s="64" t="s">
         <v>9</v>
@@ -5888,24 +6203,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="60">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>216</v>
+        <v>292</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>232</v>
+        <v>113</v>
       </c>
       <c r="E33" s="42" t="s">
-        <v>268</v>
+        <v>208</v>
       </c>
       <c r="F33" s="42" t="s">
-        <v>271</v>
+        <v>169</v>
       </c>
       <c r="G33" s="61" t="s">
         <v>9</v>
@@ -5923,58 +6238,58 @@
         <v>9</v>
       </c>
       <c r="L33" s="33" t="str">
-        <f t="shared" si="42"/>
-        <v>De.Incêndio</v>
+        <f t="shared" ref="L33:L35" si="18">CONCATENATE("", C33)</f>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M33" s="33" t="str">
-        <f t="shared" si="43"/>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N33" s="52" t="s">
-        <v>267</v>
+        <f t="shared" ref="M33:M35" si="19">CONCATENATE("", D33)</f>
+        <v>Sistema.Incêndio</v>
+      </c>
+      <c r="N33" s="33" t="s">
+        <v>202</v>
       </c>
       <c r="O33" s="52" t="s">
-        <v>276</v>
-      </c>
-      <c r="P33" s="63" t="s">
-        <v>281</v>
+        <v>196</v>
+      </c>
+      <c r="P33" s="52" t="s">
+        <v>102</v>
       </c>
       <c r="Q33" s="30" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="R33" s="30" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="S33" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T33" s="30" t="str">
-        <f t="shared" si="44"/>
-        <v>De Incêndio</v>
+        <f t="shared" ref="T33:T35" si="20">SUBSTITUTE(C33, ".", " ")</f>
+        <v>Sistemas Prediais</v>
       </c>
       <c r="U33" s="30" t="str">
-        <f t="shared" si="45"/>
-        <v>Sistemas Ativos</v>
+        <f t="shared" si="15"/>
+        <v>Sistema Incêndio</v>
       </c>
       <c r="V33" s="30" t="str">
-        <f t="shared" si="46"/>
-        <v>De Detecção</v>
+        <f t="shared" si="15"/>
+        <v>Tubulação de Incêndio</v>
       </c>
       <c r="W33" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X33" s="59" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="2"/>
         <v>Key-INC-33</v>
       </c>
-      <c r="Y33" s="30" t="s">
-        <v>249</v>
+      <c r="Y33" s="29" t="s">
+        <v>248</v>
       </c>
       <c r="Z33" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA33" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AB33" s="64" t="s">
         <v>9</v>
@@ -5986,7 +6301,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="60">
         <v>34</v>
       </c>
@@ -5997,13 +6312,13 @@
         <v>216</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="F34" s="42" t="s">
-        <v>272</v>
+        <v>224</v>
       </c>
       <c r="G34" s="61" t="s">
         <v>9</v>
@@ -6021,58 +6336,58 @@
         <v>9</v>
       </c>
       <c r="L34" s="33" t="str">
-        <f t="shared" ref="L34" si="48">CONCATENATE("", C34)</f>
+        <f t="shared" si="18"/>
         <v>De.Incêndio</v>
       </c>
       <c r="M34" s="33" t="str">
-        <f t="shared" ref="M34" si="49">CONCATENATE("", D34)</f>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N34" s="52" t="s">
-        <v>267</v>
+        <f t="shared" si="19"/>
+        <v>Sistemas.Passivos</v>
+      </c>
+      <c r="N34" s="33" t="s">
+        <v>226</v>
       </c>
       <c r="O34" s="52" t="s">
-        <v>277</v>
-      </c>
-      <c r="P34" s="63" t="s">
-        <v>280</v>
+        <v>222</v>
+      </c>
+      <c r="P34" s="52" t="s">
+        <v>217</v>
       </c>
       <c r="Q34" s="30" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="R34" s="30" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="S34" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T34" s="30" t="str">
-        <f t="shared" ref="T34" si="50">SUBSTITUTE(C34, ".", " ")</f>
+        <f t="shared" si="20"/>
         <v>De Incêndio</v>
       </c>
       <c r="U34" s="30" t="str">
-        <f t="shared" ref="U34" si="51">SUBSTITUTE(D34, ".", " ")</f>
-        <v>Sistemas Ativos</v>
+        <f t="shared" ref="U34:U36" si="21">SUBSTITUTE(D34, ".", " ")</f>
+        <v>Sistemas Passivos</v>
       </c>
       <c r="V34" s="30" t="str">
-        <f t="shared" ref="V34" si="52">SUBSTITUTE(E34, ".", " ")</f>
-        <v>De Detecção</v>
+        <f t="shared" ref="V34:V36" si="22">SUBSTITUTE(E34, ".", " ")</f>
+        <v>De Selagem</v>
       </c>
       <c r="W34" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X34" s="59" t="str">
-        <f t="shared" ref="X34" si="53">CONCATENATE("Key-INC-",A34)</f>
+        <f t="shared" si="2"/>
         <v>Key-INC-34</v>
       </c>
-      <c r="Y34" s="30" t="s">
-        <v>249</v>
+      <c r="Y34" s="29" t="s">
+        <v>218</v>
       </c>
       <c r="Z34" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA34" s="29" t="s">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="AB34" s="64" t="s">
         <v>9</v>
@@ -6084,7 +6399,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="60">
         <v>35</v>
       </c>
@@ -6095,13 +6410,13 @@
         <v>216</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E35" s="42" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="F35" s="42" t="s">
-        <v>273</v>
+        <v>223</v>
       </c>
       <c r="G35" s="61" t="s">
         <v>9</v>
@@ -6119,58 +6434,58 @@
         <v>9</v>
       </c>
       <c r="L35" s="33" t="str">
-        <f t="shared" ref="L35" si="54">CONCATENATE("", C35)</f>
+        <f t="shared" si="18"/>
         <v>De.Incêndio</v>
       </c>
       <c r="M35" s="33" t="str">
-        <f t="shared" ref="M35" si="55">CONCATENATE("", D35)</f>
-        <v>Sistemas.Ativos</v>
-      </c>
-      <c r="N35" s="52" t="s">
-        <v>267</v>
+        <f t="shared" si="19"/>
+        <v>Sistemas.Passivos</v>
+      </c>
+      <c r="N35" s="33" t="s">
+        <v>226</v>
       </c>
       <c r="O35" s="52" t="s">
-        <v>278</v>
-      </c>
-      <c r="P35" s="63" t="s">
-        <v>279</v>
+        <v>221</v>
+      </c>
+      <c r="P35" s="52" t="s">
+        <v>228</v>
       </c>
       <c r="Q35" s="30" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="R35" s="30" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="S35" s="30" t="s">
         <v>9</v>
       </c>
       <c r="T35" s="30" t="str">
-        <f t="shared" ref="T35:V40" si="56">SUBSTITUTE(C35, ".", " ")</f>
+        <f t="shared" si="20"/>
         <v>De Incêndio</v>
       </c>
       <c r="U35" s="30" t="str">
-        <f t="shared" ref="U35" si="57">SUBSTITUTE(D35, ".", " ")</f>
-        <v>Sistemas Ativos</v>
+        <f t="shared" si="21"/>
+        <v>Sistemas Passivos</v>
       </c>
       <c r="V35" s="30" t="str">
-        <f t="shared" ref="V35" si="58">SUBSTITUTE(E35, ".", " ")</f>
-        <v>De Detecção</v>
+        <f t="shared" si="22"/>
+        <v>De Selagem</v>
       </c>
       <c r="W35" s="30" t="s">
         <v>220</v>
       </c>
       <c r="X35" s="59" t="str">
-        <f t="shared" ref="X35:X40" si="59">CONCATENATE("Key-INC-",A35)</f>
+        <f t="shared" si="2"/>
         <v>Key-INC-35</v>
       </c>
-      <c r="Y35" s="30" t="s">
-        <v>249</v>
+      <c r="Y35" s="29" t="s">
+        <v>244</v>
       </c>
       <c r="Z35" s="64" t="s">
         <v>9</v>
       </c>
       <c r="AA35" s="29" t="s">
-        <v>247</v>
+        <v>9</v>
       </c>
       <c r="AB35" s="64" t="s">
         <v>9</v>
@@ -6182,571 +6497,1474 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="60">
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C36" s="66" t="s">
+      <c r="C36" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E36" s="42" t="s">
+        <v>231</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>225</v>
+      </c>
+      <c r="G36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K36" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L36" s="33" t="str">
+        <f t="shared" ref="L36:L38" si="23">CONCATENATE("", C36)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M36" s="33" t="str">
+        <f t="shared" ref="M36:M38" si="24">CONCATENATE("", D36)</f>
+        <v>Sistemas.Passivos</v>
+      </c>
+      <c r="N36" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="O36" s="52" t="s">
+        <v>227</v>
+      </c>
+      <c r="P36" s="52" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q36" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="R36" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="S36" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T36" s="30" t="str">
+        <f t="shared" ref="T36:T38" si="25">SUBSTITUTE(C36, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="U36" s="30" t="str">
+        <f t="shared" si="21"/>
+        <v>Sistemas Passivos</v>
+      </c>
+      <c r="V36" s="30" t="str">
+        <f t="shared" si="22"/>
+        <v>De Selagem</v>
+      </c>
+      <c r="W36" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X36" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-36</v>
+      </c>
+      <c r="Y36" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z36" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA36" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB36" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC36" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD36" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="60">
+        <v>37</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E37" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>234</v>
+      </c>
+      <c r="G37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K37" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L37" s="33" t="str">
+        <f t="shared" ref="L37" si="26">CONCATENATE("", C37)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M37" s="33" t="str">
+        <f t="shared" ref="M37" si="27">CONCATENATE("", D37)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N37" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="O37" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="P37" s="63" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q37" s="30" t="s">
+        <v>336</v>
+      </c>
+      <c r="R37" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="S37" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T37" s="30" t="str">
+        <f t="shared" ref="T37" si="28">SUBSTITUTE(C37, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="U37" s="30" t="str">
+        <f t="shared" ref="U37:U39" si="29">SUBSTITUTE(D37, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="V37" s="30" t="str">
+        <f t="shared" ref="V37:V39" si="30">SUBSTITUTE(E37, ".", " ")</f>
+        <v>De Combate</v>
+      </c>
+      <c r="W37" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X37" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-37</v>
+      </c>
+      <c r="Y37" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z37" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA37" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB37" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC37" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD37" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="60">
+        <v>38</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C38" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E38" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="G38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K38" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L38" s="33" t="str">
+        <f t="shared" si="23"/>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M38" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N38" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="O38" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="P38" s="63" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q38" s="30" t="s">
+        <v>337</v>
+      </c>
+      <c r="R38" s="30" t="s">
+        <v>323</v>
+      </c>
+      <c r="S38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T38" s="30" t="str">
+        <f t="shared" si="25"/>
+        <v>De Incêndio</v>
+      </c>
+      <c r="U38" s="30" t="str">
+        <f t="shared" ref="U38" si="31">SUBSTITUTE(D38, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="V38" s="30" t="str">
+        <f t="shared" ref="V38" si="32">SUBSTITUTE(E38, ".", " ")</f>
+        <v>De Combate</v>
+      </c>
+      <c r="W38" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X38" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-38</v>
+      </c>
+      <c r="Y38" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z38" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA38" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB38" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC38" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD38" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="60">
+        <v>39</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C39" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E39" s="42" t="s">
+        <v>233</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="G39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K39" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L39" s="33" t="str">
+        <f t="shared" ref="L39" si="33">CONCATENATE("", C39)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M39" s="33" t="str">
+        <f t="shared" ref="M39" si="34">CONCATENATE("", D39)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N39" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="O39" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="P39" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q39" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="R39" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="S39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T39" s="30" t="str">
+        <f t="shared" ref="T39" si="35">SUBSTITUTE(C39, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="U39" s="30" t="str">
+        <f t="shared" si="29"/>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="V39" s="30" t="str">
+        <f t="shared" si="30"/>
+        <v>De Combate</v>
+      </c>
+      <c r="W39" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X39" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-39</v>
+      </c>
+      <c r="Y39" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z39" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA39" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB39" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC39" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD39" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="60">
+        <v>40</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C40" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E40" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="F40" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="G40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K40" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L40" s="33" t="str">
+        <f t="shared" ref="L40" si="36">CONCATENATE("", C40)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M40" s="33" t="str">
+        <f t="shared" ref="M40" si="37">CONCATENATE("", D40)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N40" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="O40" s="52" t="s">
+        <v>274</v>
+      </c>
+      <c r="P40" s="63" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q40" s="30" t="s">
+        <v>339</v>
+      </c>
+      <c r="R40" s="30" t="s">
+        <v>325</v>
+      </c>
+      <c r="S40" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T40" s="30" t="str">
+        <f t="shared" ref="T40" si="38">SUBSTITUTE(C40, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="U40" s="30" t="str">
+        <f t="shared" ref="U40" si="39">SUBSTITUTE(D40, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="V40" s="30" t="str">
+        <f t="shared" ref="V40" si="40">SUBSTITUTE(E40, ".", " ")</f>
+        <v>De Detecção</v>
+      </c>
+      <c r="W40" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X40" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-40</v>
+      </c>
+      <c r="Y40" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z40" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA40" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB40" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC40" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD40" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="60">
+        <v>41</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C41" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E41" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="F41" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="G41" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I41" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J41" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K41" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L41" s="33" t="str">
+        <f t="shared" ref="L41:L42" si="41">CONCATENATE("", C41)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M41" s="33" t="str">
+        <f t="shared" ref="M41:M42" si="42">CONCATENATE("", D41)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N41" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="O41" s="52" t="s">
+        <v>275</v>
+      </c>
+      <c r="P41" s="63" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q41" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="R41" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="S41" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T41" s="30" t="str">
+        <f t="shared" ref="T41:T42" si="43">SUBSTITUTE(C41, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="U41" s="30" t="str">
+        <f t="shared" ref="U41:U42" si="44">SUBSTITUTE(D41, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="V41" s="30" t="str">
+        <f t="shared" ref="V41:V42" si="45">SUBSTITUTE(E41, ".", " ")</f>
+        <v>De Detecção</v>
+      </c>
+      <c r="W41" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X41" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-41</v>
+      </c>
+      <c r="Y41" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z41" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA41" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB41" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC41" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD41" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="60">
+        <v>42</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C42" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E42" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="F42" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="G42" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I42" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J42" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K42" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L42" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M42" s="33" t="str">
+        <f t="shared" si="42"/>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N42" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="O42" s="52" t="s">
+        <v>276</v>
+      </c>
+      <c r="P42" s="63" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q42" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="R42" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="S42" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T42" s="30" t="str">
+        <f t="shared" si="43"/>
+        <v>De Incêndio</v>
+      </c>
+      <c r="U42" s="30" t="str">
+        <f t="shared" si="44"/>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="V42" s="30" t="str">
+        <f t="shared" si="45"/>
+        <v>De Detecção</v>
+      </c>
+      <c r="W42" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X42" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-42</v>
+      </c>
+      <c r="Y42" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z42" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA42" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB42" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC42" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD42" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="60">
+        <v>43</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C43" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E43" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="F43" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="G43" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H43" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I43" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J43" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K43" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L43" s="33" t="str">
+        <f t="shared" ref="L43" si="46">CONCATENATE("", C43)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M43" s="33" t="str">
+        <f t="shared" ref="M43" si="47">CONCATENATE("", D43)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N43" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="O43" s="52" t="s">
+        <v>277</v>
+      </c>
+      <c r="P43" s="63" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q43" s="30" t="s">
+        <v>342</v>
+      </c>
+      <c r="R43" s="30" t="s">
+        <v>328</v>
+      </c>
+      <c r="S43" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T43" s="30" t="str">
+        <f t="shared" ref="T43" si="48">SUBSTITUTE(C43, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="U43" s="30" t="str">
+        <f t="shared" ref="U43" si="49">SUBSTITUTE(D43, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="V43" s="30" t="str">
+        <f t="shared" ref="V43" si="50">SUBSTITUTE(E43, ".", " ")</f>
+        <v>De Detecção</v>
+      </c>
+      <c r="W43" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X43" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-43</v>
+      </c>
+      <c r="Y43" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z43" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA43" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB43" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC43" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD43" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="60">
+        <v>44</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C44" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E44" s="42" t="s">
+        <v>268</v>
+      </c>
+      <c r="F44" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="G44" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I44" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J44" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K44" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L44" s="33" t="str">
+        <f t="shared" ref="L44" si="51">CONCATENATE("", C44)</f>
+        <v>De.Incêndio</v>
+      </c>
+      <c r="M44" s="33" t="str">
+        <f t="shared" ref="M44" si="52">CONCATENATE("", D44)</f>
+        <v>Sistemas.Ativos</v>
+      </c>
+      <c r="N44" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="O44" s="52" t="s">
+        <v>278</v>
+      </c>
+      <c r="P44" s="63" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q44" s="30" t="s">
+        <v>343</v>
+      </c>
+      <c r="R44" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="S44" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T44" s="30" t="str">
+        <f t="shared" ref="T44:V49" si="53">SUBSTITUTE(C44, ".", " ")</f>
+        <v>De Incêndio</v>
+      </c>
+      <c r="U44" s="30" t="str">
+        <f t="shared" ref="U44" si="54">SUBSTITUTE(D44, ".", " ")</f>
+        <v>Sistemas Ativos</v>
+      </c>
+      <c r="V44" s="30" t="str">
+        <f t="shared" ref="V44" si="55">SUBSTITUTE(E44, ".", " ")</f>
+        <v>De Detecção</v>
+      </c>
+      <c r="W44" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X44" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-44</v>
+      </c>
+      <c r="Y44" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z44" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA44" s="29" t="s">
+        <v>247</v>
+      </c>
+      <c r="AB44" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC44" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="AD44" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="60">
+        <v>45</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C45" s="66" t="s">
         <v>348</v>
       </c>
-      <c r="D36" s="66" t="s">
+      <c r="D45" s="66" t="s">
         <v>350</v>
       </c>
-      <c r="E36" s="66" t="s">
+      <c r="E45" s="66" t="s">
         <v>349</v>
       </c>
-      <c r="F36" s="66" t="s">
+      <c r="F45" s="66" t="s">
         <v>351</v>
       </c>
-      <c r="G36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K36" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L36" s="33" t="str">
-        <f t="shared" ref="L36:O40" si="60">SUBSTITUTE(CONCATENATE("", C36), ".", " ")</f>
+      <c r="G45" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H45" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I45" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J45" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K45" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L45" s="33" t="str">
+        <f t="shared" ref="L45:O49" si="56">SUBSTITUTE(CONCATENATE("", C45), ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="M36" s="33" t="str">
-        <f t="shared" si="60"/>
+      <c r="M45" s="33" t="str">
+        <f t="shared" si="56"/>
         <v>Macros</v>
       </c>
-      <c r="N36" s="33" t="str">
-        <f t="shared" si="60"/>
+      <c r="N45" s="33" t="str">
+        <f t="shared" si="56"/>
         <v>Métodos</v>
       </c>
-      <c r="O36" s="33" t="str">
-        <f t="shared" si="60"/>
+      <c r="O45" s="33" t="str">
+        <f t="shared" si="56"/>
         <v>Função Auxiliar</v>
       </c>
-      <c r="P36" s="30" t="s">
+      <c r="P45" s="30" t="s">
         <v>352</v>
       </c>
-      <c r="Q36" s="30" t="s">
+      <c r="Q45" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="R36" s="30" t="s">
+      <c r="R45" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="S36" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T36" s="30" t="str">
+      <c r="S45" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T45" s="30" t="str">
+        <f t="shared" si="53"/>
+        <v>De API</v>
+      </c>
+      <c r="U45" s="30" t="str">
+        <f t="shared" si="53"/>
+        <v>Macros</v>
+      </c>
+      <c r="V45" s="63" t="str">
+        <f t="shared" si="53"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W45" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="X45" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-45</v>
+      </c>
+      <c r="Y45" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z45" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA45" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB45" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC45" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD45" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="60">
+        <v>46</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C46" s="66" t="s">
+        <v>348</v>
+      </c>
+      <c r="D46" s="66" t="s">
+        <v>350</v>
+      </c>
+      <c r="E46" s="66" t="s">
+        <v>349</v>
+      </c>
+      <c r="F46" s="66" t="s">
+        <v>355</v>
+      </c>
+      <c r="G46" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H46" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I46" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J46" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K46" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L46" s="33" t="str">
         <f t="shared" si="56"/>
         <v>De API</v>
       </c>
-      <c r="U36" s="30" t="str">
+      <c r="M46" s="33" t="str">
         <f t="shared" si="56"/>
         <v>Macros</v>
       </c>
-      <c r="V36" s="63" t="str">
+      <c r="N46" s="33" t="str">
         <f t="shared" si="56"/>
         <v>Métodos</v>
       </c>
-      <c r="W36" s="30" t="s">
+      <c r="O46" s="33" t="str">
+        <f t="shared" si="56"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P46" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q46" s="30" t="s">
+        <v>357</v>
+      </c>
+      <c r="R46" s="30" t="s">
+        <v>358</v>
+      </c>
+      <c r="S46" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T46" s="30" t="str">
+        <f t="shared" si="53"/>
+        <v>De API</v>
+      </c>
+      <c r="U46" s="30" t="str">
+        <f t="shared" si="53"/>
+        <v>Macros</v>
+      </c>
+      <c r="V46" s="63" t="str">
+        <f t="shared" si="53"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W46" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="X36" s="59" t="str">
-        <f t="shared" si="59"/>
-        <v>Key-INC-36</v>
-      </c>
-      <c r="Y36" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z36" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA36" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB36" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC36" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD36" s="64" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="60">
-        <v>37</v>
-      </c>
-      <c r="B37" s="1" t="s">
+      <c r="X46" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-46</v>
+      </c>
+      <c r="Y46" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z46" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA46" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB46" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC46" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD46" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="60">
+        <v>47</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C37" s="66" t="s">
+      <c r="C47" s="66" t="s">
         <v>348</v>
       </c>
-      <c r="D37" s="66" t="s">
+      <c r="D47" s="66" t="s">
         <v>350</v>
       </c>
-      <c r="E37" s="66" t="s">
+      <c r="E47" s="66" t="s">
         <v>349</v>
       </c>
-      <c r="F37" s="66" t="s">
-        <v>355</v>
-      </c>
-      <c r="G37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K37" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L37" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>De API</v>
-      </c>
-      <c r="M37" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
-      </c>
-      <c r="N37" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O37" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>Função Global</v>
-      </c>
-      <c r="P37" s="30" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q37" s="30" t="s">
-        <v>357</v>
-      </c>
-      <c r="R37" s="30" t="s">
-        <v>358</v>
-      </c>
-      <c r="S37" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T37" s="30" t="str">
+      <c r="F47" s="66" t="s">
+        <v>359</v>
+      </c>
+      <c r="G47" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H47" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I47" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J47" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K47" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L47" s="33" t="str">
         <f t="shared" si="56"/>
         <v>De API</v>
       </c>
-      <c r="U37" s="30" t="str">
+      <c r="M47" s="33" t="str">
         <f t="shared" si="56"/>
         <v>Macros</v>
       </c>
-      <c r="V37" s="63" t="str">
+      <c r="N47" s="33" t="str">
         <f t="shared" si="56"/>
         <v>Métodos</v>
       </c>
-      <c r="W37" s="30" t="s">
+      <c r="O47" s="33" t="str">
+        <f t="shared" si="56"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P47" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q47" s="30" t="s">
+        <v>361</v>
+      </c>
+      <c r="R47" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="S47" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T47" s="30" t="str">
+        <f t="shared" si="53"/>
+        <v>De API</v>
+      </c>
+      <c r="U47" s="30" t="str">
+        <f t="shared" si="53"/>
+        <v>Macros</v>
+      </c>
+      <c r="V47" s="63" t="str">
+        <f t="shared" si="53"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W47" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="X37" s="59" t="str">
-        <f t="shared" si="59"/>
-        <v>Key-INC-37</v>
-      </c>
-      <c r="Y37" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z37" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA37" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB37" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC37" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD37" s="64" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="60">
-        <v>38</v>
-      </c>
-      <c r="B38" s="1" t="s">
+      <c r="X47" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-47</v>
+      </c>
+      <c r="Y47" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z47" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA47" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB47" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC47" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD47" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="60">
+        <v>48</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C38" s="66" t="s">
+      <c r="C48" s="66" t="s">
         <v>348</v>
       </c>
-      <c r="D38" s="66" t="s">
+      <c r="D48" s="66" t="s">
         <v>350</v>
       </c>
-      <c r="E38" s="66" t="s">
+      <c r="E48" s="66" t="s">
         <v>349</v>
       </c>
-      <c r="F38" s="66" t="s">
-        <v>359</v>
-      </c>
-      <c r="G38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K38" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L38" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>De API</v>
-      </c>
-      <c r="M38" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
-      </c>
-      <c r="N38" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O38" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>Função Local</v>
-      </c>
-      <c r="P38" s="30" t="s">
-        <v>360</v>
-      </c>
-      <c r="Q38" s="30" t="s">
-        <v>361</v>
-      </c>
-      <c r="R38" s="30" t="s">
-        <v>362</v>
-      </c>
-      <c r="S38" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T38" s="30" t="str">
+      <c r="F48" s="66" t="s">
+        <v>363</v>
+      </c>
+      <c r="G48" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H48" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I48" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J48" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K48" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L48" s="33" t="str">
         <f t="shared" si="56"/>
         <v>De API</v>
       </c>
-      <c r="U38" s="30" t="str">
+      <c r="M48" s="33" t="str">
         <f t="shared" si="56"/>
         <v>Macros</v>
       </c>
-      <c r="V38" s="63" t="str">
+      <c r="N48" s="33" t="str">
         <f t="shared" si="56"/>
         <v>Métodos</v>
       </c>
-      <c r="W38" s="30" t="s">
+      <c r="O48" s="33" t="str">
+        <f t="shared" si="56"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P48" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q48" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="R48" s="30" t="s">
+        <v>366</v>
+      </c>
+      <c r="S48" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T48" s="30" t="str">
+        <f t="shared" si="53"/>
+        <v>De API</v>
+      </c>
+      <c r="U48" s="30" t="str">
+        <f t="shared" si="53"/>
+        <v>Macros</v>
+      </c>
+      <c r="V48" s="63" t="str">
+        <f t="shared" si="53"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W48" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="X38" s="59" t="str">
-        <f t="shared" si="59"/>
-        <v>Key-INC-38</v>
-      </c>
-      <c r="Y38" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z38" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA38" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB38" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC38" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD38" s="64" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="60">
-        <v>39</v>
-      </c>
-      <c r="B39" s="1" t="s">
+      <c r="X48" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-48</v>
+      </c>
+      <c r="Y48" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z48" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA48" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB48" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC48" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD48" s="64" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="60">
+        <v>49</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C39" s="66" t="s">
+      <c r="C49" s="66" t="s">
         <v>348</v>
       </c>
-      <c r="D39" s="66" t="s">
+      <c r="D49" s="66" t="s">
         <v>350</v>
       </c>
-      <c r="E39" s="66" t="s">
-        <v>349</v>
-      </c>
-      <c r="F39" s="66" t="s">
-        <v>363</v>
-      </c>
-      <c r="G39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K39" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L39" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>De API</v>
-      </c>
-      <c r="M39" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
-      </c>
-      <c r="N39" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O39" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>Função Filtro</v>
-      </c>
-      <c r="P39" s="30" t="s">
-        <v>364</v>
-      </c>
-      <c r="Q39" s="30" t="s">
-        <v>365</v>
-      </c>
-      <c r="R39" s="30" t="s">
-        <v>366</v>
-      </c>
-      <c r="S39" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T39" s="30" t="str">
+      <c r="E49" s="66" t="s">
+        <v>367</v>
+      </c>
+      <c r="F49" s="66" t="s">
+        <v>368</v>
+      </c>
+      <c r="G49" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H49" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="I49" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J49" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="K49" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L49" s="33" t="str">
         <f t="shared" si="56"/>
         <v>De API</v>
       </c>
-      <c r="U39" s="30" t="str">
+      <c r="M49" s="33" t="str">
         <f t="shared" si="56"/>
         <v>Macros</v>
       </c>
-      <c r="V39" s="63" t="str">
-        <f t="shared" si="56"/>
-        <v>Métodos</v>
-      </c>
-      <c r="W39" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="X39" s="59" t="str">
-        <f t="shared" si="59"/>
-        <v>Key-INC-39</v>
-      </c>
-      <c r="Y39" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z39" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA39" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB39" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC39" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD39" s="64" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:30" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="60">
-        <v>40</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C40" s="66" t="s">
-        <v>348</v>
-      </c>
-      <c r="D40" s="66" t="s">
-        <v>350</v>
-      </c>
-      <c r="E40" s="66" t="s">
-        <v>367</v>
-      </c>
-      <c r="F40" s="66" t="s">
-        <v>368</v>
-      </c>
-      <c r="G40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K40" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L40" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>De API</v>
-      </c>
-      <c r="M40" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>Macros</v>
-      </c>
-      <c r="N40" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O40" s="33" t="str">
-        <f t="shared" si="60"/>
-        <v>Bloco de Código</v>
-      </c>
-      <c r="P40" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="Q40" s="30" t="s">
-        <v>370</v>
-      </c>
-      <c r="R40" s="30" t="s">
-        <v>371</v>
-      </c>
-      <c r="S40" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="T40" s="30" t="str">
-        <f t="shared" si="56"/>
-        <v>De API</v>
-      </c>
-      <c r="U40" s="30" t="str">
-        <f t="shared" si="56"/>
-        <v>Macros</v>
-      </c>
-      <c r="V40" s="63" t="str">
+      <c r="N49" s="33" t="str">
         <f t="shared" si="56"/>
         <v>Códigos Visuais</v>
       </c>
-      <c r="W40" s="30" t="s">
+      <c r="O49" s="33" t="str">
+        <f t="shared" si="56"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P49" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q49" s="30" t="s">
+        <v>370</v>
+      </c>
+      <c r="R49" s="30" t="s">
+        <v>371</v>
+      </c>
+      <c r="S49" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="T49" s="30" t="str">
+        <f t="shared" si="53"/>
+        <v>De API</v>
+      </c>
+      <c r="U49" s="30" t="str">
+        <f t="shared" si="53"/>
+        <v>Macros</v>
+      </c>
+      <c r="V49" s="63" t="str">
+        <f t="shared" si="53"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W49" s="30" t="s">
         <v>220</v>
       </c>
-      <c r="X40" s="59" t="str">
-        <f t="shared" si="59"/>
-        <v>Key-INC-40</v>
-      </c>
-      <c r="Y40" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z40" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA40" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB40" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC40" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD40" s="64" t="s">
+      <c r="X49" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>Key-INC-49</v>
+      </c>
+      <c r="Y49" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z49" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA49" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB49" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC49" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD49" s="64" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC883">
-    <sortCondition ref="F2:F883"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:AC892">
+    <sortCondition ref="F11:F892"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B40">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B49">
+    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E40:F40">
-    <cfRule type="duplicateValues" dxfId="25" priority="2"/>
+  <conditionalFormatting sqref="E49:F49">
+    <cfRule type="duplicateValues" dxfId="40" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="24" priority="1530"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="1547"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F2 F19:F35 F41:F1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="1552"/>
+  <conditionalFormatting sqref="F2:F7">
+    <cfRule type="duplicateValues" dxfId="38" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F18">
-    <cfRule type="duplicateValues" dxfId="22" priority="1574"/>
+  <conditionalFormatting sqref="F8:F9">
+    <cfRule type="duplicateValues" dxfId="33" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F36:F39">
-    <cfRule type="duplicateValues" dxfId="21" priority="3"/>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="duplicateValues" dxfId="28" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F41:F1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="287"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="289"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="1502"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1523"/>
+  <conditionalFormatting sqref="F12:F27">
+    <cfRule type="duplicateValues" dxfId="23" priority="1591"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O16:O18 A1:D1 F1:O1 Q1:Z1 AB1:AD1 E3:F15 L3:O15 Q3:Q18 AA3:AA18 AE3:XFD18 F16:F18 L16:M18 E16:E19 N16:N19">
-    <cfRule type="cellIs" dxfId="16" priority="94" operator="equal">
+  <conditionalFormatting sqref="F28:F44 F1 F50:F1048576 F11">
+    <cfRule type="duplicateValues" dxfId="22" priority="1569"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F45:F48">
+    <cfRule type="duplicateValues" dxfId="21" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F50:F1048576">
+    <cfRule type="duplicateValues" dxfId="20" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1519"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1540"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O25:O27 A1:D1 F1:O1 Q1:Z1 AB1:AD1 E12:F24 L12:O24 Q12:Q27 AA12:AA27 AE12:XFD27 F25:F27 L25:M27 E25:E28 N25:N28">
+    <cfRule type="cellIs" dxfId="16" priority="111" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O18">
-    <cfRule type="duplicateValues" dxfId="15" priority="42"/>
+  <conditionalFormatting sqref="O27">
+    <cfRule type="duplicateValues" dxfId="15" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O19:O27">
-    <cfRule type="duplicateValues" dxfId="14" priority="1581"/>
+  <conditionalFormatting sqref="O28:O36">
+    <cfRule type="duplicateValues" dxfId="14" priority="1598"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O28:O35">
-    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
+  <conditionalFormatting sqref="O37:O44">
+    <cfRule type="duplicateValues" dxfId="13" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2">
-    <cfRule type="duplicateValues" dxfId="12" priority="53"/>
+  <conditionalFormatting sqref="Q11">
+    <cfRule type="duplicateValues" dxfId="12" priority="70"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R35">
-    <cfRule type="cellIs" dxfId="11" priority="16" operator="equal">
+  <conditionalFormatting sqref="T11:T44">
+    <cfRule type="cellIs" dxfId="11" priority="45" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T35">
-    <cfRule type="cellIs" dxfId="10" priority="28" operator="equal">
+  <conditionalFormatting sqref="Y2:Y10 AA2:AA10 AC2:AC10 R2:R44">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y3:Y19">
-    <cfRule type="cellIs" dxfId="9" priority="46" operator="equal">
+  <conditionalFormatting sqref="Y12:Y28">
+    <cfRule type="cellIs" dxfId="9" priority="63" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y28:Y35">
-    <cfRule type="cellIs" dxfId="8" priority="15" operator="equal">
+  <conditionalFormatting sqref="Y37:Y44">
+    <cfRule type="cellIs" dxfId="8" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6761,15 +7979,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -6834,7 +8052,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -6899,7 +8117,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -6982,15 +8200,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="26" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="26" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="31">
         <v>0</v>
       </c>
@@ -7013,7 +8231,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="32">
         <v>2</v>
       </c>
@@ -7069,30 +8287,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S22"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" customWidth="1"/>
-    <col min="7" max="7" width="56.140625" customWidth="1"/>
-    <col min="8" max="8" width="5.140625" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" customWidth="1"/>
+    <col min="3" max="3" width="10.3828125" customWidth="1"/>
+    <col min="4" max="4" width="7.84375" customWidth="1"/>
+    <col min="5" max="5" width="7.53515625" customWidth="1"/>
+    <col min="6" max="6" width="5.15234375" customWidth="1"/>
+    <col min="7" max="7" width="56.15234375" customWidth="1"/>
+    <col min="8" max="8" width="5.15234375" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="6.85546875" customWidth="1"/>
-    <col min="11" max="11" width="18.7109375" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" customWidth="1"/>
-    <col min="15" max="15" width="33.5703125" customWidth="1"/>
-    <col min="16" max="16" width="4.7109375" customWidth="1"/>
-    <col min="17" max="17" width="42.85546875" customWidth="1"/>
-    <col min="18" max="18" width="6.7109375" customWidth="1"/>
-    <col min="19" max="19" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.84375" customWidth="1"/>
+    <col min="11" max="11" width="18.69140625" customWidth="1"/>
+    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.53515625" customWidth="1"/>
+    <col min="14" max="14" width="6.84375" customWidth="1"/>
+    <col min="15" max="15" width="33.53515625" customWidth="1"/>
+    <col min="16" max="16" width="4.69140625" customWidth="1"/>
+    <col min="17" max="17" width="42.84375" customWidth="1"/>
+    <col min="18" max="18" width="6.69140625" customWidth="1"/>
+    <col min="19" max="19" width="6.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>10</v>
       </c>
@@ -7151,7 +8369,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -7210,7 +8428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="20">
         <v>3</v>
       </c>
@@ -7269,7 +8487,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="20">
         <v>4</v>
       </c>
@@ -7328,7 +8546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="20">
         <v>5</v>
       </c>
@@ -7387,7 +8605,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20">
         <v>6</v>
       </c>
@@ -7446,7 +8664,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20">
         <v>7</v>
       </c>
@@ -7505,7 +8723,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20">
         <v>8</v>
       </c>
@@ -7564,7 +8782,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20">
         <v>9</v>
       </c>
@@ -7623,7 +8841,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20">
         <v>10</v>
       </c>
@@ -7682,7 +8900,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20">
         <v>11</v>
       </c>
@@ -7741,7 +8959,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20">
         <v>12</v>
       </c>
@@ -7800,7 +9018,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="20">
         <v>13</v>
       </c>
@@ -7859,7 +9077,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="20">
         <v>14</v>
       </c>
@@ -7918,7 +9136,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20">
         <v>15</v>
       </c>
@@ -7977,7 +9195,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20">
         <v>16</v>
       </c>
@@ -8036,7 +9254,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="20">
         <v>17</v>
       </c>
@@ -8095,7 +9313,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20">
         <v>18</v>
       </c>
@@ -8154,7 +9372,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20">
         <v>19</v>
       </c>
@@ -8213,7 +9431,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="20">
         <v>20</v>
       </c>
@@ -8272,7 +9490,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="20">
         <v>21</v>
       </c>
@@ -8331,7 +9549,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="20">
         <v>22</v>
       </c>
